--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -9001,80 +9001,316 @@
       </c>
     </row>
     <row r="115" ht="15" customHeight="1">
-      <c r="A115" s="5" t="n"/>
-      <c r="B115" s="6" t="n"/>
-      <c r="C115" s="5" t="n"/>
-      <c r="D115" s="7" t="n"/>
-      <c r="E115" s="6" t="n"/>
-      <c r="F115" s="6" t="n"/>
-      <c r="G115" s="6" t="n"/>
-      <c r="H115" s="6" t="n"/>
-      <c r="I115" s="6" t="n"/>
-      <c r="J115" s="7" t="n"/>
-      <c r="K115" s="5" t="n"/>
-      <c r="L115" s="6" t="n"/>
-      <c r="M115" s="5" t="n"/>
-      <c r="N115" s="5" t="n"/>
-      <c r="O115" s="5" t="n"/>
-      <c r="P115" s="8" t="n"/>
-      <c r="Q115" s="9" t="n"/>
+      <c r="A115" s="12" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B115" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C115" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D115" s="14" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E115" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F115" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G115" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="H115" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I115" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J115" s="14" t="inlineStr"/>
+      <c r="K115" s="12" t="inlineStr">
+        <is>
+          <t>116_Austria_2013_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L115" s="13" t="inlineStr"/>
+      <c r="M115" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N115" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O115" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P115" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q115" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+This coin features a gentian, as part of a floral series, symbolising a duty to the environment and the part Austria is playing in the development of a Community environmental policy.</t>
+        </is>
+      </c>
     </row>
     <row r="116" ht="15" customHeight="1">
-      <c r="A116" s="5" t="n"/>
-      <c r="B116" s="6" t="n"/>
-      <c r="C116" s="5" t="n"/>
-      <c r="D116" s="7" t="n"/>
-      <c r="E116" s="6" t="n"/>
-      <c r="F116" s="6" t="n"/>
-      <c r="G116" s="6" t="n"/>
-      <c r="H116" s="6" t="n"/>
-      <c r="I116" s="6" t="n"/>
-      <c r="J116" s="7" t="n"/>
-      <c r="K116" s="5" t="n"/>
-      <c r="L116" s="6" t="n"/>
-      <c r="M116" s="5" t="n"/>
-      <c r="N116" s="5" t="n"/>
-      <c r="O116" s="5" t="n"/>
-      <c r="P116" s="8" t="n"/>
-      <c r="Q116" s="9" t="n"/>
+      <c r="A116" s="12" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B116" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C116" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D116" s="14" t="n">
+        <v>2013</v>
+      </c>
+      <c r="E116" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F116" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G116" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="H116" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I116" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J116" s="14" t="inlineStr"/>
+      <c r="K116" s="12" t="inlineStr">
+        <is>
+          <t>117_Austria_2013_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L116" s="13" t="inlineStr"/>
+      <c r="M116" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N116" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O116" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P116" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q116" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+This coin features an edelweiss, as part of a floral series, symbolising a duty to the environment and the part Austria is playing in the development of a Community environmental policy.</t>
+        </is>
+      </c>
     </row>
     <row r="117" ht="15" customHeight="1">
-      <c r="A117" s="5" t="n"/>
-      <c r="B117" s="6" t="n"/>
-      <c r="C117" s="5" t="n"/>
-      <c r="D117" s="7" t="n"/>
-      <c r="E117" s="6" t="n"/>
-      <c r="F117" s="6" t="n"/>
-      <c r="G117" s="6" t="n"/>
-      <c r="H117" s="6" t="n"/>
-      <c r="I117" s="6" t="n"/>
-      <c r="J117" s="7" t="n"/>
-      <c r="K117" s="5" t="n"/>
-      <c r="L117" s="6" t="n"/>
-      <c r="M117" s="5" t="n"/>
-      <c r="N117" s="5" t="n"/>
-      <c r="O117" s="5" t="n"/>
-      <c r="P117" s="8" t="n"/>
-      <c r="Q117" s="9" t="n"/>
+      <c r="A117" s="12" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B117" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C117" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D117" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E117" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F117" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G117" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="H117" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I117" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J117" s="14" t="inlineStr"/>
+      <c r="K117" s="12" t="inlineStr">
+        <is>
+          <t>118_Austria_2002_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L117" s="13" t="inlineStr"/>
+      <c r="M117" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N117" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O117" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P117" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q117" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+This coin features alpine primroses, as part of a floral series, symbolising a duty to the environment and the part Austria is playing in the development of a Community environmental policy.</t>
+        </is>
+      </c>
     </row>
     <row r="118" ht="15" customHeight="1">
-      <c r="A118" s="5" t="n"/>
-      <c r="B118" s="6" t="n"/>
-      <c r="C118" s="5" t="n"/>
-      <c r="D118" s="7" t="n"/>
-      <c r="E118" s="6" t="n"/>
-      <c r="F118" s="6" t="n"/>
-      <c r="G118" s="6" t="n"/>
-      <c r="H118" s="6" t="n"/>
-      <c r="I118" s="6" t="n"/>
-      <c r="J118" s="7" t="n"/>
-      <c r="K118" s="5" t="n"/>
-      <c r="L118" s="6" t="n"/>
-      <c r="M118" s="5" t="n"/>
-      <c r="N118" s="5" t="n"/>
-      <c r="O118" s="5" t="n"/>
-      <c r="P118" s="8" t="n"/>
-      <c r="Q118" s="9" t="n"/>
+      <c r="A118" s="12" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B118" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C118" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D118" s="14" t="n">
+        <v>2011</v>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F118" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G118" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="H118" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I118" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J118" s="14" t="inlineStr"/>
+      <c r="K118" s="12" t="inlineStr">
+        <is>
+          <t>119_Austria_2011_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L118" s="13" t="inlineStr"/>
+      <c r="M118" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N118" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O118" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P118" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q118" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+St. Stephen's Cathedral, one of the jewels of Viennese Gothic architecture and a popular tourist venue, is depicted on this coin.</t>
+        </is>
+      </c>
     </row>
     <row r="119" ht="15" customHeight="1">
       <c r="A119" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -9313,99 +9313,397 @@
       </c>
     </row>
     <row r="119" ht="15" customHeight="1">
-      <c r="A119" s="5" t="n"/>
-      <c r="B119" s="6" t="n"/>
-      <c r="C119" s="5" t="n"/>
-      <c r="D119" s="7" t="n"/>
-      <c r="E119" s="6" t="n"/>
-      <c r="F119" s="6" t="n"/>
-      <c r="G119" s="6" t="n"/>
-      <c r="H119" s="6" t="n"/>
-      <c r="I119" s="6" t="n"/>
-      <c r="J119" s="7" t="n"/>
-      <c r="K119" s="5" t="n"/>
-      <c r="L119" s="6" t="n"/>
-      <c r="M119" s="5" t="n"/>
-      <c r="N119" s="5" t="n"/>
-      <c r="O119" s="5" t="n"/>
-      <c r="P119" s="8" t="n"/>
-      <c r="Q119" s="9" t="n"/>
+      <c r="A119" s="12" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B119" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C119" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D119" s="14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F119" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G119" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="H119" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I119" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="inlineStr"/>
+      <c r="K119" s="12" t="inlineStr">
+        <is>
+          <t>120_Austria_2021_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L119" s="13" t="inlineStr"/>
+      <c r="M119" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N119" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O119" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P119" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q119" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+This design features the Belvedere Palace, one of the most beautiful baroque palaces in Austria. It was here that the treaty re-establishing the sovereignty of Austria was signed in 1955, making its name synonymous with freedom.</t>
+        </is>
+      </c>
     </row>
     <row r="120" ht="15" customHeight="1">
-      <c r="A120" s="5" t="n"/>
-      <c r="B120" s="6" t="n"/>
-      <c r="C120" s="5" t="n"/>
-      <c r="D120" s="7" t="n"/>
-      <c r="E120" s="6" t="n"/>
-      <c r="F120" s="6" t="n"/>
-      <c r="G120" s="6" t="n"/>
-      <c r="H120" s="6" t="n"/>
-      <c r="I120" s="6" t="n"/>
-      <c r="J120" s="7" t="n"/>
-      <c r="K120" s="5" t="n"/>
-      <c r="L120" s="6" t="n"/>
-      <c r="M120" s="5" t="n"/>
-      <c r="N120" s="5" t="n"/>
-      <c r="O120" s="5" t="n"/>
-      <c r="P120" s="8" t="n"/>
-      <c r="Q120" s="9" t="n"/>
+      <c r="A120" s="12" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B120" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C120" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D120" s="14" t="n">
+        <v>2021</v>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F120" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G120" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="H120" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I120" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J120" s="14" t="inlineStr"/>
+      <c r="K120" s="12" t="inlineStr">
+        <is>
+          <t>121_Austria_2021_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L120" s="13" t="inlineStr"/>
+      <c r="M120" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N120" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O120" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P120" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q120" s="16" t="inlineStr">
+        <is>
+          <t>Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs.
+This coin shows the secession building in Vienna, illustrating the birth of art nouveau in Austria. The building symbolises the birth of a new age and represents a bridge to a new monetary era.</t>
+        </is>
+      </c>
     </row>
     <row r="121" ht="15" customHeight="1">
-      <c r="A121" s="5" t="n"/>
-      <c r="B121" s="6" t="n"/>
-      <c r="C121" s="5" t="n"/>
-      <c r="D121" s="7" t="n"/>
-      <c r="E121" s="6" t="n"/>
-      <c r="F121" s="6" t="n"/>
-      <c r="G121" s="6" t="n"/>
-      <c r="H121" s="6" t="n"/>
-      <c r="I121" s="6" t="n"/>
-      <c r="J121" s="7" t="n"/>
-      <c r="K121" s="5" t="n"/>
-      <c r="L121" s="6" t="n"/>
-      <c r="M121" s="5" t="n"/>
-      <c r="N121" s="5" t="n"/>
-      <c r="O121" s="5" t="n"/>
-      <c r="P121" s="8" t="n"/>
-      <c r="Q121" s="9" t="n"/>
+      <c r="A121" s="12" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B121" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C121" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D121" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F121" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G121" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="H121" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I121" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J121" s="14" t="inlineStr"/>
+      <c r="K121" s="12" t="inlineStr">
+        <is>
+          <t>122_Bulgaria_2026_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L121" s="13" t="inlineStr"/>
+      <c r="M121" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N121" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O121" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P121" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q121" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 1 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКА” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="122" ht="15" customHeight="1">
-      <c r="A122" s="5" t="n"/>
-      <c r="B122" s="6" t="n"/>
-      <c r="C122" s="5" t="n"/>
-      <c r="D122" s="7" t="n"/>
-      <c r="E122" s="6" t="n"/>
-      <c r="F122" s="6" t="n"/>
-      <c r="G122" s="6" t="n"/>
-      <c r="H122" s="6" t="n"/>
-      <c r="I122" s="6" t="n"/>
-      <c r="J122" s="7" t="n"/>
-      <c r="K122" s="5" t="n"/>
-      <c r="L122" s="6" t="n"/>
-      <c r="M122" s="5" t="n"/>
-      <c r="N122" s="5" t="n"/>
-      <c r="O122" s="5" t="n"/>
-      <c r="P122" s="8" t="n"/>
-      <c r="Q122" s="9" t="n"/>
+      <c r="A122" s="12" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B122" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C122" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D122" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F122" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G122" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="H122" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I122" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="inlineStr"/>
+      <c r="K122" s="12" t="inlineStr">
+        <is>
+          <t>123_Bulgaria_2026_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L122" s="13" t="inlineStr"/>
+      <c r="M122" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N122" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O122" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P122" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q122" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 2 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКИ” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="123" ht="15" customHeight="1">
-      <c r="A123" s="5" t="n"/>
-      <c r="B123" s="6" t="n"/>
-      <c r="C123" s="5" t="n"/>
-      <c r="D123" s="7" t="n"/>
-      <c r="E123" s="6" t="n"/>
-      <c r="F123" s="6" t="n"/>
-      <c r="G123" s="6" t="n"/>
-      <c r="H123" s="6" t="n"/>
-      <c r="I123" s="6" t="n"/>
-      <c r="J123" s="7" t="n"/>
-      <c r="K123" s="5" t="n"/>
-      <c r="L123" s="6" t="n"/>
-      <c r="M123" s="5" t="n"/>
-      <c r="N123" s="5" t="n"/>
-      <c r="O123" s="5" t="n"/>
-      <c r="P123" s="8" t="n"/>
-      <c r="Q123" s="9" t="n"/>
+      <c r="A123" s="12" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B123" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C123" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D123" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F123" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G123" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="H123" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I123" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J123" s="14" t="inlineStr"/>
+      <c r="K123" s="12" t="inlineStr">
+        <is>
+          <t>124_Bulgaria_2026_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L123" s="13" t="inlineStr"/>
+      <c r="M123" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N123" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O123" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P123" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q123" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 5 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКИ” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="124" ht="15" customHeight="1">
       <c r="A124" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -9706,175 +9706,709 @@
       </c>
     </row>
     <row r="124" ht="15" customHeight="1">
-      <c r="A124" s="5" t="n"/>
-      <c r="B124" s="6" t="n"/>
-      <c r="C124" s="5" t="n"/>
-      <c r="D124" s="7" t="n"/>
-      <c r="E124" s="6" t="n"/>
-      <c r="F124" s="6" t="n"/>
-      <c r="G124" s="6" t="n"/>
-      <c r="H124" s="6" t="n"/>
-      <c r="I124" s="6" t="n"/>
-      <c r="J124" s="7" t="n"/>
-      <c r="K124" s="5" t="n"/>
-      <c r="L124" s="6" t="n"/>
-      <c r="M124" s="5" t="n"/>
-      <c r="N124" s="5" t="n"/>
-      <c r="O124" s="5" t="n"/>
-      <c r="P124" s="8" t="n"/>
-      <c r="Q124" s="9" t="n"/>
+      <c r="A124" s="12" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B124" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C124" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D124" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F124" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G124" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="H124" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I124" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J124" s="14" t="inlineStr"/>
+      <c r="K124" s="12" t="inlineStr">
+        <is>
+          <t>125_Bulgaria_2026_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L124" s="13" t="inlineStr"/>
+      <c r="M124" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N124" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O124" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P124" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q124" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 10 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКИ” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="125" ht="15" customHeight="1">
-      <c r="A125" s="5" t="n"/>
-      <c r="B125" s="6" t="n"/>
-      <c r="C125" s="5" t="n"/>
-      <c r="D125" s="7" t="n"/>
-      <c r="E125" s="6" t="n"/>
-      <c r="F125" s="6" t="n"/>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="6" t="n"/>
-      <c r="I125" s="6" t="n"/>
-      <c r="J125" s="7" t="n"/>
-      <c r="K125" s="5" t="n"/>
-      <c r="L125" s="6" t="n"/>
-      <c r="M125" s="5" t="n"/>
-      <c r="N125" s="5" t="n"/>
-      <c r="O125" s="5" t="n"/>
-      <c r="P125" s="8" t="n"/>
-      <c r="Q125" s="9" t="n"/>
+      <c r="A125" s="12" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B125" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C125" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D125" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F125" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G125" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="H125" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I125" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr"/>
+      <c r="K125" s="12" t="inlineStr">
+        <is>
+          <t>126_Bulgaria_2026_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L125" s="13" t="inlineStr"/>
+      <c r="M125" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N125" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O125" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P125" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q125" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 20 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКИ” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="126" ht="15" customHeight="1">
-      <c r="A126" s="5" t="n"/>
-      <c r="B126" s="6" t="n"/>
-      <c r="C126" s="5" t="n"/>
-      <c r="D126" s="7" t="n"/>
-      <c r="E126" s="6" t="n"/>
-      <c r="F126" s="6" t="n"/>
-      <c r="G126" s="6" t="n"/>
-      <c r="H126" s="6" t="n"/>
-      <c r="I126" s="6" t="n"/>
-      <c r="J126" s="7" t="n"/>
-      <c r="K126" s="5" t="n"/>
-      <c r="L126" s="6" t="n"/>
-      <c r="M126" s="5" t="n"/>
-      <c r="N126" s="5" t="n"/>
-      <c r="O126" s="5" t="n"/>
-      <c r="P126" s="8" t="n"/>
-      <c r="Q126" s="9" t="n"/>
+      <c r="A126" s="12" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B126" s="13" t="inlineStr">
+        <is>
+          <t>Bulgaria</t>
+        </is>
+      </c>
+      <c r="C126" s="12" t="inlineStr">
+        <is>
+          <t>BG</t>
+        </is>
+      </c>
+      <c r="D126" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F126" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G126" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="H126" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I126" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="inlineStr"/>
+      <c r="K126" s="12" t="inlineStr">
+        <is>
+          <t>127_Bulgaria_2026_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L126" s="13" t="inlineStr"/>
+      <c r="M126" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N126" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O126" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P126" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Bulgaria.</t>
+        </is>
+      </c>
+      <c r="Q126" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The 50 cent coin features a relief image of the Madara Horseman – an eighth-century rock carving and UNESCO World Heritage Site. The horseman faces right, spearing a lion – a powerful symbol from Bulgaria’s past.
+The design also includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “СТОТИНКИ” (“CENT”) in Cyrillic script.</t>
+        </is>
+      </c>
     </row>
     <row r="127" ht="15" customHeight="1">
-      <c r="A127" s="5" t="n"/>
-      <c r="B127" s="6" t="n"/>
-      <c r="C127" s="5" t="n"/>
-      <c r="D127" s="7" t="n"/>
-      <c r="E127" s="6" t="n"/>
-      <c r="F127" s="6" t="n"/>
-      <c r="G127" s="6" t="n"/>
-      <c r="H127" s="6" t="n"/>
-      <c r="I127" s="6" t="n"/>
-      <c r="J127" s="7" t="n"/>
-      <c r="K127" s="5" t="n"/>
-      <c r="L127" s="6" t="n"/>
-      <c r="M127" s="5" t="n"/>
-      <c r="N127" s="5" t="n"/>
-      <c r="O127" s="5" t="n"/>
-      <c r="P127" s="8" t="n"/>
-      <c r="Q127" s="9" t="n"/>
+      <c r="A127" s="12" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B127" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C127" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D127" s="14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F127" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G127" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="H127" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I127" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J127" s="14" t="inlineStr"/>
+      <c r="K127" s="12" t="inlineStr">
+        <is>
+          <t>128_Croatia_2023_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L127" s="13" t="inlineStr"/>
+      <c r="M127" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N127" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O127" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P127" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q127" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 1-cent coin shows a motif of the letters “HR” in the angular Glagolitic script. The Glagolitic alphabet is the oldest known Slavic script and was used in Croatia until the 19th century. The coin was designed by Maja Škripelj and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="128" ht="15" customHeight="1">
-      <c r="A128" s="5" t="n"/>
-      <c r="B128" s="6" t="n"/>
-      <c r="C128" s="5" t="n"/>
-      <c r="D128" s="7" t="n"/>
-      <c r="E128" s="6" t="n"/>
-      <c r="F128" s="6" t="n"/>
-      <c r="G128" s="6" t="n"/>
-      <c r="H128" s="6" t="n"/>
-      <c r="I128" s="6" t="n"/>
-      <c r="J128" s="7" t="n"/>
-      <c r="K128" s="5" t="n"/>
-      <c r="L128" s="6" t="n"/>
-      <c r="M128" s="5" t="n"/>
-      <c r="N128" s="5" t="n"/>
-      <c r="O128" s="5" t="n"/>
-      <c r="P128" s="8" t="n"/>
-      <c r="Q128" s="9" t="n"/>
+      <c r="A128" s="12" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B128" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C128" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D128" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F128" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G128" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="H128" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I128" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J128" s="14" t="inlineStr"/>
+      <c r="K128" s="12" t="inlineStr">
+        <is>
+          <t>129_Croatia_2025_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L128" s="13" t="inlineStr"/>
+      <c r="M128" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N128" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O128" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P128" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q128" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 2-cent coin shows a motif of the letters “HR” in the angular Glagolitic script. The Glagolitic alphabet is the oldest known Slavic script and was used in Croatia until the 19th century. The coin was designed by Maja Škripelj and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="129" ht="15" customHeight="1">
-      <c r="A129" s="5" t="n"/>
-      <c r="B129" s="6" t="n"/>
-      <c r="C129" s="5" t="n"/>
-      <c r="D129" s="7" t="n"/>
-      <c r="E129" s="6" t="n"/>
-      <c r="F129" s="6" t="n"/>
-      <c r="G129" s="6" t="n"/>
-      <c r="H129" s="6" t="n"/>
-      <c r="I129" s="6" t="n"/>
-      <c r="J129" s="7" t="n"/>
-      <c r="K129" s="5" t="n"/>
-      <c r="L129" s="6" t="n"/>
-      <c r="M129" s="5" t="n"/>
-      <c r="N129" s="5" t="n"/>
-      <c r="O129" s="5" t="n"/>
-      <c r="P129" s="8" t="n"/>
-      <c r="Q129" s="9" t="n"/>
+      <c r="A129" s="12" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B129" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C129" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D129" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F129" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G129" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="H129" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I129" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J129" s="14" t="inlineStr"/>
+      <c r="K129" s="12" t="inlineStr">
+        <is>
+          <t>130_Croatia_2025_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L129" s="13" t="inlineStr"/>
+      <c r="M129" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N129" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O129" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P129" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q129" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 5-cent coin shows a motif of the letters “HR” in the angular Glagolitic script. The Glagolitic alphabet is the oldest known Slavic script and was used in Croatia until the 19th century. The coin was designed by Maja Škripelj and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="130" ht="15" customHeight="1">
-      <c r="A130" s="5" t="n"/>
-      <c r="B130" s="6" t="n"/>
-      <c r="C130" s="5" t="n"/>
-      <c r="D130" s="7" t="n"/>
-      <c r="E130" s="6" t="n"/>
-      <c r="F130" s="6" t="n"/>
-      <c r="G130" s="6" t="n"/>
-      <c r="H130" s="6" t="n"/>
-      <c r="I130" s="6" t="n"/>
-      <c r="J130" s="7" t="n"/>
-      <c r="K130" s="5" t="n"/>
-      <c r="L130" s="6" t="n"/>
-      <c r="M130" s="5" t="n"/>
-      <c r="N130" s="5" t="n"/>
-      <c r="O130" s="5" t="n"/>
-      <c r="P130" s="8" t="n"/>
-      <c r="Q130" s="9" t="n"/>
+      <c r="A130" s="12" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B130" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C130" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D130" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F130" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G130" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="H130" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I130" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J130" s="14" t="inlineStr"/>
+      <c r="K130" s="12" t="inlineStr">
+        <is>
+          <t>131_Croatia_2025_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L130" s="13" t="inlineStr"/>
+      <c r="M130" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N130" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O130" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P130" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q130" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 10-cent coin features a portrait of inventor and engineer Nikola Tesla, who developed alternating current technology. The coin was designed by Ivan Domagoj Račić and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="131" ht="15" customHeight="1">
-      <c r="A131" s="5" t="n"/>
-      <c r="B131" s="6" t="n"/>
-      <c r="C131" s="5" t="n"/>
-      <c r="D131" s="7" t="n"/>
-      <c r="E131" s="6" t="n"/>
-      <c r="F131" s="6" t="n"/>
-      <c r="G131" s="6" t="n"/>
-      <c r="H131" s="6" t="n"/>
-      <c r="I131" s="6" t="n"/>
-      <c r="J131" s="7" t="n"/>
-      <c r="K131" s="5" t="n"/>
-      <c r="L131" s="6" t="n"/>
-      <c r="M131" s="5" t="n"/>
-      <c r="N131" s="5" t="n"/>
-      <c r="O131" s="5" t="n"/>
-      <c r="P131" s="8" t="n"/>
-      <c r="Q131" s="9" t="n"/>
+      <c r="A131" s="12" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B131" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C131" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="n">
+        <v>2025</v>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F131" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G131" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="H131" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I131" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="inlineStr"/>
+      <c r="K131" s="12" t="inlineStr">
+        <is>
+          <t>132_Croatia_2025_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L131" s="13" t="inlineStr"/>
+      <c r="M131" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N131" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O131" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P131" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q131" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 20-cent coin features a portrait of inventor and engineer Nikola Tesla, who developed alternating current technology. The coin was designed by Ivan Domagoj Račić and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="132" ht="15" customHeight="1">
-      <c r="A132" s="5" t="n"/>
-      <c r="B132" s="6" t="n"/>
-      <c r="C132" s="5" t="n"/>
-      <c r="D132" s="7" t="n"/>
-      <c r="E132" s="6" t="n"/>
-      <c r="F132" s="6" t="n"/>
-      <c r="G132" s="6" t="n"/>
-      <c r="H132" s="6" t="n"/>
-      <c r="I132" s="6" t="n"/>
-      <c r="J132" s="7" t="n"/>
-      <c r="K132" s="5" t="n"/>
-      <c r="L132" s="6" t="n"/>
-      <c r="M132" s="5" t="n"/>
-      <c r="N132" s="5" t="n"/>
-      <c r="O132" s="5" t="n"/>
-      <c r="P132" s="8" t="n"/>
-      <c r="Q132" s="9" t="n"/>
+      <c r="A132" s="12" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B132" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C132" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D132" s="14" t="n">
+        <v>2023</v>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F132" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G132" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="H132" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I132" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J132" s="14" t="inlineStr"/>
+      <c r="K132" s="12" t="inlineStr">
+        <is>
+          <t>133_Croatia_2023_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L132" s="13" t="inlineStr"/>
+      <c r="M132" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N132" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O132" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P132" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q132" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The 50-cent coin features a portrait of inventor and engineer Nikola Tesla, who developed alternating current technology. The coin was designed by Ivan Domagoj Račić and includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.</t>
+        </is>
+      </c>
     </row>
     <row r="133" ht="15" customHeight="1">
       <c r="A133" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -10411,118 +10411,472 @@
       </c>
     </row>
     <row r="133" ht="15" customHeight="1">
-      <c r="A133" s="5" t="n"/>
-      <c r="B133" s="6" t="n"/>
-      <c r="C133" s="5" t="n"/>
-      <c r="D133" s="7" t="n"/>
-      <c r="E133" s="6" t="n"/>
-      <c r="F133" s="6" t="n"/>
-      <c r="G133" s="6" t="n"/>
-      <c r="H133" s="6" t="n"/>
-      <c r="I133" s="6" t="n"/>
-      <c r="J133" s="7" t="n"/>
-      <c r="K133" s="5" t="n"/>
-      <c r="L133" s="6" t="n"/>
-      <c r="M133" s="5" t="n"/>
-      <c r="N133" s="5" t="n"/>
-      <c r="O133" s="5" t="n"/>
-      <c r="P133" s="8" t="n"/>
-      <c r="Q133" s="9" t="n"/>
+      <c r="A133" s="12" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B133" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C133" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D133" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E133" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F133" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="H133" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I133" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J133" s="14" t="inlineStr"/>
+      <c r="K133" s="12" t="inlineStr">
+        <is>
+          <t>134_Germany_2002_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L133" s="13" t="inlineStr"/>
+      <c r="M133" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N133" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O133" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P133" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q133" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+1, 2 and 5-cent coins: the oak twig, reminiscent of that found on the former German pfennig coins, provides the motif for these coins. It was designed by Professor Rolf Lederbogen.</t>
+        </is>
+      </c>
     </row>
     <row r="134" ht="15" customHeight="1">
-      <c r="A134" s="5" t="n"/>
-      <c r="B134" s="6" t="n"/>
-      <c r="C134" s="5" t="n"/>
-      <c r="D134" s="7" t="n"/>
-      <c r="E134" s="6" t="n"/>
-      <c r="F134" s="6" t="n"/>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="n"/>
-      <c r="I134" s="6" t="n"/>
-      <c r="J134" s="7" t="n"/>
-      <c r="K134" s="5" t="n"/>
-      <c r="L134" s="6" t="n"/>
-      <c r="M134" s="5" t="n"/>
-      <c r="N134" s="5" t="n"/>
-      <c r="O134" s="5" t="n"/>
-      <c r="P134" s="8" t="n"/>
-      <c r="Q134" s="9" t="n"/>
+      <c r="A134" s="12" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B134" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C134" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D134" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E134" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F134" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G134" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="H134" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I134" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J134" s="14" t="inlineStr"/>
+      <c r="K134" s="12" t="inlineStr">
+        <is>
+          <t>135_Germany_2002_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L134" s="13" t="inlineStr"/>
+      <c r="M134" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N134" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O134" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P134" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q134" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+1, 2 and 5-cent coins: the oak twig, reminiscent of that found on the former German pfennig coins, provides the motif for these coins. It was designed by Professor Rolf Lederbogen.</t>
+        </is>
+      </c>
     </row>
     <row r="135" ht="15" customHeight="1">
-      <c r="A135" s="5" t="n"/>
-      <c r="B135" s="6" t="n"/>
-      <c r="C135" s="5" t="n"/>
-      <c r="D135" s="7" t="n"/>
-      <c r="E135" s="6" t="n"/>
-      <c r="F135" s="6" t="n"/>
-      <c r="G135" s="6" t="n"/>
-      <c r="H135" s="6" t="n"/>
-      <c r="I135" s="6" t="n"/>
-      <c r="J135" s="7" t="n"/>
-      <c r="K135" s="5" t="n"/>
-      <c r="L135" s="6" t="n"/>
-      <c r="M135" s="5" t="n"/>
-      <c r="N135" s="5" t="n"/>
-      <c r="O135" s="5" t="n"/>
-      <c r="P135" s="8" t="n"/>
-      <c r="Q135" s="9" t="n"/>
+      <c r="A135" s="12" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B135" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C135" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D135" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E135" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F135" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G135" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="H135" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I135" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="inlineStr"/>
+      <c r="K135" s="12" t="inlineStr">
+        <is>
+          <t>136_Germany_2002_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L135" s="13" t="inlineStr"/>
+      <c r="M135" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N135" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O135" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P135" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q135" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+1, 2 and 5-cent coins: the oak twig, reminiscent of that found on the former German pfennig coins, provides the motif for these coins. It was designed by Professor Rolf Lederbogen.</t>
+        </is>
+      </c>
     </row>
     <row r="136" ht="15" customHeight="1">
-      <c r="A136" s="5" t="n"/>
-      <c r="B136" s="6" t="n"/>
-      <c r="C136" s="5" t="n"/>
-      <c r="D136" s="7" t="n"/>
-      <c r="E136" s="6" t="n"/>
-      <c r="F136" s="6" t="n"/>
-      <c r="G136" s="6" t="n"/>
-      <c r="H136" s="6" t="n"/>
-      <c r="I136" s="6" t="n"/>
-      <c r="J136" s="7" t="n"/>
-      <c r="K136" s="5" t="n"/>
-      <c r="L136" s="6" t="n"/>
-      <c r="M136" s="5" t="n"/>
-      <c r="N136" s="5" t="n"/>
-      <c r="O136" s="5" t="n"/>
-      <c r="P136" s="8" t="n"/>
-      <c r="Q136" s="9" t="n"/>
+      <c r="A136" s="12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B136" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C136" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D136" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E136" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F136" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G136" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="H136" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I136" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J136" s="14" t="inlineStr"/>
+      <c r="K136" s="12" t="inlineStr">
+        <is>
+          <t>137_Germany_2002_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L136" s="13" t="inlineStr"/>
+      <c r="M136" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N136" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O136" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P136" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q136" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.</t>
+        </is>
+      </c>
     </row>
     <row r="137" ht="15" customHeight="1">
-      <c r="A137" s="5" t="n"/>
-      <c r="B137" s="6" t="n"/>
-      <c r="C137" s="5" t="n"/>
-      <c r="D137" s="7" t="n"/>
-      <c r="E137" s="6" t="n"/>
-      <c r="F137" s="6" t="n"/>
-      <c r="G137" s="6" t="n"/>
-      <c r="H137" s="6" t="n"/>
-      <c r="I137" s="6" t="n"/>
-      <c r="J137" s="7" t="n"/>
-      <c r="K137" s="5" t="n"/>
-      <c r="L137" s="6" t="n"/>
-      <c r="M137" s="5" t="n"/>
-      <c r="N137" s="5" t="n"/>
-      <c r="O137" s="5" t="n"/>
-      <c r="P137" s="8" t="n"/>
-      <c r="Q137" s="9" t="n"/>
+      <c r="A137" s="12" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B137" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C137" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D137" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E137" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F137" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G137" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="H137" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I137" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J137" s="14" t="inlineStr"/>
+      <c r="K137" s="12" t="inlineStr">
+        <is>
+          <t>138_Germany_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L137" s="13" t="inlineStr"/>
+      <c r="M137" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N137" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O137" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P137" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q137" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.</t>
+        </is>
+      </c>
     </row>
     <row r="138" ht="15" customHeight="1">
-      <c r="A138" s="5" t="n"/>
-      <c r="B138" s="6" t="n"/>
-      <c r="C138" s="5" t="n"/>
-      <c r="D138" s="7" t="n"/>
-      <c r="E138" s="6" t="n"/>
-      <c r="F138" s="6" t="n"/>
-      <c r="G138" s="6" t="n"/>
-      <c r="H138" s="6" t="n"/>
-      <c r="I138" s="6" t="n"/>
-      <c r="J138" s="7" t="n"/>
-      <c r="K138" s="5" t="n"/>
-      <c r="L138" s="6" t="n"/>
-      <c r="M138" s="5" t="n"/>
-      <c r="N138" s="5" t="n"/>
-      <c r="O138" s="5" t="n"/>
-      <c r="P138" s="8" t="n"/>
-      <c r="Q138" s="9" t="n"/>
+      <c r="A138" s="12" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B138" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C138" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D138" s="14" t="n">
+        <v>2024</v>
+      </c>
+      <c r="E138" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F138" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G138" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="H138" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I138" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J138" s="14" t="inlineStr"/>
+      <c r="K138" s="12" t="inlineStr">
+        <is>
+          <t>139_Germany_2024_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L138" s="13" t="inlineStr"/>
+      <c r="M138" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N138" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O138" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P138" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q138" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins.
+10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.</t>
+        </is>
+      </c>
     </row>
     <row r="139" ht="15" customHeight="1">
       <c r="A139" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -10879,23 +10879,82 @@
       </c>
     </row>
     <row r="139" ht="15" customHeight="1">
-      <c r="A139" s="5" t="n"/>
-      <c r="B139" s="6" t="n"/>
-      <c r="C139" s="5" t="n"/>
-      <c r="D139" s="7" t="n"/>
-      <c r="E139" s="6" t="n"/>
-      <c r="F139" s="6" t="n"/>
-      <c r="G139" s="6" t="n"/>
-      <c r="H139" s="6" t="n"/>
-      <c r="I139" s="6" t="n"/>
-      <c r="J139" s="7" t="n"/>
-      <c r="K139" s="5" t="n"/>
-      <c r="L139" s="6" t="n"/>
-      <c r="M139" s="5" t="n"/>
-      <c r="N139" s="5" t="n"/>
-      <c r="O139" s="5" t="n"/>
-      <c r="P139" s="8" t="n"/>
-      <c r="Q139" s="9" t="n"/>
+      <c r="A139" s="12" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B139" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C139" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E139" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F139" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G139" s="13" t="inlineStr">
+        <is>
+          <t>1 Euro</t>
+        </is>
+      </c>
+      <c r="H139" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I139" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J139" s="14" t="inlineStr"/>
+      <c r="K139" s="12" t="inlineStr">
+        <is>
+          <t>140_Portugal_2002_1Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L139" s="13" t="inlineStr"/>
+      <c r="M139" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O139" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P139" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q139" s="16" t="inlineStr">
+        <is>
+          <t>Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs: 10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
+€1 and €2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144</t>
+        </is>
+      </c>
     </row>
     <row r="140" ht="15" customHeight="1">
       <c r="A140" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -5182,8 +5182,10 @@
           <t>ES</t>
         </is>
       </c>
-      <c r="D62" s="14" t="n">
-        <v>1999</v>
+      <c r="D62" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
       </c>
       <c r="E62" s="13" t="inlineStr">
         <is>
@@ -5195,14 +5197,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G62" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G62" s="13" t="inlineStr"/>
       <c r="H62" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>VG</t>
         </is>
       </c>
       <c r="I62" s="13" t="inlineStr">
@@ -10886,20 +10884,22 @@
       </c>
       <c r="B139" s="13" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C139" s="12" t="inlineStr">
         <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="D139" s="14" t="n">
-        <v>2002</v>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D139" s="14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
       </c>
       <c r="E139" s="13" t="inlineStr">
         <is>
-          <t>1 €</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="F139" s="13" t="inlineStr">
@@ -10907,14 +10907,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G139" s="13" t="inlineStr">
-        <is>
-          <t>1 Euro</t>
-        </is>
-      </c>
+      <c r="G139" s="13" t="inlineStr"/>
       <c r="H139" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="I139" s="13" t="inlineStr">
@@ -10925,188 +10921,629 @@
       <c r="J139" s="14" t="inlineStr"/>
       <c r="K139" s="12" t="inlineStr">
         <is>
-          <t>140_Portugal_2002_1Euro_Regular.jpeg</t>
+          <t>140_Vatican-City_2025_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L139" s="13" t="inlineStr"/>
       <c r="M139" s="12" t="inlineStr">
         <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N139" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O139" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P139" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
+        </is>
+      </c>
+      <c r="Q139" s="16" t="inlineStr"/>
+    </row>
+    <row r="140" ht="15" customHeight="1">
+      <c r="A140" s="12" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B140" s="13" t="inlineStr">
+        <is>
+          <t>Vatican City</t>
+        </is>
+      </c>
+      <c r="C140" s="12" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D140" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E140" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F140" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G140" s="13" t="inlineStr"/>
+      <c r="H140" s="13" t="inlineStr">
+        <is>
+          <t>UNC</t>
+        </is>
+      </c>
+      <c r="I140" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J140" s="14" t="inlineStr"/>
+      <c r="K140" s="12" t="inlineStr">
+        <is>
+          <t>141_Vatican-City_2026_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L140" s="13" t="inlineStr"/>
+      <c r="M140" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N140" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O140" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P140" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Vatican City.</t>
+        </is>
+      </c>
+      <c r="Q140" s="16" t="inlineStr"/>
+    </row>
+    <row r="141" ht="15" customHeight="1">
+      <c r="A141" s="12" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B141" s="13" t="inlineStr">
+        <is>
+          <t>Vatican City</t>
+        </is>
+      </c>
+      <c r="C141" s="12" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D141" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E141" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F141" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G141" s="13" t="inlineStr"/>
+      <c r="H141" s="13" t="inlineStr">
+        <is>
+          <t>UNC</t>
+        </is>
+      </c>
+      <c r="I141" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J141" s="14" t="inlineStr"/>
+      <c r="K141" s="12" t="inlineStr">
+        <is>
+          <t>142_Vatican-City_2026_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L141" s="13" t="inlineStr"/>
+      <c r="M141" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N141" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O141" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P141" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Vatican City.</t>
+        </is>
+      </c>
+      <c r="Q141" s="16" t="inlineStr"/>
+    </row>
+    <row r="142" ht="15" customHeight="1">
+      <c r="A142" s="12" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B142" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C142" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D142" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E142" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F142" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G142" s="13" t="inlineStr"/>
+      <c r="H142" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I142" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J142" s="14" t="inlineStr"/>
+      <c r="K142" s="12" t="inlineStr">
+        <is>
+          <t>143_Slovenia_2023_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L142" s="13" t="inlineStr"/>
+      <c r="M142" s="12" t="inlineStr">
+        <is>
           <t>Bimetallic</t>
         </is>
       </c>
-      <c r="N139" s="12" t="inlineStr">
+      <c r="N142" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O142" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P142" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q142" s="16" t="inlineStr">
+        <is>
+          <t>This coin shows the poet France Prešeren and the inscription "Shivé naj vsi naródi" (God’s blessing on all nations) − a line taken from his poem "Zdravljica" which is also used in the country’s national anthem. Edge lettering of the €2 coin: SLOVENIJA followed by an engraved dot.</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="15" customHeight="1">
+      <c r="A143" s="12" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B143" s="13" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C143" s="12" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D143" s="14" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E143" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F143" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G143" s="13" t="inlineStr"/>
+      <c r="H143" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I143" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J143" s="14" t="inlineStr"/>
+      <c r="K143" s="12" t="inlineStr">
+        <is>
+          <t>144_Andorra_2030_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L143" s="13" t="inlineStr"/>
+      <c r="M143" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N143" s="12" t="inlineStr">
         <is>
           <t>7.50 g</t>
         </is>
       </c>
-      <c r="O139" s="12" t="inlineStr">
+      <c r="O143" s="12" t="inlineStr">
         <is>
           <t>23.25 mm</t>
         </is>
       </c>
-      <c r="P139" s="15" t="inlineStr">
+      <c r="P143" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Andorra.</t>
+        </is>
+      </c>
+      <c r="Q143" s="16" t="inlineStr">
+        <is>
+          <t>TETS COIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144" ht="15" customHeight="1">
+      <c r="A144" s="12" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B144" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C144" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D144" s="14" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="E144" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F144" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G144" s="13" t="inlineStr"/>
+      <c r="H144" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I144" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J144" s="14" t="inlineStr"/>
+      <c r="K144" s="12" t="inlineStr">
+        <is>
+          <t>145_Germany_2004_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L144" s="13" t="inlineStr"/>
+      <c r="M144" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N144" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O144" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P144" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q144" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins. 10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.
+€1 and €2 coins: the traditional symbol of German sovereignty, the eagle, surrounded by the stars of Europe, appears on these coins. This motif was designed by Heinz and Sneschana Russewa-Hoyer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="145" ht="15" customHeight="1">
+      <c r="A145" s="12" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B145" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C145" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D145" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E145" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F145" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G145" s="13" t="inlineStr"/>
+      <c r="H145" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I145" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J145" s="14" t="inlineStr"/>
+      <c r="K145" s="12" t="inlineStr">
+        <is>
+          <t>146_Greece_2023_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L145" s="13" t="inlineStr"/>
+      <c r="M145" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N145" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O145" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P145" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q145" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+The image of the owl featured in this design was copied from an ancient Athenian 4-drachma coin (fifth century BC).</t>
+        </is>
+      </c>
+    </row>
+    <row r="146" ht="15" customHeight="1">
+      <c r="A146" s="12" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B146" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C146" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F146" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G146" s="13" t="inlineStr"/>
+      <c r="H146" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I146" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J146" s="14" t="inlineStr"/>
+      <c r="K146" s="12" t="inlineStr">
+        <is>
+          <t>147_Italy_2011_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L146" s="13" t="inlineStr"/>
+      <c r="M146" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N146" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O146" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P146" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q146" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+This coin shows the famous drawing by Leonardo da Vinci, displayed in the gallery of the Academy in Venice, illustrating the ideal proportions of the human body.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147" ht="15" customHeight="1">
+      <c r="A147" s="12" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B147" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C147" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F147" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>1 Euro</t>
+        </is>
+      </c>
+      <c r="H147" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I147" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="inlineStr"/>
+      <c r="K147" s="12" t="inlineStr">
+        <is>
+          <t>148_Portugal_2002_1Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L147" s="13" t="inlineStr"/>
+      <c r="M147" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N147" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O147" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P147" s="15" t="inlineStr">
         <is>
           <t>Regular 1 € circulation coin of Portugal.</t>
         </is>
       </c>
-      <c r="Q139" s="16" t="inlineStr">
+      <c r="Q147" s="16" t="inlineStr">
         <is>
           <t>Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs: 10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
 €1 and €2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144</t>
         </is>
       </c>
-    </row>
-    <row r="140" ht="15" customHeight="1">
-      <c r="A140" s="5" t="n"/>
-      <c r="B140" s="6" t="n"/>
-      <c r="C140" s="5" t="n"/>
-      <c r="D140" s="7" t="n"/>
-      <c r="E140" s="6" t="n"/>
-      <c r="F140" s="6" t="n"/>
-      <c r="G140" s="6" t="n"/>
-      <c r="H140" s="6" t="n"/>
-      <c r="I140" s="6" t="n"/>
-      <c r="J140" s="7" t="n"/>
-      <c r="K140" s="5" t="n"/>
-      <c r="L140" s="6" t="n"/>
-      <c r="M140" s="5" t="n"/>
-      <c r="N140" s="5" t="n"/>
-      <c r="O140" s="5" t="n"/>
-      <c r="P140" s="8" t="n"/>
-      <c r="Q140" s="9" t="n"/>
-    </row>
-    <row r="141" ht="15" customHeight="1">
-      <c r="A141" s="5" t="n"/>
-      <c r="B141" s="6" t="n"/>
-      <c r="C141" s="5" t="n"/>
-      <c r="D141" s="7" t="n"/>
-      <c r="E141" s="6" t="n"/>
-      <c r="F141" s="6" t="n"/>
-      <c r="G141" s="6" t="n"/>
-      <c r="H141" s="6" t="n"/>
-      <c r="I141" s="6" t="n"/>
-      <c r="J141" s="7" t="n"/>
-      <c r="K141" s="5" t="n"/>
-      <c r="L141" s="6" t="n"/>
-      <c r="M141" s="5" t="n"/>
-      <c r="N141" s="5" t="n"/>
-      <c r="O141" s="5" t="n"/>
-      <c r="P141" s="8" t="n"/>
-      <c r="Q141" s="9" t="n"/>
-    </row>
-    <row r="142" ht="15" customHeight="1">
-      <c r="A142" s="5" t="n"/>
-      <c r="B142" s="6" t="n"/>
-      <c r="C142" s="5" t="n"/>
-      <c r="D142" s="7" t="n"/>
-      <c r="E142" s="6" t="n"/>
-      <c r="F142" s="6" t="n"/>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="n"/>
-      <c r="I142" s="6" t="n"/>
-      <c r="J142" s="7" t="n"/>
-      <c r="K142" s="5" t="n"/>
-      <c r="L142" s="6" t="n"/>
-      <c r="M142" s="5" t="n"/>
-      <c r="N142" s="5" t="n"/>
-      <c r="O142" s="5" t="n"/>
-      <c r="P142" s="8" t="n"/>
-      <c r="Q142" s="9" t="n"/>
-    </row>
-    <row r="143" ht="15" customHeight="1">
-      <c r="A143" s="5" t="n"/>
-      <c r="B143" s="6" t="n"/>
-      <c r="C143" s="5" t="n"/>
-      <c r="D143" s="7" t="n"/>
-      <c r="E143" s="6" t="n"/>
-      <c r="F143" s="6" t="n"/>
-      <c r="G143" s="6" t="n"/>
-      <c r="H143" s="6" t="n"/>
-      <c r="I143" s="6" t="n"/>
-      <c r="J143" s="7" t="n"/>
-      <c r="K143" s="5" t="n"/>
-      <c r="L143" s="6" t="n"/>
-      <c r="M143" s="5" t="n"/>
-      <c r="N143" s="5" t="n"/>
-      <c r="O143" s="5" t="n"/>
-      <c r="P143" s="8" t="n"/>
-      <c r="Q143" s="9" t="n"/>
-    </row>
-    <row r="144" ht="15" customHeight="1">
-      <c r="A144" s="5" t="n"/>
-      <c r="B144" s="6" t="n"/>
-      <c r="C144" s="5" t="n"/>
-      <c r="D144" s="7" t="n"/>
-      <c r="E144" s="6" t="n"/>
-      <c r="F144" s="6" t="n"/>
-      <c r="G144" s="6" t="n"/>
-      <c r="H144" s="6" t="n"/>
-      <c r="I144" s="6" t="n"/>
-      <c r="J144" s="7" t="n"/>
-      <c r="K144" s="5" t="n"/>
-      <c r="L144" s="6" t="n"/>
-      <c r="M144" s="5" t="n"/>
-      <c r="N144" s="5" t="n"/>
-      <c r="O144" s="5" t="n"/>
-      <c r="P144" s="8" t="n"/>
-      <c r="Q144" s="9" t="n"/>
-    </row>
-    <row r="145" ht="15" customHeight="1">
-      <c r="A145" s="5" t="n"/>
-      <c r="B145" s="6" t="n"/>
-      <c r="C145" s="5" t="n"/>
-      <c r="D145" s="7" t="n"/>
-      <c r="E145" s="6" t="n"/>
-      <c r="F145" s="6" t="n"/>
-      <c r="G145" s="6" t="n"/>
-      <c r="H145" s="6" t="n"/>
-      <c r="I145" s="6" t="n"/>
-      <c r="J145" s="7" t="n"/>
-      <c r="K145" s="5" t="n"/>
-      <c r="L145" s="6" t="n"/>
-      <c r="M145" s="5" t="n"/>
-      <c r="N145" s="5" t="n"/>
-      <c r="O145" s="5" t="n"/>
-      <c r="P145" s="8" t="n"/>
-      <c r="Q145" s="9" t="n"/>
-    </row>
-    <row r="146" ht="15" customHeight="1">
-      <c r="A146" s="5" t="n"/>
-      <c r="B146" s="6" t="n"/>
-      <c r="C146" s="5" t="n"/>
-      <c r="D146" s="7" t="n"/>
-      <c r="E146" s="6" t="n"/>
-      <c r="F146" s="6" t="n"/>
-      <c r="G146" s="6" t="n"/>
-      <c r="H146" s="6" t="n"/>
-      <c r="I146" s="6" t="n"/>
-      <c r="J146" s="7" t="n"/>
-      <c r="K146" s="5" t="n"/>
-      <c r="L146" s="6" t="n"/>
-      <c r="M146" s="5" t="n"/>
-      <c r="N146" s="5" t="n"/>
-      <c r="O146" s="5" t="n"/>
-      <c r="P146" s="8" t="n"/>
-      <c r="Q146" s="9" t="n"/>
-    </row>
-    <row r="147" ht="15" customHeight="1">
-      <c r="A147" s="5" t="n"/>
-      <c r="B147" s="6" t="n"/>
-      <c r="C147" s="5" t="n"/>
-      <c r="D147" s="7" t="n"/>
-      <c r="E147" s="6" t="n"/>
-      <c r="F147" s="6" t="n"/>
-      <c r="G147" s="6" t="n"/>
-      <c r="H147" s="6" t="n"/>
-      <c r="I147" s="6" t="n"/>
-      <c r="J147" s="7" t="n"/>
-      <c r="K147" s="5" t="n"/>
-      <c r="L147" s="6" t="n"/>
-      <c r="M147" s="5" t="n"/>
-      <c r="N147" s="5" t="n"/>
-      <c r="O147" s="5" t="n"/>
-      <c r="P147" s="8" t="n"/>
-      <c r="Q147" s="9" t="n"/>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11546,23 +11546,81 @@
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="6" t="n"/>
-      <c r="C148" s="5" t="n"/>
-      <c r="D148" s="7" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="n"/>
-      <c r="H148" s="6" t="n"/>
-      <c r="I148" s="6" t="n"/>
-      <c r="J148" s="7" t="n"/>
-      <c r="K148" s="5" t="n"/>
-      <c r="L148" s="6" t="n"/>
-      <c r="M148" s="5" t="n"/>
-      <c r="N148" s="5" t="n"/>
-      <c r="O148" s="5" t="n"/>
-      <c r="P148" s="8" t="n"/>
-      <c r="Q148" s="9" t="n"/>
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr"/>
+      <c r="K148" s="12" t="inlineStr">
+        <is>
+          <t>149_Greece_2002_2Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L148" s="13" t="inlineStr"/>
+      <c r="M148" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N148" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O148" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P148" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q148" s="16" t="inlineStr">
+        <is>
+          <t>Тест Тест Тест</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11618,7 +11618,7 @@
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Тест Тест Тест</t>
+          <t>Vercel Edit Test</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11546,81 +11546,23 @@
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="12" t="inlineStr">
-        <is>
-          <t>149</t>
-        </is>
-      </c>
-      <c r="B148" s="13" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="C148" s="12" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D148" s="14" t="n">
-        <v>2002</v>
-      </c>
-      <c r="E148" s="13" t="inlineStr">
-        <is>
-          <t>2 €</t>
-        </is>
-      </c>
-      <c r="F148" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G148" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
-      <c r="H148" s="13" t="inlineStr">
-        <is>
-          <t>VF</t>
-        </is>
-      </c>
-      <c r="I148" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J148" s="14" t="inlineStr"/>
-      <c r="K148" s="12" t="inlineStr">
-        <is>
-          <t>149_Greece_2002_2Euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L148" s="13" t="inlineStr"/>
-      <c r="M148" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N148" s="12" t="inlineStr">
-        <is>
-          <t>8.50 g</t>
-        </is>
-      </c>
-      <c r="O148" s="12" t="inlineStr">
-        <is>
-          <t>25.75 mm</t>
-        </is>
-      </c>
-      <c r="P148" s="15" t="inlineStr">
-        <is>
-          <t>Regular 2 € circulation coin of Greece.</t>
-        </is>
-      </c>
-      <c r="Q148" s="16" t="inlineStr">
-        <is>
-          <t>Vercel Edit Test</t>
-        </is>
-      </c>
+      <c r="A148" s="5" t="n"/>
+      <c r="B148" s="6" t="n"/>
+      <c r="C148" s="5" t="n"/>
+      <c r="D148" s="7" t="n"/>
+      <c r="E148" s="6" t="n"/>
+      <c r="F148" s="6" t="n"/>
+      <c r="G148" s="6" t="n"/>
+      <c r="H148" s="6" t="n"/>
+      <c r="I148" s="6" t="n"/>
+      <c r="J148" s="7" t="n"/>
+      <c r="K148" s="5" t="n"/>
+      <c r="L148" s="6" t="n"/>
+      <c r="M148" s="5" t="n"/>
+      <c r="N148" s="5" t="n"/>
+      <c r="O148" s="5" t="n"/>
+      <c r="P148" s="8" t="n"/>
+      <c r="Q148" s="9" t="n"/>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11546,23 +11546,81 @@
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
-      <c r="A148" s="5" t="n"/>
-      <c r="B148" s="6" t="n"/>
-      <c r="C148" s="5" t="n"/>
-      <c r="D148" s="7" t="n"/>
-      <c r="E148" s="6" t="n"/>
-      <c r="F148" s="6" t="n"/>
-      <c r="G148" s="6" t="n"/>
-      <c r="H148" s="6" t="n"/>
-      <c r="I148" s="6" t="n"/>
-      <c r="J148" s="7" t="n"/>
-      <c r="K148" s="5" t="n"/>
-      <c r="L148" s="6" t="n"/>
-      <c r="M148" s="5" t="n"/>
-      <c r="N148" s="5" t="n"/>
-      <c r="O148" s="5" t="n"/>
-      <c r="P148" s="8" t="n"/>
-      <c r="Q148" s="9" t="n"/>
+      <c r="A148" s="12" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B148" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C148" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>2002</v>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F148" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
+      <c r="H148" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I148" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr"/>
+      <c r="K148" s="12" t="inlineStr">
+        <is>
+          <t>149_Greece_2002_2Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L148" s="13" t="inlineStr"/>
+      <c r="M148" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N148" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O148" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P148" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q148" s="16" t="inlineStr">
+        <is>
+          <t>Auto TEST</t>
+        </is>
+      </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11623,23 +11623,81 @@
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="7" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="7" t="n"/>
-      <c r="K149" s="5" t="n"/>
-      <c r="L149" s="6" t="n"/>
-      <c r="M149" s="5" t="n"/>
-      <c r="N149" s="5" t="n"/>
-      <c r="O149" s="5" t="n"/>
-      <c r="P149" s="8" t="n"/>
-      <c r="Q149" s="9" t="n"/>
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr"/>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>150_Greece_2030_2Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L149" s="13" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N149" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O149" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P149" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q149" s="16" t="inlineStr">
+        <is>
+          <t>2ND TEST</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11623,81 +11623,23 @@
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="12" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="B149" s="13" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="C149" s="12" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D149" s="14" t="n">
-        <v>2030</v>
-      </c>
-      <c r="E149" s="13" t="inlineStr">
-        <is>
-          <t>2 €</t>
-        </is>
-      </c>
-      <c r="F149" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J149" s="14" t="inlineStr"/>
-      <c r="K149" s="12" t="inlineStr">
-        <is>
-          <t>150_Greece_2030_2Euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L149" s="13" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N149" s="12" t="inlineStr">
-        <is>
-          <t>8.50 g</t>
-        </is>
-      </c>
-      <c r="O149" s="12" t="inlineStr">
-        <is>
-          <t>25.75 mm</t>
-        </is>
-      </c>
-      <c r="P149" s="15" t="inlineStr">
-        <is>
-          <t>Regular 2 € circulation coin of Greece.</t>
-        </is>
-      </c>
-      <c r="Q149" s="16" t="inlineStr">
-        <is>
-          <t>2ND TEST</t>
-        </is>
-      </c>
+      <c r="A149" s="5" t="n"/>
+      <c r="B149" s="6" t="n"/>
+      <c r="C149" s="5" t="n"/>
+      <c r="D149" s="7" t="n"/>
+      <c r="E149" s="6" t="n"/>
+      <c r="F149" s="6" t="n"/>
+      <c r="G149" s="6" t="n"/>
+      <c r="H149" s="6" t="n"/>
+      <c r="I149" s="6" t="n"/>
+      <c r="J149" s="7" t="n"/>
+      <c r="K149" s="5" t="n"/>
+      <c r="L149" s="6" t="n"/>
+      <c r="M149" s="5" t="n"/>
+      <c r="N149" s="5" t="n"/>
+      <c r="O149" s="5" t="n"/>
+      <c r="P149" s="8" t="n"/>
+      <c r="Q149" s="9" t="n"/>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11623,23 +11623,77 @@
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="5" t="n"/>
-      <c r="B149" s="6" t="n"/>
-      <c r="C149" s="5" t="n"/>
-      <c r="D149" s="7" t="n"/>
-      <c r="E149" s="6" t="n"/>
-      <c r="F149" s="6" t="n"/>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
-      <c r="I149" s="6" t="n"/>
-      <c r="J149" s="7" t="n"/>
-      <c r="K149" s="5" t="n"/>
-      <c r="L149" s="6" t="n"/>
-      <c r="M149" s="5" t="n"/>
-      <c r="N149" s="5" t="n"/>
-      <c r="O149" s="5" t="n"/>
-      <c r="P149" s="8" t="n"/>
-      <c r="Q149" s="9" t="n"/>
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr"/>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>150_Greece_2030_2Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L149" s="13" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N149" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O149" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P149" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q149" s="16" t="inlineStr"/>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11618,7 +11618,7 @@
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Auto TEST</t>
+          <t>Тест на двойное изменение</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11638,8 +11638,10 @@
           <t>GR</t>
         </is>
       </c>
-      <c r="D149" s="14" t="n">
-        <v>2030</v>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
@@ -11651,11 +11653,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G149" s="13" t="inlineStr"/>
       <c r="H149" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -11693,7 +11691,11 @@
           <t>Regular 2 € circulation coin of Greece.</t>
         </is>
       </c>
-      <c r="Q149" s="16" t="inlineStr"/>
+      <c r="Q149" s="16" t="inlineStr">
+        <is>
+          <t>Тест изменений</t>
+        </is>
+      </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11698,23 +11698,81 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="5" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
-      <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
-      <c r="P150" s="8" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>Тест 62</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11618,7 +11618,8 @@
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Тест на двойное изменение</t>
+          <t>Тест 62 
+ двойное изменение</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11626,7 +11626,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -11639,10 +11639,8 @@
           <t>GR</t>
         </is>
       </c>
-      <c r="D149" s="14" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+      <c r="D149" s="14" t="n">
+        <v>2035</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
@@ -11654,7 +11652,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G149" s="13" t="inlineStr"/>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>2 Euro</t>
+        </is>
+      </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -11668,7 +11670,7 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>150_Greece_2030_2Euro_Regular.jpeg</t>
+          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
@@ -11694,86 +11696,28 @@
       </c>
       <c r="Q149" s="16" t="inlineStr">
         <is>
-          <t>Тест изменений</t>
+          <t>Тест 62</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>151</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D150" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="E150" s="13" t="inlineStr">
-        <is>
-          <t>2 €</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G150" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J150" s="14" t="inlineStr"/>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L150" s="13" t="inlineStr"/>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N150" s="12" t="inlineStr">
-        <is>
-          <t>8.50 g</t>
-        </is>
-      </c>
-      <c r="O150" s="12" t="inlineStr">
-        <is>
-          <t>25.75 mm</t>
-        </is>
-      </c>
-      <c r="P150" s="15" t="inlineStr">
-        <is>
-          <t>Regular 2 € circulation coin of Greece.</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>Тест 62</t>
-        </is>
-      </c>
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="F150" s="6" t="n"/>
+      <c r="G150" s="6" t="n"/>
+      <c r="H150" s="6" t="n"/>
+      <c r="I150" s="6" t="n"/>
+      <c r="J150" s="7" t="n"/>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="6" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="9" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11701,23 +11701,79 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="5" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
-      <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
-      <c r="P150" s="8" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>152_Greece_2026_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>Test 62 ADD</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11701,79 +11701,23 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="E150" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G150" s="13" t="inlineStr"/>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J150" s="14" t="inlineStr"/>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>152_Greece_2026_1cent_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L150" s="13" t="inlineStr"/>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>Copper-plated steel</t>
-        </is>
-      </c>
-      <c r="N150" s="12" t="inlineStr">
-        <is>
-          <t>2.30 g</t>
-        </is>
-      </c>
-      <c r="O150" s="12" t="inlineStr">
-        <is>
-          <t>16.25 mm</t>
-        </is>
-      </c>
-      <c r="P150" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 cent circulation coin of Greece.</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>Test 62 ADD</t>
-        </is>
-      </c>
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="F150" s="6" t="n"/>
+      <c r="G150" s="6" t="n"/>
+      <c r="H150" s="6" t="n"/>
+      <c r="I150" s="6" t="n"/>
+      <c r="J150" s="7" t="n"/>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="6" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="9" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11701,23 +11701,79 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="5" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
-      <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
-      <c r="P150" s="8" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2035</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>152_Greece_2035_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>аыауцацау</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11701,79 +11701,23 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>152</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>Greece</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>2035</t>
-        </is>
-      </c>
-      <c r="E150" s="13" t="inlineStr">
-        <is>
-          <t>5 cent</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G150" s="13" t="inlineStr"/>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J150" s="14" t="inlineStr"/>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>152_Greece_2035_5cent_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L150" s="13" t="inlineStr"/>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>Copper-plated steel</t>
-        </is>
-      </c>
-      <c r="N150" s="12" t="inlineStr">
-        <is>
-          <t>3.92 g</t>
-        </is>
-      </c>
-      <c r="O150" s="12" t="inlineStr">
-        <is>
-          <t>21.25 mm</t>
-        </is>
-      </c>
-      <c r="P150" s="15" t="inlineStr">
-        <is>
-          <t>Regular 5 cent circulation coin of Greece.</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>аыауцацау</t>
-        </is>
-      </c>
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="F150" s="6" t="n"/>
+      <c r="G150" s="6" t="n"/>
+      <c r="H150" s="6" t="n"/>
+      <c r="I150" s="6" t="n"/>
+      <c r="J150" s="7" t="n"/>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="6" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="9" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11701,23 +11701,79 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="5" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
-      <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
-      <c r="P150" s="8" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>152_Andorra_2030_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Andorra.</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>dvjdvjdsjlvjvv</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11776,23 +11776,81 @@
       </c>
     </row>
     <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="7" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="6" t="n"/>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="7" t="n"/>
-      <c r="K151" s="5" t="n"/>
-      <c r="L151" s="6" t="n"/>
-      <c r="M151" s="5" t="n"/>
-      <c r="N151" s="5" t="n"/>
-      <c r="O151" s="5" t="n"/>
-      <c r="P151" s="8" t="n"/>
-      <c r="Q151" s="9" t="n"/>
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>Andorra</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G151" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t>UNC</t>
+        </is>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr"/>
+      <c r="K151" s="12" t="inlineStr">
+        <is>
+          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L151" s="13" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N151" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O151" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P151" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Andorra.</t>
+        </is>
+      </c>
+      <c r="Q151" s="16" t="inlineStr">
+        <is>
+          <t>FINAL LOCAL CRUD TEST</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11548,7 +11548,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>151</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -11562,7 +11562,7 @@
         </is>
       </c>
       <c r="D148" s="14" t="n">
-        <v>2002</v>
+        <v>2035</v>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
@@ -11592,7 +11592,7 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>149_Greece_2002_2Euro_Regular.jpeg</t>
+          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>
@@ -11618,33 +11618,34 @@
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Тест 62 
- двойное изменение</t>
+          <t>Тест 62</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D149" s="14" t="n">
-        <v>2035</v>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>2 €</t>
+          <t>50 cent</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -11652,11 +11653,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G149" s="13" t="inlineStr"/>
       <c r="H149" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -11670,40 +11667,40 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
+          <t>152_Andorra_2030_50cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>Bimetallic</t>
+          <t>Nordic gold</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
         <is>
-          <t>8.50 g</t>
+          <t>7.80 g</t>
         </is>
       </c>
       <c r="O149" s="12" t="inlineStr">
         <is>
-          <t>25.75 mm</t>
+          <t>24.25 mm</t>
         </is>
       </c>
       <c r="P149" s="15" t="inlineStr">
         <is>
-          <t>Regular 2 € circulation coin of Greece.</t>
+          <t>Regular 50 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q149" s="16" t="inlineStr">
         <is>
-          <t>Тест 62</t>
+          <t>dvjdvjdsjlvjvv</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -11716,14 +11713,12 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+      <c r="D150" s="14" t="n">
+        <v>2035</v>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>50 cent</t>
+          <t>10 cent</t>
         </is>
       </c>
       <c r="F150" s="13" t="inlineStr">
@@ -11731,10 +11726,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G150" s="13" t="inlineStr"/>
+      <c r="G150" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="I150" s="13" t="inlineStr">
@@ -11745,7 +11744,7 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>152_Andorra_2030_50cent_Regular.jpeg</t>
+          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr"/>
@@ -11756,101 +11755,43 @@
       </c>
       <c r="N150" s="12" t="inlineStr">
         <is>
-          <t>7.80 g</t>
+          <t>4.10 g</t>
         </is>
       </c>
       <c r="O150" s="12" t="inlineStr">
         <is>
-          <t>24.25 mm</t>
+          <t>19.75 mm</t>
         </is>
       </c>
       <c r="P150" s="15" t="inlineStr">
         <is>
-          <t>Regular 50 cent circulation coin of Andorra.</t>
+          <t>Regular 10 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q150" s="16" t="inlineStr">
         <is>
-          <t>dvjdvjdsjlvjvv</t>
+          <t>FINAL LOCAL CRUD TEST</t>
         </is>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="12" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
-      <c r="B151" s="13" t="inlineStr">
-        <is>
-          <t>Andorra</t>
-        </is>
-      </c>
-      <c r="C151" s="12" t="inlineStr">
-        <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="D151" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="E151" s="13" t="inlineStr">
-        <is>
-          <t>10 cent</t>
-        </is>
-      </c>
-      <c r="F151" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G151" s="13" t="inlineStr">
-        <is>
-          <t>10 cent</t>
-        </is>
-      </c>
-      <c r="H151" s="13" t="inlineStr">
-        <is>
-          <t>UNC</t>
-        </is>
-      </c>
-      <c r="I151" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J151" s="14" t="inlineStr"/>
-      <c r="K151" s="12" t="inlineStr">
-        <is>
-          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L151" s="13" t="inlineStr"/>
-      <c r="M151" s="12" t="inlineStr">
-        <is>
-          <t>Nordic gold</t>
-        </is>
-      </c>
-      <c r="N151" s="12" t="inlineStr">
-        <is>
-          <t>4.10 g</t>
-        </is>
-      </c>
-      <c r="O151" s="12" t="inlineStr">
-        <is>
-          <t>19.75 mm</t>
-        </is>
-      </c>
-      <c r="P151" s="15" t="inlineStr">
-        <is>
-          <t>Regular 10 cent circulation coin of Andorra.</t>
-        </is>
-      </c>
-      <c r="Q151" s="16" t="inlineStr">
-        <is>
-          <t>FINAL LOCAL CRUD TEST</t>
-        </is>
-      </c>
+      <c r="A151" s="5" t="n"/>
+      <c r="B151" s="6" t="n"/>
+      <c r="C151" s="5" t="n"/>
+      <c r="D151" s="7" t="n"/>
+      <c r="E151" s="6" t="n"/>
+      <c r="F151" s="6" t="n"/>
+      <c r="G151" s="6" t="n"/>
+      <c r="H151" s="6" t="n"/>
+      <c r="I151" s="6" t="n"/>
+      <c r="J151" s="7" t="n"/>
+      <c r="K151" s="5" t="n"/>
+      <c r="L151" s="6" t="n"/>
+      <c r="M151" s="5" t="n"/>
+      <c r="N151" s="5" t="n"/>
+      <c r="O151" s="5" t="n"/>
+      <c r="P151" s="8" t="n"/>
+      <c r="Q151" s="9" t="n"/>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11548,25 +11548,27 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>151</t>
+          <t>152</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>GR</t>
-        </is>
-      </c>
-      <c r="D148" s="14" t="n">
-        <v>2035</v>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>2 €</t>
+          <t>2 cent</t>
         </is>
       </c>
       <c r="F148" s="13" t="inlineStr">
@@ -11574,11 +11576,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G148" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G148" s="13" t="inlineStr"/>
       <c r="H148" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -11592,40 +11590,40 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>151_Greece_2035_2Euro_Regular.jpeg</t>
+          <t>152_Andorra_2029_2cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>
       <c r="M148" s="12" t="inlineStr">
         <is>
-          <t>Bimetallic</t>
+          <t>Copper-plated steel</t>
         </is>
       </c>
       <c r="N148" s="12" t="inlineStr">
         <is>
-          <t>8.50 g</t>
+          <t>3.06 g</t>
         </is>
       </c>
       <c r="O148" s="12" t="inlineStr">
         <is>
-          <t>25.75 mm</t>
+          <t>18.75 mm</t>
         </is>
       </c>
       <c r="P148" s="15" t="inlineStr">
         <is>
-          <t>Regular 2 € circulation coin of Greece.</t>
+          <t>Regular 2 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Тест 62</t>
+          <t>FINAL LOCAL CRUD TEST</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>153</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -11638,14 +11636,12 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="D149" s="14" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
+      <c r="D149" s="14" t="n">
+        <v>2035</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>50 cent</t>
+          <t>10 cent</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -11653,10 +11649,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G149" s="13" t="inlineStr"/>
+      <c r="G149" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -11667,7 +11667,7 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>152_Andorra_2030_50cent_Regular.jpeg</t>
+          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
@@ -11678,29 +11678,29 @@
       </c>
       <c r="N149" s="12" t="inlineStr">
         <is>
-          <t>7.80 g</t>
+          <t>4.10 g</t>
         </is>
       </c>
       <c r="O149" s="12" t="inlineStr">
         <is>
-          <t>24.25 mm</t>
+          <t>19.75 mm</t>
         </is>
       </c>
       <c r="P149" s="15" t="inlineStr">
         <is>
-          <t>Regular 50 cent circulation coin of Andorra.</t>
+          <t>Regular 10 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q149" s="16" t="inlineStr">
         <is>
-          <t>dvjdvjdsjlvjvv</t>
+          <t>FINAL LOCAL CRUD TEST</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
@@ -11713,12 +11713,14 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="D150" s="14" t="n">
-        <v>2035</v>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
-          <t>10 cent</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="F150" s="13" t="inlineStr">
@@ -11726,11 +11728,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G150" s="13" t="inlineStr">
-        <is>
-          <t>10 cent</t>
-        </is>
-      </c>
+      <c r="G150" s="13" t="inlineStr"/>
       <c r="H150" s="13" t="inlineStr">
         <is>
           <t>UNC</t>
@@ -11744,28 +11742,28 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
+          <t>154_Andorra_2028_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr"/>
       <c r="M150" s="12" t="inlineStr">
         <is>
-          <t>Nordic gold</t>
+          <t>Copper-plated steel</t>
         </is>
       </c>
       <c r="N150" s="12" t="inlineStr">
         <is>
-          <t>4.10 g</t>
+          <t>2.30 g</t>
         </is>
       </c>
       <c r="O150" s="12" t="inlineStr">
         <is>
-          <t>19.75 mm</t>
+          <t>16.25 mm</t>
         </is>
       </c>
       <c r="P150" s="15" t="inlineStr">
         <is>
-          <t>Regular 10 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q150" s="16" t="inlineStr">

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -5255,8 +5255,10 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="D63" s="14" t="n">
-        <v>2012</v>
+      <c r="D63" s="14" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
       </c>
       <c r="E63" s="13" t="inlineStr">
         <is>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11715,10 +11715,8 @@
           <t>AD</t>
         </is>
       </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
+      <c r="D150" s="14" t="n">
+        <v>2028</v>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
@@ -11730,7 +11728,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G150" s="13" t="inlineStr"/>
+      <c r="G150" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
           <t>UNC</t>
@@ -11770,7 +11772,7 @@
       </c>
       <c r="Q150" s="16" t="inlineStr">
         <is>
-          <t>FINAL LOCAL CRUD TEST</t>
+          <t>image TEST</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11565,7 +11565,7 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>2029</t>
+          <t>2031</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
@@ -11592,7 +11592,7 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>152_Andorra_2029_2cent_Regular.jpeg</t>
+          <t>152_Andorra_2031_2cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11716,7 +11716,7 @@
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I150" s="13" t="inlineStr">
@@ -11746,7 +11746,7 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>154_Andorra_2028_1cent_Regular.jpeg</t>
+          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11625,7 +11625,7 @@
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>153</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
@@ -11639,11 +11639,11 @@
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>2035</v>
+        <v>2029</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>10 cent</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -11653,12 +11653,12 @@
       </c>
       <c r="G149" s="13" t="inlineStr">
         <is>
-          <t>10 cent</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>G</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -11669,54 +11669,54 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>153_Andorra_2035_10cent_Regular.jpeg</t>
+          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>Nordic gold</t>
+          <t>Copper-plated steel</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
         <is>
-          <t>4.10 g</t>
+          <t>2.30 g</t>
         </is>
       </c>
       <c r="O149" s="12" t="inlineStr">
         <is>
-          <t>19.75 mm</t>
+          <t>16.25 mm</t>
         </is>
       </c>
       <c r="P149" s="15" t="inlineStr">
         <is>
-          <t>Regular 10 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q149" s="16" t="inlineStr">
         <is>
-          <t>FINAL LOCAL CRUD TEST</t>
+          <t>image TEST</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="D150" s="14" t="n">
-        <v>2029</v>
+        <v>2035</v>
       </c>
       <c r="E150" s="13" t="inlineStr">
         <is>
@@ -11735,7 +11735,7 @@
       </c>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I150" s="13" t="inlineStr">
@@ -11746,7 +11746,7 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
+          <t>155_Vatican-City_2035_1cent_Regular.png</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr"/>
@@ -11767,12 +11767,12 @@
       </c>
       <c r="P150" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
         </is>
       </c>
       <c r="Q150" s="16" t="inlineStr">
         <is>
-          <t>image TEST</t>
+          <t>Test test</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11550,7 +11550,7 @@
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>152</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
@@ -11565,12 +11565,12 @@
       </c>
       <c r="D148" s="14" t="inlineStr">
         <is>
-          <t>2031</t>
+          <t>2029</t>
         </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>2 cent</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="F148" s="13" t="inlineStr">
@@ -11581,7 +11581,7 @@
       <c r="G148" s="13" t="inlineStr"/>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="I148" s="13" t="inlineStr">
@@ -11592,7 +11592,7 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>152_Andorra_2031_2cent_Regular.jpeg</t>
+          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>
@@ -11603,43 +11603,43 @@
       </c>
       <c r="N148" s="12" t="inlineStr">
         <is>
-          <t>3.06 g</t>
+          <t>2.30 g</t>
         </is>
       </c>
       <c r="O148" s="12" t="inlineStr">
         <is>
-          <t>18.75 mm</t>
+          <t>16.25 mm</t>
         </is>
       </c>
       <c r="P148" s="15" t="inlineStr">
         <is>
-          <t>Regular 2 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>FINAL LOCAL CRUD TEST</t>
+          <t>Test TEST</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>VA</t>
         </is>
       </c>
       <c r="D149" s="14" t="n">
-        <v>2029</v>
+        <v>2035</v>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>G</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -11669,7 +11669,7 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
+          <t>155_Vatican-City_2035_1cent_Regular.png</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
@@ -11690,91 +11690,33 @@
       </c>
       <c r="P149" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
         </is>
       </c>
       <c r="Q149" s="16" t="inlineStr">
         <is>
-          <t>image TEST</t>
+          <t>Test test</t>
         </is>
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>155</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>Vatican City</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D150" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="E150" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G150" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J150" s="14" t="inlineStr"/>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>155_Vatican-City_2035_1cent_Regular.png</t>
-        </is>
-      </c>
-      <c r="L150" s="13" t="inlineStr"/>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>Copper-plated steel</t>
-        </is>
-      </c>
-      <c r="N150" s="12" t="inlineStr">
-        <is>
-          <t>2.30 g</t>
-        </is>
-      </c>
-      <c r="O150" s="12" t="inlineStr">
-        <is>
-          <t>16.25 mm</t>
-        </is>
-      </c>
-      <c r="P150" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 cent circulation coin of Vatican City.</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
-        <is>
-          <t>Test test</t>
-        </is>
-      </c>
+      <c r="A150" s="5" t="n"/>
+      <c r="B150" s="6" t="n"/>
+      <c r="C150" s="5" t="n"/>
+      <c r="D150" s="7" t="n"/>
+      <c r="E150" s="6" t="n"/>
+      <c r="F150" s="6" t="n"/>
+      <c r="G150" s="6" t="n"/>
+      <c r="H150" s="6" t="n"/>
+      <c r="I150" s="6" t="n"/>
+      <c r="J150" s="7" t="n"/>
+      <c r="K150" s="5" t="n"/>
+      <c r="L150" s="6" t="n"/>
+      <c r="M150" s="5" t="n"/>
+      <c r="N150" s="5" t="n"/>
+      <c r="O150" s="5" t="n"/>
+      <c r="P150" s="8" t="n"/>
+      <c r="Q150" s="9" t="n"/>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11700,42 +11700,156 @@
       </c>
     </row>
     <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="5" t="n"/>
-      <c r="B150" s="6" t="n"/>
-      <c r="C150" s="5" t="n"/>
-      <c r="D150" s="7" t="n"/>
-      <c r="E150" s="6" t="n"/>
-      <c r="F150" s="6" t="n"/>
-      <c r="G150" s="6" t="n"/>
-      <c r="H150" s="6" t="n"/>
-      <c r="I150" s="6" t="n"/>
-      <c r="J150" s="7" t="n"/>
-      <c r="K150" s="5" t="n"/>
-      <c r="L150" s="6" t="n"/>
-      <c r="M150" s="5" t="n"/>
-      <c r="N150" s="5" t="n"/>
-      <c r="O150" s="5" t="n"/>
-      <c r="P150" s="8" t="n"/>
-      <c r="Q150" s="9" t="n"/>
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>156_France_2000_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>The design chosen for the first series of €1 and €2 coins was the work of the artist Joaquin Jimenez. It features a tree symbolising life, continuity and growth, standing within a hexagon and encircled by the motto of the French Republic, "Liberté, Egalité, Fraternité" (Liberty, equality, fraternity).</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+On the €1 and €2 coins, a tree symbolising life, growth and stability is framed by a hexagon – France – and surrounded by the motto of the French Republic: ‘Liberté, Égalité, Fraternité’ (Freedom, Equality, Fraternity). The edge lettering on the €2 coin is ‘2**’ repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="151" ht="15" customHeight="1">
-      <c r="A151" s="5" t="n"/>
-      <c r="B151" s="6" t="n"/>
-      <c r="C151" s="5" t="n"/>
-      <c r="D151" s="7" t="n"/>
-      <c r="E151" s="6" t="n"/>
-      <c r="F151" s="6" t="n"/>
-      <c r="G151" s="6" t="n"/>
-      <c r="H151" s="6" t="n"/>
-      <c r="I151" s="6" t="n"/>
-      <c r="J151" s="7" t="n"/>
-      <c r="K151" s="5" t="n"/>
-      <c r="L151" s="6" t="n"/>
-      <c r="M151" s="5" t="n"/>
-      <c r="N151" s="5" t="n"/>
-      <c r="O151" s="5" t="n"/>
-      <c r="P151" s="8" t="n"/>
-      <c r="Q151" s="9" t="n"/>
+      <c r="A151" s="12" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B151" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C151" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D151" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E151" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F151" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G151" s="13" t="inlineStr"/>
+      <c r="H151" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I151" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr"/>
+      <c r="K151" s="12" t="inlineStr">
+        <is>
+          <t>157_Ireland_2000_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L151" s="13" t="inlineStr"/>
+      <c r="M151" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N151" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O151" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P151" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q151" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11852,80 +11852,305 @@
       </c>
     </row>
     <row r="152" ht="15" customHeight="1">
-      <c r="A152" s="5" t="n"/>
-      <c r="B152" s="6" t="n"/>
-      <c r="C152" s="5" t="n"/>
-      <c r="D152" s="7" t="n"/>
-      <c r="E152" s="6" t="n"/>
-      <c r="F152" s="6" t="n"/>
-      <c r="G152" s="6" t="n"/>
-      <c r="H152" s="6" t="n"/>
-      <c r="I152" s="6" t="n"/>
-      <c r="J152" s="7" t="n"/>
-      <c r="K152" s="5" t="n"/>
-      <c r="L152" s="6" t="n"/>
-      <c r="M152" s="5" t="n"/>
-      <c r="N152" s="5" t="n"/>
-      <c r="O152" s="5" t="n"/>
-      <c r="P152" s="8" t="n"/>
-      <c r="Q152" s="9" t="n"/>
+      <c r="A152" s="12" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B152" s="13" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="C152" s="12" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="D152" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E152" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F152" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G152" s="13" t="inlineStr"/>
+      <c r="H152" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I152" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="inlineStr"/>
+      <c r="K152" s="12" t="inlineStr">
+        <is>
+          <t>158_Latvia_2011_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L152" s="13" t="inlineStr"/>
+      <c r="M152" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N152" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O152" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P152" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Latvia.</t>
+        </is>
+      </c>
+      <c r="Q152" s="16" t="inlineStr">
+        <is>
+          <t>The €1 coin features a Latvian folk maiden. This image was originally used on the silver 5 lats coin in 1929. The designer is Guntars Sietiņš.</t>
+        </is>
+      </c>
     </row>
     <row r="153" ht="15" customHeight="1">
-      <c r="A153" s="5" t="n"/>
-      <c r="B153" s="6" t="n"/>
-      <c r="C153" s="5" t="n"/>
-      <c r="D153" s="7" t="n"/>
-      <c r="E153" s="6" t="n"/>
-      <c r="F153" s="6" t="n"/>
-      <c r="G153" s="6" t="n"/>
-      <c r="H153" s="6" t="n"/>
-      <c r="I153" s="6" t="n"/>
-      <c r="J153" s="7" t="n"/>
-      <c r="K153" s="5" t="n"/>
-      <c r="L153" s="6" t="n"/>
-      <c r="M153" s="5" t="n"/>
-      <c r="N153" s="5" t="n"/>
-      <c r="O153" s="5" t="n"/>
-      <c r="P153" s="8" t="n"/>
-      <c r="Q153" s="9" t="n"/>
+      <c r="A153" s="12" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B153" s="13" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C153" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D153" s="14" t="inlineStr">
+        <is>
+          <t>2019</t>
+        </is>
+      </c>
+      <c r="E153" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F153" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G153" s="13" t="inlineStr"/>
+      <c r="H153" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I153" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="inlineStr"/>
+      <c r="K153" s="12" t="inlineStr">
+        <is>
+          <t>159_Malta_2019_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L153" s="13" t="inlineStr"/>
+      <c r="M153" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N153" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O153" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P153" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Malta.</t>
+        </is>
+      </c>
+      <c r="Q153" s="16" t="inlineStr">
+        <is>
+          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+        </is>
+      </c>
     </row>
     <row r="154" ht="15" customHeight="1">
-      <c r="A154" s="5" t="n"/>
-      <c r="B154" s="6" t="n"/>
-      <c r="C154" s="5" t="n"/>
-      <c r="D154" s="7" t="n"/>
-      <c r="E154" s="6" t="n"/>
-      <c r="F154" s="6" t="n"/>
-      <c r="G154" s="6" t="n"/>
-      <c r="H154" s="6" t="n"/>
-      <c r="I154" s="6" t="n"/>
-      <c r="J154" s="7" t="n"/>
-      <c r="K154" s="5" t="n"/>
-      <c r="L154" s="6" t="n"/>
-      <c r="M154" s="5" t="n"/>
-      <c r="N154" s="5" t="n"/>
-      <c r="O154" s="5" t="n"/>
-      <c r="P154" s="8" t="n"/>
-      <c r="Q154" s="9" t="n"/>
+      <c r="A154" s="12" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B154" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C154" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D154" s="14" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E154" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F154" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G154" s="13" t="inlineStr"/>
+      <c r="H154" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I154" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="inlineStr"/>
+      <c r="K154" s="12" t="inlineStr">
+        <is>
+          <t>160_Slovenia_2007_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L154" s="13" t="inlineStr"/>
+      <c r="M154" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N154" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O154" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P154" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q154" s="16" t="inlineStr">
+        <is>
+          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+        </is>
+      </c>
     </row>
     <row r="155" ht="15" customHeight="1">
-      <c r="A155" s="5" t="n"/>
-      <c r="B155" s="6" t="n"/>
-      <c r="C155" s="5" t="n"/>
-      <c r="D155" s="7" t="n"/>
-      <c r="E155" s="6" t="n"/>
-      <c r="F155" s="6" t="n"/>
-      <c r="G155" s="6" t="n"/>
-      <c r="H155" s="6" t="n"/>
-      <c r="I155" s="6" t="n"/>
-      <c r="J155" s="7" t="n"/>
-      <c r="K155" s="5" t="n"/>
-      <c r="L155" s="6" t="n"/>
-      <c r="M155" s="5" t="n"/>
-      <c r="N155" s="5" t="n"/>
-      <c r="O155" s="5" t="n"/>
-      <c r="P155" s="8" t="n"/>
-      <c r="Q155" s="9" t="n"/>
+      <c r="A155" s="12" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B155" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C155" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D155" s="14" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E155" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F155" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G155" s="13" t="inlineStr"/>
+      <c r="H155" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I155" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="inlineStr"/>
+      <c r="K155" s="12" t="inlineStr">
+        <is>
+          <t>161_Spain_2007_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L155" s="13" t="inlineStr"/>
+      <c r="M155" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N155" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O155" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P155" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q155" s="16" t="inlineStr">
+        <is>
+          <t>Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela. There are three series of coins in circulation. All are valid.
+The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.</t>
+        </is>
+      </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11949,7 +11949,7 @@
       </c>
       <c r="E153" s="13" t="inlineStr">
         <is>
-          <t>2 €</t>
+          <t>1 €</t>
         </is>
       </c>
       <c r="F153" s="13" t="inlineStr">
@@ -11982,17 +11982,17 @@
       </c>
       <c r="N153" s="12" t="inlineStr">
         <is>
-          <t>8.50 g</t>
+          <t>7.50 g</t>
         </is>
       </c>
       <c r="O153" s="12" t="inlineStr">
         <is>
-          <t>25.75 mm</t>
+          <t>23.25 mm</t>
         </is>
       </c>
       <c r="P153" s="15" t="inlineStr">
         <is>
-          <t>Regular 2 € circulation coin of Malta.</t>
+          <t>Regular 1 € circulation coin of Malta.</t>
         </is>
       </c>
       <c r="Q153" s="16" t="inlineStr">
@@ -12072,7 +12072,8 @@
       </c>
       <c r="Q154" s="16" t="inlineStr">
         <is>
-          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+          <t>This coin bears a portrait of Primož Trubar, author of the first book printed in Slovene.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -12154,42 +12154,156 @@
       </c>
     </row>
     <row r="156" ht="15" customHeight="1">
-      <c r="A156" s="5" t="n"/>
-      <c r="B156" s="6" t="n"/>
-      <c r="C156" s="5" t="n"/>
-      <c r="D156" s="7" t="n"/>
-      <c r="E156" s="6" t="n"/>
-      <c r="F156" s="6" t="n"/>
-      <c r="G156" s="6" t="n"/>
-      <c r="H156" s="6" t="n"/>
-      <c r="I156" s="6" t="n"/>
-      <c r="J156" s="7" t="n"/>
-      <c r="K156" s="5" t="n"/>
-      <c r="L156" s="6" t="n"/>
-      <c r="M156" s="5" t="n"/>
-      <c r="N156" s="5" t="n"/>
-      <c r="O156" s="5" t="n"/>
-      <c r="P156" s="8" t="n"/>
-      <c r="Q156" s="9" t="n"/>
+      <c r="A156" s="12" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B156" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C156" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D156" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E156" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F156" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G156" s="13" t="inlineStr"/>
+      <c r="H156" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I156" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="inlineStr"/>
+      <c r="K156" s="12" t="inlineStr">
+        <is>
+          <t>162_Spain_2011_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L156" s="13" t="inlineStr"/>
+      <c r="M156" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N156" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O156" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P156" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q156" s="16" t="inlineStr">
+        <is>
+          <t>For the second series, the coins were slightly redesigned in 2010 in order to comply with the common guidelines issued by the European Commission. The year, for instance, is inscribed on the inner part of the coin.
+In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
+        </is>
+      </c>
     </row>
     <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="5" t="n"/>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="5" t="n"/>
-      <c r="D157" s="7" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
-      <c r="G157" s="6" t="n"/>
-      <c r="H157" s="6" t="n"/>
-      <c r="I157" s="6" t="n"/>
-      <c r="J157" s="7" t="n"/>
-      <c r="K157" s="5" t="n"/>
-      <c r="L157" s="6" t="n"/>
-      <c r="M157" s="5" t="n"/>
-      <c r="N157" s="5" t="n"/>
-      <c r="O157" s="5" t="n"/>
-      <c r="P157" s="8" t="n"/>
-      <c r="Q157" s="9" t="n"/>
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G157" s="13" t="inlineStr"/>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr"/>
+      <c r="K157" s="12" t="inlineStr">
+        <is>
+          <t>163_Spain_2024_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L157" s="13" t="inlineStr"/>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N157" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O157" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P157" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q157" s="16" t="inlineStr">
+        <is>
+          <t>Spain has updated the design of the Spanish national face of the 1 and 2 euro coins to be produced from 2015 in order to illustrate the change in the position of the Head of State. 1 and 2 euro coins from previous years featuring the old Spanish national face will remain valid.
+In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
+        </is>
+      </c>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11169,22 +11169,22 @@
     <row r="143" ht="15" customHeight="1">
       <c r="A143" s="12" t="inlineStr">
         <is>
-          <t>144</t>
+          <t>145</t>
         </is>
       </c>
       <c r="B143" s="13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="C143" s="12" t="inlineStr">
         <is>
-          <t>AD</t>
+          <t>DE</t>
         </is>
       </c>
       <c r="D143" s="14" t="inlineStr">
         <is>
-          <t>2030</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="E143" s="13" t="inlineStr">
@@ -11211,7 +11211,7 @@
       <c r="J143" s="14" t="inlineStr"/>
       <c r="K143" s="12" t="inlineStr">
         <is>
-          <t>144_Andorra_2030_1euro_Regular.jpeg</t>
+          <t>145_Germany_2004_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L143" s="13" t="inlineStr"/>
@@ -11232,34 +11232,35 @@
       </c>
       <c r="P143" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Andorra.</t>
+          <t>Regular 1 € circulation coin of Germany.</t>
         </is>
       </c>
       <c r="Q143" s="16" t="inlineStr">
         <is>
-          <t>TETS COIN</t>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins. 10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.
+€1 and €2 coins: the traditional symbol of German sovereignty, the eagle, surrounded by the stars of Europe, appears on these coins. This motif was designed by Heinz and Sneschana Russewa-Hoyer.</t>
         </is>
       </c>
     </row>
     <row r="144" ht="15" customHeight="1">
       <c r="A144" s="12" t="inlineStr">
         <is>
-          <t>145</t>
+          <t>146</t>
         </is>
       </c>
       <c r="B144" s="13" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
       <c r="C144" s="12" t="inlineStr">
         <is>
-          <t>DE</t>
+          <t>GR</t>
         </is>
       </c>
       <c r="D144" s="14" t="inlineStr">
         <is>
-          <t>2004</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E144" s="13" t="inlineStr">
@@ -11275,7 +11276,7 @@
       <c r="G144" s="13" t="inlineStr"/>
       <c r="H144" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>VF</t>
         </is>
       </c>
       <c r="I144" s="13" t="inlineStr">
@@ -11286,7 +11287,7 @@
       <c r="J144" s="14" t="inlineStr"/>
       <c r="K144" s="12" t="inlineStr">
         <is>
-          <t>145_Germany_2004_1euro_Regular.jpeg</t>
+          <t>146_Greece_2023_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L144" s="13" t="inlineStr"/>
@@ -11307,35 +11308,35 @@
       </c>
       <c r="P144" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Germany.</t>
+          <t>Regular 1 € circulation coin of Greece.</t>
         </is>
       </c>
       <c r="Q144" s="16" t="inlineStr">
         <is>
-          <t>German officials and experts in numismatics chose three different designs for their euro coins. 10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.
-€1 and €2 coins: the traditional symbol of German sovereignty, the eagle, surrounded by the stars of Europe, appears on these coins. This motif was designed by Heinz and Sneschana Russewa-Hoyer.</t>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+The image of the owl featured in this design was copied from an ancient Athenian 4-drachma coin (fifth century BC).</t>
         </is>
       </c>
     </row>
     <row r="145" ht="15" customHeight="1">
       <c r="A145" s="12" t="inlineStr">
         <is>
-          <t>146</t>
+          <t>147</t>
         </is>
       </c>
       <c r="B145" s="13" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Italy</t>
         </is>
       </c>
       <c r="C145" s="12" t="inlineStr">
         <is>
-          <t>GR</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D145" s="14" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E145" s="13" t="inlineStr">
@@ -11362,7 +11363,7 @@
       <c r="J145" s="14" t="inlineStr"/>
       <c r="K145" s="12" t="inlineStr">
         <is>
-          <t>146_Greece_2023_1euro_Regular.jpeg</t>
+          <t>147_Italy_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L145" s="13" t="inlineStr"/>
@@ -11383,36 +11384,34 @@
       </c>
       <c r="P145" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Greece.</t>
+          <t>Regular 1 € circulation coin of Italy.</t>
         </is>
       </c>
       <c r="Q145" s="16" t="inlineStr">
         <is>
-          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
-The image of the owl featured in this design was copied from an ancient Athenian 4-drachma coin (fifth century BC).</t>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+This coin shows the famous drawing by Leonardo da Vinci, displayed in the gallery of the Academy in Venice, illustrating the ideal proportions of the human body.</t>
         </is>
       </c>
     </row>
     <row r="146" ht="15" customHeight="1">
       <c r="A146" s="12" t="inlineStr">
         <is>
-          <t>147</t>
+          <t>148</t>
         </is>
       </c>
       <c r="B146" s="13" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Portugal</t>
         </is>
       </c>
       <c r="C146" s="12" t="inlineStr">
         <is>
-          <t>IT</t>
-        </is>
-      </c>
-      <c r="D146" s="14" t="inlineStr">
-        <is>
-          <t>2011</t>
-        </is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D146" s="14" t="n">
+        <v>2002</v>
       </c>
       <c r="E146" s="13" t="inlineStr">
         <is>
@@ -11424,10 +11423,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G146" s="13" t="inlineStr"/>
+      <c r="G146" s="13" t="inlineStr">
+        <is>
+          <t>1 Euro</t>
+        </is>
+      </c>
       <c r="H146" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I146" s="13" t="inlineStr">
@@ -11438,7 +11441,7 @@
       <c r="J146" s="14" t="inlineStr"/>
       <c r="K146" s="12" t="inlineStr">
         <is>
-          <t>147_Italy_2011_1euro_Regular.jpeg</t>
+          <t>148_Portugal_2002_1Euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L146" s="13" t="inlineStr"/>
@@ -11459,38 +11462,40 @@
       </c>
       <c r="P146" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Italy.</t>
+          <t>Regular 1 € circulation coin of Portugal.</t>
         </is>
       </c>
       <c r="Q146" s="16" t="inlineStr">
         <is>
-          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
-This coin shows the famous drawing by Leonardo da Vinci, displayed in the gallery of the Academy in Venice, illustrating the ideal proportions of the human body.</t>
+          <t>Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs: 10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
+€1 and €2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144</t>
         </is>
       </c>
     </row>
     <row r="147" ht="15" customHeight="1">
       <c r="A147" s="12" t="inlineStr">
         <is>
-          <t>148</t>
+          <t>154</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Andorra</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>PT</t>
-        </is>
-      </c>
-      <c r="D147" s="14" t="n">
-        <v>2002</v>
+          <t>AD</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="inlineStr">
+        <is>
+          <t>2029</t>
+        </is>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
-          <t>1 €</t>
+          <t>1 cent</t>
         </is>
       </c>
       <c r="F147" s="13" t="inlineStr">
@@ -11498,14 +11503,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G147" s="13" t="inlineStr">
-        <is>
-          <t>1 Euro</t>
-        </is>
-      </c>
+      <c r="G147" s="13" t="inlineStr"/>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>UNC</t>
         </is>
       </c>
       <c r="I147" s="13" t="inlineStr">
@@ -11516,57 +11517,54 @@
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>148_Portugal_2002_1Euro_Regular.jpeg</t>
+          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr"/>
       <c r="M147" s="12" t="inlineStr">
         <is>
-          <t>Bimetallic</t>
+          <t>Copper-plated steel</t>
         </is>
       </c>
       <c r="N147" s="12" t="inlineStr">
         <is>
-          <t>7.50 g</t>
+          <t>2.30 g</t>
         </is>
       </c>
       <c r="O147" s="12" t="inlineStr">
         <is>
-          <t>23.25 mm</t>
+          <t>16.25 mm</t>
         </is>
       </c>
       <c r="P147" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Portugal.</t>
+          <t>Regular 1 cent circulation coin of Andorra.</t>
         </is>
       </c>
       <c r="Q147" s="16" t="inlineStr">
         <is>
-          <t>Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs: 10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
-€1 and €2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144</t>
+          <t>Test TEST</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="D148" s="14" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="n">
+        <v>2035</v>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
@@ -11578,10 +11576,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G148" s="13" t="inlineStr"/>
+      <c r="G148" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I148" s="13" t="inlineStr">
@@ -11592,7 +11594,7 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
+          <t>155_Vatican-City_2035_1cent_Regular.png</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>
@@ -11613,37 +11615,39 @@
       </c>
       <c r="P148" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
         </is>
       </c>
       <c r="Q148" s="16" t="inlineStr">
         <is>
-          <t>Test TEST</t>
+          <t>Test test</t>
         </is>
       </c>
     </row>
     <row r="149" ht="15" customHeight="1">
       <c r="A149" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B149" s="13" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C149" s="12" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D149" s="14" t="n">
-        <v>2035</v>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="E149" s="13" t="inlineStr">
         <is>
-          <t>1 cent</t>
+          <t>1 €</t>
         </is>
       </c>
       <c r="F149" s="13" t="inlineStr">
@@ -11651,14 +11655,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G149" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
+      <c r="G149" s="13" t="inlineStr"/>
       <c r="H149" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I149" s="13" t="inlineStr">
@@ -11669,106 +11669,31 @@
       <c r="J149" s="14" t="inlineStr"/>
       <c r="K149" s="12" t="inlineStr">
         <is>
-          <t>155_Vatican-City_2035_1cent_Regular.png</t>
+          <t>156_France_2000_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L149" s="13" t="inlineStr"/>
       <c r="M149" s="12" t="inlineStr">
         <is>
-          <t>Copper-plated steel</t>
+          <t>Bimetallic</t>
         </is>
       </c>
       <c r="N149" s="12" t="inlineStr">
         <is>
-          <t>2.30 g</t>
+          <t>7.50 g</t>
         </is>
       </c>
       <c r="O149" s="12" t="inlineStr">
         <is>
-          <t>16.25 mm</t>
+          <t>23.25 mm</t>
         </is>
       </c>
       <c r="P149" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Vatican City.</t>
+          <t>The design chosen for the first series of €1 and €2 coins was the work of the artist Joaquin Jimenez. It features a tree symbolising life, continuity and growth, standing within a hexagon and encircled by the motto of the French Republic, "Liberté, Egalité, Fraternité" (Liberty, equality, fraternity).</t>
         </is>
       </c>
       <c r="Q149" s="16" t="inlineStr">
-        <is>
-          <t>Test test</t>
-        </is>
-      </c>
-    </row>
-    <row r="150" ht="15" customHeight="1">
-      <c r="A150" s="12" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B150" s="13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C150" s="12" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="D150" s="14" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E150" s="13" t="inlineStr">
-        <is>
-          <t>1 €</t>
-        </is>
-      </c>
-      <c r="F150" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G150" s="13" t="inlineStr"/>
-      <c r="H150" s="13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I150" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J150" s="14" t="inlineStr"/>
-      <c r="K150" s="12" t="inlineStr">
-        <is>
-          <t>156_France_2000_1euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L150" s="13" t="inlineStr"/>
-      <c r="M150" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N150" s="12" t="inlineStr">
-        <is>
-          <t>7.50 g</t>
-        </is>
-      </c>
-      <c r="O150" s="12" t="inlineStr">
-        <is>
-          <t>23.25 mm</t>
-        </is>
-      </c>
-      <c r="P150" s="15" t="inlineStr">
-        <is>
-          <t>The design chosen for the first series of €1 and €2 coins was the work of the artist Joaquin Jimenez. It features a tree symbolising life, continuity and growth, standing within a hexagon and encircled by the motto of the French Republic, "Liberté, Egalité, Fraternité" (Liberty, equality, fraternity).</t>
-        </is>
-      </c>
-      <c r="Q150" s="16" t="inlineStr">
         <is>
           <t>A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
 A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
@@ -11776,25 +11701,100 @@
         </is>
       </c>
     </row>
+    <row r="150" ht="15" customHeight="1">
+      <c r="A150" s="12" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B150" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C150" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D150" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E150" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F150" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G150" s="13" t="inlineStr"/>
+      <c r="H150" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I150" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr"/>
+      <c r="K150" s="12" t="inlineStr">
+        <is>
+          <t>157_Ireland_2000_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L150" s="13" t="inlineStr"/>
+      <c r="M150" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N150" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O150" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P150" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q150" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
+    </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="12" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
@@ -11810,7 +11810,7 @@
       <c r="G151" s="13" t="inlineStr"/>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I151" s="13" t="inlineStr">
@@ -11821,7 +11821,7 @@
       <c r="J151" s="14" t="inlineStr"/>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>157_Ireland_2000_1euro_Regular.jpeg</t>
+          <t>158_Latvia_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr"/>
@@ -11842,34 +11842,34 @@
       </c>
       <c r="P151" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Ireland.</t>
+          <t>Regular 1 € circulation coin of Latvia.</t>
         </is>
       </c>
       <c r="Q151" s="16" t="inlineStr">
         <is>
-          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+          <t>The €1 coin features a Latvian folk maiden. This image was originally used on the silver 5 lats coin in 1929. The designer is Guntars Sietiņš.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
@@ -11885,7 +11885,7 @@
       <c r="G152" s="13" t="inlineStr"/>
       <c r="H152" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I152" s="13" t="inlineStr">
@@ -11896,7 +11896,7 @@
       <c r="J152" s="14" t="inlineStr"/>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>158_Latvia_2011_1euro_Regular.jpeg</t>
+          <t>159_Malta_2019_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L152" s="13" t="inlineStr"/>
@@ -11917,34 +11917,34 @@
       </c>
       <c r="P152" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Latvia.</t>
+          <t>Regular 1 € circulation coin of Malta.</t>
         </is>
       </c>
       <c r="Q152" s="16" t="inlineStr">
         <is>
-          <t>The €1 coin features a Latvian folk maiden. This image was originally used on the silver 5 lats coin in 1929. The designer is Guntars Sietiņš.</t>
+          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
         </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E153" s="13" t="inlineStr">
@@ -11971,7 +11971,7 @@
       <c r="J153" s="14" t="inlineStr"/>
       <c r="K153" s="12" t="inlineStr">
         <is>
-          <t>159_Malta_2019_2euro_Regular.jpeg</t>
+          <t>160_Slovenia_2007_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L153" s="13" t="inlineStr"/>
@@ -11992,29 +11992,30 @@
       </c>
       <c r="P153" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Malta.</t>
+          <t>Regular 1 € circulation coin of Slovenia.</t>
         </is>
       </c>
       <c r="Q153" s="16" t="inlineStr">
         <is>
-          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+          <t>This coin bears a portrait of Primož Trubar, author of the first book printed in Slovene.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C154" s="12" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D154" s="14" t="inlineStr">
@@ -12046,7 +12047,7 @@
       <c r="J154" s="14" t="inlineStr"/>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>160_Slovenia_2007_1euro_Regular.jpeg</t>
+          <t>161_Spain_2007_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L154" s="13" t="inlineStr"/>
@@ -12067,20 +12068,20 @@
       </c>
       <c r="P154" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Slovenia.</t>
+          <t>Regular 1 € circulation coin of Spain.</t>
         </is>
       </c>
       <c r="Q154" s="16" t="inlineStr">
         <is>
-          <t>This coin bears a portrait of Primož Trubar, author of the first book printed in Slovene.
-The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+          <t>Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela. There are three series of coins in circulation. All are valid.
+The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -12095,7 +12096,7 @@
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
@@ -12111,7 +12112,7 @@
       <c r="G155" s="13" t="inlineStr"/>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -12122,7 +12123,7 @@
       <c r="J155" s="14" t="inlineStr"/>
       <c r="K155" s="12" t="inlineStr">
         <is>
-          <t>161_Spain_2007_1euro_Regular.jpeg</t>
+          <t>162_Spain_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L155" s="13" t="inlineStr"/>
@@ -12148,15 +12149,15 @@
       </c>
       <c r="Q155" s="16" t="inlineStr">
         <is>
-          <t>Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela. There are three series of coins in circulation. All are valid.
-The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.</t>
+          <t>For the second series, the coins were slightly redesigned in 2010 in order to comply with the common guidelines issued by the European Commission. The year, for instance, is inscribed on the inner part of the coin.
+In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
         </is>
       </c>
     </row>
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
@@ -12171,7 +12172,7 @@
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
@@ -12187,7 +12188,7 @@
       <c r="G156" s="13" t="inlineStr"/>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I156" s="13" t="inlineStr">
@@ -12198,7 +12199,7 @@
       <c r="J156" s="14" t="inlineStr"/>
       <c r="K156" s="12" t="inlineStr">
         <is>
-          <t>162_Spain_2011_1euro_Regular.jpeg</t>
+          <t>163_Spain_2024_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L156" s="13" t="inlineStr"/>
@@ -12224,7 +12225,7 @@
       </c>
       <c r="Q156" s="16" t="inlineStr">
         <is>
-          <t>For the second series, the coins were slightly redesigned in 2010 in order to comply with the common guidelines issued by the European Commission. The year, for instance, is inscribed on the inner part of the coin.
+          <t>Spain has updated the design of the Spanish national face of the 1 and 2 euro coins to be produced from 2015 in order to illustrate the change in the position of the Head of State. 1 and 2 euro coins from previous years featuring the old Spanish national face will remain valid.
 In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
         </is>
       </c>
@@ -12232,22 +12233,22 @@
     <row r="157" ht="15" customHeight="1">
       <c r="A157" s="12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B157" s="13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C157" s="12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D157" s="14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E157" s="13" t="inlineStr">
@@ -12263,7 +12264,7 @@
       <c r="G157" s="13" t="inlineStr"/>
       <c r="H157" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I157" s="13" t="inlineStr">
@@ -12274,7 +12275,7 @@
       <c r="J157" s="14" t="inlineStr"/>
       <c r="K157" s="12" t="inlineStr">
         <is>
-          <t>163_Spain_2024_1euro_Regular.jpeg</t>
+          <t>164_Netherlands_2000_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L157" s="13" t="inlineStr"/>
@@ -12295,13 +12296,13 @@
       </c>
       <c r="P157" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Spain.</t>
+          <t>Regular 1 € circulation coin of Netherlands.</t>
         </is>
       </c>
       <c r="Q157" s="16" t="inlineStr">
         <is>
-          <t>Spain has updated the design of the Spanish national face of the 1 and 2 euro coins to be produced from 2015 in order to illustrate the change in the position of the Head of State. 1 and 2 euro coins from previous years featuring the old Spanish national face will remain valid.
-In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
+          <t>The Netherlands chose two designs by Bruno Ninaber van Eyben, showing Queen Beatrix, for the first series. There are two series of coins in circulation. Both are valid.
+First series: Queen Beatrix is shown with the inscription "Beatrix Koningin der Nederlanden" (Queen of the Netherlands).</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -11475,23 +11475,21 @@
     <row r="147" ht="15" customHeight="1">
       <c r="A147" s="12" t="inlineStr">
         <is>
-          <t>154</t>
+          <t>155</t>
         </is>
       </c>
       <c r="B147" s="13" t="inlineStr">
         <is>
-          <t>Andorra</t>
+          <t>Vatican City</t>
         </is>
       </c>
       <c r="C147" s="12" t="inlineStr">
         <is>
-          <t>AD</t>
-        </is>
-      </c>
-      <c r="D147" s="14" t="inlineStr">
-        <is>
-          <t>2029</t>
-        </is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D147" s="14" t="n">
+        <v>2035</v>
       </c>
       <c r="E147" s="13" t="inlineStr">
         <is>
@@ -11503,10 +11501,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G147" s="13" t="inlineStr"/>
+      <c r="G147" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
       <c r="H147" s="13" t="inlineStr">
         <is>
-          <t>UNC</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I147" s="13" t="inlineStr">
@@ -11517,7 +11519,7 @@
       <c r="J147" s="14" t="inlineStr"/>
       <c r="K147" s="12" t="inlineStr">
         <is>
-          <t>154_Andorra_2029_1cent_Regular.jpeg</t>
+          <t>155_Vatican-City_2035_1cent_Regular.png</t>
         </is>
       </c>
       <c r="L147" s="13" t="inlineStr"/>
@@ -11538,37 +11540,39 @@
       </c>
       <c r="P147" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Andorra.</t>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
         </is>
       </c>
       <c r="Q147" s="16" t="inlineStr">
         <is>
-          <t>Test TEST</t>
+          <t>Test test</t>
         </is>
       </c>
     </row>
     <row r="148" ht="15" customHeight="1">
       <c r="A148" s="12" t="inlineStr">
         <is>
-          <t>155</t>
+          <t>156</t>
         </is>
       </c>
       <c r="B148" s="13" t="inlineStr">
         <is>
-          <t>Vatican City</t>
+          <t>France</t>
         </is>
       </c>
       <c r="C148" s="12" t="inlineStr">
         <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D148" s="14" t="n">
-        <v>2035</v>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D148" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
       </c>
       <c r="E148" s="13" t="inlineStr">
         <is>
-          <t>1 cent</t>
+          <t>1 €</t>
         </is>
       </c>
       <c r="F148" s="13" t="inlineStr">
@@ -11576,14 +11580,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G148" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
+      <c r="G148" s="13" t="inlineStr"/>
       <c r="H148" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I148" s="13" t="inlineStr">
@@ -11594,106 +11594,31 @@
       <c r="J148" s="14" t="inlineStr"/>
       <c r="K148" s="12" t="inlineStr">
         <is>
-          <t>155_Vatican-City_2035_1cent_Regular.png</t>
+          <t>156_France_2000_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L148" s="13" t="inlineStr"/>
       <c r="M148" s="12" t="inlineStr">
         <is>
-          <t>Copper-plated steel</t>
+          <t>Bimetallic</t>
         </is>
       </c>
       <c r="N148" s="12" t="inlineStr">
         <is>
-          <t>2.30 g</t>
+          <t>7.50 g</t>
         </is>
       </c>
       <c r="O148" s="12" t="inlineStr">
         <is>
-          <t>16.25 mm</t>
+          <t>23.25 mm</t>
         </is>
       </c>
       <c r="P148" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 cent circulation coin of Vatican City.</t>
+          <t>The design chosen for the first series of €1 and €2 coins was the work of the artist Joaquin Jimenez. It features a tree symbolising life, continuity and growth, standing within a hexagon and encircled by the motto of the French Republic, "Liberté, Egalité, Fraternité" (Liberty, equality, fraternity).</t>
         </is>
       </c>
       <c r="Q148" s="16" t="inlineStr">
-        <is>
-          <t>Test test</t>
-        </is>
-      </c>
-    </row>
-    <row r="149" ht="15" customHeight="1">
-      <c r="A149" s="12" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="B149" s="13" t="inlineStr">
-        <is>
-          <t>France</t>
-        </is>
-      </c>
-      <c r="C149" s="12" t="inlineStr">
-        <is>
-          <t>FR</t>
-        </is>
-      </c>
-      <c r="D149" s="14" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E149" s="13" t="inlineStr">
-        <is>
-          <t>1 €</t>
-        </is>
-      </c>
-      <c r="F149" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G149" s="13" t="inlineStr"/>
-      <c r="H149" s="13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I149" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J149" s="14" t="inlineStr"/>
-      <c r="K149" s="12" t="inlineStr">
-        <is>
-          <t>156_France_2000_1euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L149" s="13" t="inlineStr"/>
-      <c r="M149" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N149" s="12" t="inlineStr">
-        <is>
-          <t>7.50 g</t>
-        </is>
-      </c>
-      <c r="O149" s="12" t="inlineStr">
-        <is>
-          <t>23.25 mm</t>
-        </is>
-      </c>
-      <c r="P149" s="15" t="inlineStr">
-        <is>
-          <t>The design chosen for the first series of €1 and €2 coins was the work of the artist Joaquin Jimenez. It features a tree symbolising life, continuity and growth, standing within a hexagon and encircled by the motto of the French Republic, "Liberté, Egalité, Fraternité" (Liberty, equality, fraternity).</t>
-        </is>
-      </c>
-      <c r="Q149" s="16" t="inlineStr">
         <is>
           <t>A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
 A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
@@ -11701,25 +11626,100 @@
         </is>
       </c>
     </row>
+    <row r="149" ht="15" customHeight="1">
+      <c r="A149" s="12" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B149" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C149" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D149" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F149" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G149" s="13" t="inlineStr"/>
+      <c r="H149" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I149" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr"/>
+      <c r="K149" s="12" t="inlineStr">
+        <is>
+          <t>157_Ireland_2000_1euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L149" s="13" t="inlineStr"/>
+      <c r="M149" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N149" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O149" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P149" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q149" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
+    </row>
     <row r="150" ht="15" customHeight="1">
       <c r="A150" s="12" t="inlineStr">
         <is>
-          <t>157</t>
+          <t>158</t>
         </is>
       </c>
       <c r="B150" s="13" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Latvia</t>
         </is>
       </c>
       <c r="C150" s="12" t="inlineStr">
         <is>
-          <t>IE</t>
+          <t>LV</t>
         </is>
       </c>
       <c r="D150" s="14" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E150" s="13" t="inlineStr">
@@ -11735,7 +11735,7 @@
       <c r="G150" s="13" t="inlineStr"/>
       <c r="H150" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I150" s="13" t="inlineStr">
@@ -11746,7 +11746,7 @@
       <c r="J150" s="14" t="inlineStr"/>
       <c r="K150" s="12" t="inlineStr">
         <is>
-          <t>157_Ireland_2000_1euro_Regular.jpeg</t>
+          <t>158_Latvia_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L150" s="13" t="inlineStr"/>
@@ -11767,34 +11767,34 @@
       </c>
       <c r="P150" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Ireland.</t>
+          <t>Regular 1 € circulation coin of Latvia.</t>
         </is>
       </c>
       <c r="Q150" s="16" t="inlineStr">
         <is>
-          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+          <t>The €1 coin features a Latvian folk maiden. This image was originally used on the silver 5 lats coin in 1929. The designer is Guntars Sietiņš.</t>
         </is>
       </c>
     </row>
     <row r="151" ht="15" customHeight="1">
       <c r="A151" s="12" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>159</t>
         </is>
       </c>
       <c r="B151" s="13" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Malta</t>
         </is>
       </c>
       <c r="C151" s="12" t="inlineStr">
         <is>
-          <t>LV</t>
+          <t>MT</t>
         </is>
       </c>
       <c r="D151" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2019</t>
         </is>
       </c>
       <c r="E151" s="13" t="inlineStr">
@@ -11810,7 +11810,7 @@
       <c r="G151" s="13" t="inlineStr"/>
       <c r="H151" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I151" s="13" t="inlineStr">
@@ -11821,7 +11821,7 @@
       <c r="J151" s="14" t="inlineStr"/>
       <c r="K151" s="12" t="inlineStr">
         <is>
-          <t>158_Latvia_2011_1euro_Regular.jpeg</t>
+          <t>159_Malta_2019_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L151" s="13" t="inlineStr"/>
@@ -11842,34 +11842,34 @@
       </c>
       <c r="P151" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Latvia.</t>
+          <t>Regular 1 € circulation coin of Malta.</t>
         </is>
       </c>
       <c r="Q151" s="16" t="inlineStr">
         <is>
-          <t>The €1 coin features a Latvian folk maiden. This image was originally used on the silver 5 lats coin in 1929. The designer is Guntars Sietiņš.</t>
+          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
         </is>
       </c>
     </row>
     <row r="152" ht="15" customHeight="1">
       <c r="A152" s="12" t="inlineStr">
         <is>
-          <t>159</t>
+          <t>160</t>
         </is>
       </c>
       <c r="B152" s="13" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Slovenia</t>
         </is>
       </c>
       <c r="C152" s="12" t="inlineStr">
         <is>
-          <t>MT</t>
+          <t>SI</t>
         </is>
       </c>
       <c r="D152" s="14" t="inlineStr">
         <is>
-          <t>2019</t>
+          <t>2007</t>
         </is>
       </c>
       <c r="E152" s="13" t="inlineStr">
@@ -11896,7 +11896,7 @@
       <c r="J152" s="14" t="inlineStr"/>
       <c r="K152" s="12" t="inlineStr">
         <is>
-          <t>159_Malta_2019_2euro_Regular.jpeg</t>
+          <t>160_Slovenia_2007_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L152" s="13" t="inlineStr"/>
@@ -11917,29 +11917,30 @@
       </c>
       <c r="P152" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Malta.</t>
+          <t>Regular 1 € circulation coin of Slovenia.</t>
         </is>
       </c>
       <c r="Q152" s="16" t="inlineStr">
         <is>
-          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+          <t>This coin bears a portrait of Primož Trubar, author of the first book printed in Slovene.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
         </is>
       </c>
     </row>
     <row r="153" ht="15" customHeight="1">
       <c r="A153" s="12" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>161</t>
         </is>
       </c>
       <c r="B153" s="13" t="inlineStr">
         <is>
-          <t>Slovenia</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="C153" s="12" t="inlineStr">
         <is>
-          <t>SI</t>
+          <t>ES</t>
         </is>
       </c>
       <c r="D153" s="14" t="inlineStr">
@@ -11971,7 +11972,7 @@
       <c r="J153" s="14" t="inlineStr"/>
       <c r="K153" s="12" t="inlineStr">
         <is>
-          <t>160_Slovenia_2007_1euro_Regular.jpeg</t>
+          <t>161_Spain_2007_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L153" s="13" t="inlineStr"/>
@@ -11992,20 +11993,20 @@
       </c>
       <c r="P153" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Slovenia.</t>
+          <t>Regular 1 € circulation coin of Spain.</t>
         </is>
       </c>
       <c r="Q153" s="16" t="inlineStr">
         <is>
-          <t>This coin bears a portrait of Primož Trubar, author of the first book printed in Slovene.
-The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+          <t>Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela. There are three series of coins in circulation. All are valid.
+The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.</t>
         </is>
       </c>
     </row>
     <row r="154" ht="15" customHeight="1">
       <c r="A154" s="12" t="inlineStr">
         <is>
-          <t>161</t>
+          <t>162</t>
         </is>
       </c>
       <c r="B154" s="13" t="inlineStr">
@@ -12020,7 +12021,7 @@
       </c>
       <c r="D154" s="14" t="inlineStr">
         <is>
-          <t>2007</t>
+          <t>2011</t>
         </is>
       </c>
       <c r="E154" s="13" t="inlineStr">
@@ -12036,7 +12037,7 @@
       <c r="G154" s="13" t="inlineStr"/>
       <c r="H154" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I154" s="13" t="inlineStr">
@@ -12047,7 +12048,7 @@
       <c r="J154" s="14" t="inlineStr"/>
       <c r="K154" s="12" t="inlineStr">
         <is>
-          <t>161_Spain_2007_1euro_Regular.jpeg</t>
+          <t>162_Spain_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L154" s="13" t="inlineStr"/>
@@ -12073,15 +12074,15 @@
       </c>
       <c r="Q154" s="16" t="inlineStr">
         <is>
-          <t>Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela. There are three series of coins in circulation. All are valid.
-The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.</t>
+          <t>For the second series, the coins were slightly redesigned in 2010 in order to comply with the common guidelines issued by the European Commission. The year, for instance, is inscribed on the inner part of the coin.
+In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
         </is>
       </c>
     </row>
     <row r="155" ht="15" customHeight="1">
       <c r="A155" s="12" t="inlineStr">
         <is>
-          <t>162</t>
+          <t>163</t>
         </is>
       </c>
       <c r="B155" s="13" t="inlineStr">
@@ -12096,7 +12097,7 @@
       </c>
       <c r="D155" s="14" t="inlineStr">
         <is>
-          <t>2011</t>
+          <t>2024</t>
         </is>
       </c>
       <c r="E155" s="13" t="inlineStr">
@@ -12112,7 +12113,7 @@
       <c r="G155" s="13" t="inlineStr"/>
       <c r="H155" s="13" t="inlineStr">
         <is>
-          <t>F</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I155" s="13" t="inlineStr">
@@ -12123,7 +12124,7 @@
       <c r="J155" s="14" t="inlineStr"/>
       <c r="K155" s="12" t="inlineStr">
         <is>
-          <t>162_Spain_2011_1euro_Regular.jpeg</t>
+          <t>163_Spain_2024_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L155" s="13" t="inlineStr"/>
@@ -12149,7 +12150,7 @@
       </c>
       <c r="Q155" s="16" t="inlineStr">
         <is>
-          <t>For the second series, the coins were slightly redesigned in 2010 in order to comply with the common guidelines issued by the European Commission. The year, for instance, is inscribed on the inner part of the coin.
+          <t>Spain has updated the design of the Spanish national face of the 1 and 2 euro coins to be produced from 2015 in order to illustrate the change in the position of the Head of State. 1 and 2 euro coins from previous years featuring the old Spanish national face will remain valid.
 In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
         </is>
       </c>
@@ -12157,22 +12158,22 @@
     <row r="156" ht="15" customHeight="1">
       <c r="A156" s="12" t="inlineStr">
         <is>
-          <t>163</t>
+          <t>164</t>
         </is>
       </c>
       <c r="B156" s="13" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="C156" s="12" t="inlineStr">
         <is>
-          <t>ES</t>
+          <t>NL</t>
         </is>
       </c>
       <c r="D156" s="14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2000</t>
         </is>
       </c>
       <c r="E156" s="13" t="inlineStr">
@@ -12188,7 +12189,7 @@
       <c r="G156" s="13" t="inlineStr"/>
       <c r="H156" s="13" t="inlineStr">
         <is>
-          <t>XF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I156" s="13" t="inlineStr">
@@ -12199,7 +12200,7 @@
       <c r="J156" s="14" t="inlineStr"/>
       <c r="K156" s="12" t="inlineStr">
         <is>
-          <t>163_Spain_2024_1euro_Regular.jpeg</t>
+          <t>164_Netherlands_2000_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L156" s="13" t="inlineStr"/>
@@ -12220,91 +12221,34 @@
       </c>
       <c r="P156" s="15" t="inlineStr">
         <is>
-          <t>Regular 1 € circulation coin of Spain.</t>
+          <t>Regular 1 € circulation coin of Netherlands.</t>
         </is>
       </c>
       <c r="Q156" s="16" t="inlineStr">
-        <is>
-          <t>Spain has updated the design of the Spanish national face of the 1 and 2 euro coins to be produced from 2015 in order to illustrate the change in the position of the Head of State. 1 and 2 euro coins from previous years featuring the old Spanish national face will remain valid.
-In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
-        </is>
-      </c>
-    </row>
-    <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="12" t="inlineStr">
-        <is>
-          <t>164</t>
-        </is>
-      </c>
-      <c r="B157" s="13" t="inlineStr">
-        <is>
-          <t>Netherlands</t>
-        </is>
-      </c>
-      <c r="C157" s="12" t="inlineStr">
-        <is>
-          <t>NL</t>
-        </is>
-      </c>
-      <c r="D157" s="14" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="E157" s="13" t="inlineStr">
-        <is>
-          <t>1 €</t>
-        </is>
-      </c>
-      <c r="F157" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G157" s="13" t="inlineStr"/>
-      <c r="H157" s="13" t="inlineStr">
-        <is>
-          <t>F</t>
-        </is>
-      </c>
-      <c r="I157" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J157" s="14" t="inlineStr"/>
-      <c r="K157" s="12" t="inlineStr">
-        <is>
-          <t>164_Netherlands_2000_1euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L157" s="13" t="inlineStr"/>
-      <c r="M157" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N157" s="12" t="inlineStr">
-        <is>
-          <t>7.50 g</t>
-        </is>
-      </c>
-      <c r="O157" s="12" t="inlineStr">
-        <is>
-          <t>23.25 mm</t>
-        </is>
-      </c>
-      <c r="P157" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 € circulation coin of Netherlands.</t>
-        </is>
-      </c>
-      <c r="Q157" s="16" t="inlineStr">
         <is>
           <t>The Netherlands chose two designs by Bruno Ninaber van Eyben, showing Queen Beatrix, for the first series. There are two series of coins in circulation. Both are valid.
 First series: Queen Beatrix is shown with the inscription "Beatrix Koningin der Nederlanden" (Queen of the Netherlands).</t>
         </is>
       </c>
+    </row>
+    <row r="157" ht="15" customHeight="1">
+      <c r="A157" s="5" t="n"/>
+      <c r="B157" s="6" t="n"/>
+      <c r="C157" s="5" t="n"/>
+      <c r="D157" s="7" t="n"/>
+      <c r="E157" s="6" t="n"/>
+      <c r="F157" s="6" t="n"/>
+      <c r="G157" s="6" t="n"/>
+      <c r="H157" s="6" t="n"/>
+      <c r="I157" s="6" t="n"/>
+      <c r="J157" s="7" t="n"/>
+      <c r="K157" s="5" t="n"/>
+      <c r="L157" s="6" t="n"/>
+      <c r="M157" s="5" t="n"/>
+      <c r="N157" s="5" t="n"/>
+      <c r="O157" s="5" t="n"/>
+      <c r="P157" s="8" t="n"/>
+      <c r="Q157" s="9" t="n"/>
     </row>
     <row r="158" ht="15" customHeight="1">
       <c r="A158" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -1335,8 +1335,10 @@
           <t>BE</t>
         </is>
       </c>
-      <c r="D12" s="14" t="n">
-        <v>2002</v>
+      <c r="D12" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
         <is>
@@ -1348,11 +1350,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>1 Euro</t>
-        </is>
-      </c>
+      <c r="G12" s="13" t="inlineStr"/>
       <c r="H12" s="13" t="inlineStr">
         <is>
           <t>VF</t>
@@ -1366,7 +1364,7 @@
       <c r="J12" s="14" t="inlineStr"/>
       <c r="K12" s="12" t="inlineStr">
         <is>
-          <t>013_Belgium_2002_1Euro_Regular.jpeg</t>
+          <t>013_Belgium_2002_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L12" s="13" t="inlineStr"/>
@@ -8861,8 +8859,10 @@
           <t>EE</t>
         </is>
       </c>
-      <c r="D113" s="14" t="n">
-        <v>2011</v>
+      <c r="D113" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="E113" s="13" t="inlineStr">
         <is>
@@ -8874,11 +8874,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G113" s="13" t="inlineStr">
-        <is>
-          <t>1 Euro</t>
-        </is>
-      </c>
+      <c r="G113" s="13" t="inlineStr"/>
       <c r="H113" s="13" t="inlineStr">
         <is>
           <t>F</t>
@@ -8892,7 +8888,7 @@
       <c r="J113" s="14" t="inlineStr"/>
       <c r="K113" s="12" t="inlineStr">
         <is>
-          <t>114_Estonia_2011_1Euro_Regular.jpeg</t>
+          <t>114_Estonia_2011_1euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L113" s="13" t="inlineStr"/>
@@ -12232,270 +12228,1023 @@
       </c>
     </row>
     <row r="157" ht="15" customHeight="1">
-      <c r="A157" s="5" t="n"/>
-      <c r="B157" s="6" t="n"/>
-      <c r="C157" s="5" t="n"/>
-      <c r="D157" s="7" t="n"/>
-      <c r="E157" s="6" t="n"/>
-      <c r="F157" s="6" t="n"/>
-      <c r="G157" s="6" t="n"/>
-      <c r="H157" s="6" t="n"/>
-      <c r="I157" s="6" t="n"/>
-      <c r="J157" s="7" t="n"/>
-      <c r="K157" s="5" t="n"/>
-      <c r="L157" s="6" t="n"/>
-      <c r="M157" s="5" t="n"/>
-      <c r="N157" s="5" t="n"/>
-      <c r="O157" s="5" t="n"/>
-      <c r="P157" s="8" t="n"/>
-      <c r="Q157" s="9" t="n"/>
+      <c r="A157" s="12" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B157" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C157" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D157" s="14" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E157" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F157" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G157" s="13" t="inlineStr"/>
+      <c r="H157" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I157" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr"/>
+      <c r="K157" s="12" t="inlineStr">
+        <is>
+          <t>165_Netherlands_2003_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L157" s="13" t="inlineStr"/>
+      <c r="M157" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N157" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O157" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P157" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q157" s="16" t="inlineStr"/>
     </row>
     <row r="158" ht="15" customHeight="1">
-      <c r="A158" s="5" t="n"/>
-      <c r="B158" s="6" t="n"/>
-      <c r="C158" s="5" t="n"/>
-      <c r="D158" s="7" t="n"/>
-      <c r="E158" s="6" t="n"/>
-      <c r="F158" s="6" t="n"/>
-      <c r="G158" s="6" t="n"/>
-      <c r="H158" s="6" t="n"/>
-      <c r="I158" s="6" t="n"/>
-      <c r="J158" s="7" t="n"/>
-      <c r="K158" s="5" t="n"/>
-      <c r="L158" s="6" t="n"/>
-      <c r="M158" s="5" t="n"/>
-      <c r="N158" s="5" t="n"/>
-      <c r="O158" s="5" t="n"/>
-      <c r="P158" s="8" t="n"/>
-      <c r="Q158" s="9" t="n"/>
+      <c r="A158" s="12" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B158" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C158" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D158" s="14" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E158" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F158" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G158" s="13" t="inlineStr"/>
+      <c r="H158" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I158" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J158" s="14" t="inlineStr"/>
+      <c r="K158" s="12" t="inlineStr">
+        <is>
+          <t>166_Netherlands_2001_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L158" s="13" t="inlineStr"/>
+      <c r="M158" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N158" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O158" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P158" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q158" s="16" t="inlineStr"/>
     </row>
     <row r="159" ht="15" customHeight="1">
-      <c r="A159" s="5" t="n"/>
-      <c r="B159" s="6" t="n"/>
-      <c r="C159" s="5" t="n"/>
-      <c r="D159" s="7" t="n"/>
-      <c r="E159" s="6" t="n"/>
-      <c r="F159" s="6" t="n"/>
-      <c r="G159" s="6" t="n"/>
-      <c r="H159" s="6" t="n"/>
-      <c r="I159" s="6" t="n"/>
-      <c r="J159" s="7" t="n"/>
-      <c r="K159" s="5" t="n"/>
-      <c r="L159" s="6" t="n"/>
-      <c r="M159" s="5" t="n"/>
-      <c r="N159" s="5" t="n"/>
-      <c r="O159" s="5" t="n"/>
-      <c r="P159" s="8" t="n"/>
-      <c r="Q159" s="9" t="n"/>
+      <c r="A159" s="12" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B159" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C159" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D159" s="14" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="E159" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F159" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G159" s="13" t="inlineStr"/>
+      <c r="H159" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I159" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J159" s="14" t="inlineStr"/>
+      <c r="K159" s="12" t="inlineStr">
+        <is>
+          <t>167_Netherlands_2005_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L159" s="13" t="inlineStr"/>
+      <c r="M159" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N159" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O159" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P159" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q159" s="16" t="inlineStr"/>
     </row>
     <row r="160" ht="15" customHeight="1">
-      <c r="A160" s="5" t="n"/>
-      <c r="B160" s="6" t="n"/>
-      <c r="C160" s="5" t="n"/>
-      <c r="D160" s="7" t="n"/>
-      <c r="E160" s="6" t="n"/>
-      <c r="F160" s="6" t="n"/>
-      <c r="G160" s="6" t="n"/>
-      <c r="H160" s="6" t="n"/>
-      <c r="I160" s="6" t="n"/>
-      <c r="J160" s="7" t="n"/>
-      <c r="K160" s="5" t="n"/>
-      <c r="L160" s="6" t="n"/>
-      <c r="M160" s="5" t="n"/>
-      <c r="N160" s="5" t="n"/>
-      <c r="O160" s="5" t="n"/>
-      <c r="P160" s="8" t="n"/>
-      <c r="Q160" s="9" t="n"/>
+      <c r="A160" s="12" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B160" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C160" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D160" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E160" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F160" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G160" s="13" t="inlineStr"/>
+      <c r="H160" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I160" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J160" s="14" t="inlineStr"/>
+      <c r="K160" s="12" t="inlineStr">
+        <is>
+          <t>168_Netherlands_1999_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L160" s="13" t="inlineStr"/>
+      <c r="M160" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N160" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O160" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P160" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q160" s="16" t="inlineStr"/>
     </row>
     <row r="161" ht="15" customHeight="1">
-      <c r="A161" s="5" t="n"/>
-      <c r="B161" s="6" t="n"/>
-      <c r="C161" s="5" t="n"/>
-      <c r="D161" s="7" t="n"/>
-      <c r="E161" s="6" t="n"/>
-      <c r="F161" s="6" t="n"/>
-      <c r="G161" s="6" t="n"/>
-      <c r="H161" s="6" t="n"/>
-      <c r="I161" s="6" t="n"/>
-      <c r="J161" s="7" t="n"/>
-      <c r="K161" s="5" t="n"/>
-      <c r="L161" s="6" t="n"/>
-      <c r="M161" s="5" t="n"/>
-      <c r="N161" s="5" t="n"/>
-      <c r="O161" s="5" t="n"/>
-      <c r="P161" s="8" t="n"/>
-      <c r="Q161" s="9" t="n"/>
+      <c r="A161" s="12" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B161" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C161" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D161" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E161" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F161" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G161" s="13" t="inlineStr"/>
+      <c r="H161" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I161" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J161" s="14" t="inlineStr"/>
+      <c r="K161" s="12" t="inlineStr">
+        <is>
+          <t>169_Netherlands_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L161" s="13" t="inlineStr"/>
+      <c r="M161" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N161" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O161" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P161" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q161" s="16" t="inlineStr"/>
     </row>
     <row r="162" ht="15" customHeight="1">
-      <c r="A162" s="5" t="n"/>
-      <c r="B162" s="6" t="n"/>
-      <c r="C162" s="5" t="n"/>
-      <c r="D162" s="7" t="n"/>
-      <c r="E162" s="6" t="n"/>
-      <c r="F162" s="6" t="n"/>
-      <c r="G162" s="6" t="n"/>
-      <c r="H162" s="6" t="n"/>
-      <c r="I162" s="6" t="n"/>
-      <c r="J162" s="7" t="n"/>
-      <c r="K162" s="5" t="n"/>
-      <c r="L162" s="6" t="n"/>
-      <c r="M162" s="5" t="n"/>
-      <c r="N162" s="5" t="n"/>
-      <c r="O162" s="5" t="n"/>
-      <c r="P162" s="8" t="n"/>
-      <c r="Q162" s="9" t="n"/>
+      <c r="A162" s="12" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B162" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C162" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D162" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E162" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F162" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G162" s="13" t="inlineStr"/>
+      <c r="H162" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I162" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J162" s="14" t="inlineStr"/>
+      <c r="K162" s="12" t="inlineStr">
+        <is>
+          <t>170_Netherlands_2002_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L162" s="13" t="inlineStr"/>
+      <c r="M162" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N162" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O162" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P162" s="15" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the profile of Queen Beatrix with the inscription ‘Beatrix Koningin der Nederlanden’ (Beatrix Queen of The Netherlands) in Dutch. They were designed by Bruno Ninaber van Eyben.</t>
+        </is>
+      </c>
+      <c r="Q162" s="16" t="inlineStr"/>
     </row>
     <row r="163" ht="15" customHeight="1">
-      <c r="A163" s="5" t="n"/>
-      <c r="B163" s="6" t="n"/>
-      <c r="C163" s="5" t="n"/>
-      <c r="D163" s="7" t="n"/>
-      <c r="E163" s="6" t="n"/>
-      <c r="F163" s="6" t="n"/>
-      <c r="G163" s="6" t="n"/>
-      <c r="H163" s="6" t="n"/>
-      <c r="I163" s="6" t="n"/>
-      <c r="J163" s="7" t="n"/>
-      <c r="K163" s="5" t="n"/>
-      <c r="L163" s="6" t="n"/>
-      <c r="M163" s="5" t="n"/>
-      <c r="N163" s="5" t="n"/>
-      <c r="O163" s="5" t="n"/>
-      <c r="P163" s="8" t="n"/>
-      <c r="Q163" s="9" t="n"/>
+      <c r="A163" s="12" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B163" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C163" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D163" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E163" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F163" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G163" s="13" t="inlineStr"/>
+      <c r="H163" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I163" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J163" s="14" t="inlineStr"/>
+      <c r="K163" s="12" t="inlineStr">
+        <is>
+          <t>171_Netherlands_2022_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L163" s="13" t="inlineStr"/>
+      <c r="M163" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N163" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O163" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P163" s="15" t="inlineStr">
+        <is>
+          <t>Second series: As of 2014, Superimposed on an effigy of the King Willem-Alexander are the words "Willem-Alexander Koning der Nederlanden" (King of the Netherlands). The mint marks appear on either side of the name.</t>
+        </is>
+      </c>
+      <c r="Q163" s="16" t="inlineStr"/>
     </row>
     <row r="164" ht="15" customHeight="1">
-      <c r="A164" s="5" t="n"/>
-      <c r="B164" s="6" t="n"/>
-      <c r="C164" s="5" t="n"/>
-      <c r="D164" s="7" t="n"/>
-      <c r="E164" s="6" t="n"/>
-      <c r="F164" s="6" t="n"/>
-      <c r="G164" s="6" t="n"/>
-      <c r="H164" s="6" t="n"/>
-      <c r="I164" s="6" t="n"/>
-      <c r="J164" s="7" t="n"/>
-      <c r="K164" s="5" t="n"/>
-      <c r="L164" s="6" t="n"/>
-      <c r="M164" s="5" t="n"/>
-      <c r="N164" s="5" t="n"/>
-      <c r="O164" s="5" t="n"/>
-      <c r="P164" s="8" t="n"/>
-      <c r="Q164" s="9" t="n"/>
+      <c r="A164" s="12" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B164" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C164" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D164" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E164" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F164" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G164" s="13" t="inlineStr"/>
+      <c r="H164" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I164" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J164" s="14" t="inlineStr"/>
+      <c r="K164" s="12" t="inlineStr">
+        <is>
+          <t>172_Netherlands_2024_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L164" s="13" t="inlineStr"/>
+      <c r="M164" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N164" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O164" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P164" s="15" t="inlineStr">
+        <is>
+          <t>Second series: As of 2014, Superimposed on an effigy of the King Willem-Alexander are the words "Willem-Alexander Koning der Nederlanden" (King of the Netherlands). The mint marks appear on either side of the name.</t>
+        </is>
+      </c>
+      <c r="Q164" s="16" t="inlineStr"/>
     </row>
     <row r="165" ht="15" customHeight="1">
-      <c r="A165" s="5" t="n"/>
-      <c r="B165" s="6" t="n"/>
-      <c r="C165" s="5" t="n"/>
-      <c r="D165" s="7" t="n"/>
-      <c r="E165" s="6" t="n"/>
-      <c r="F165" s="6" t="n"/>
-      <c r="G165" s="6" t="n"/>
-      <c r="H165" s="6" t="n"/>
-      <c r="I165" s="6" t="n"/>
-      <c r="J165" s="7" t="n"/>
-      <c r="K165" s="5" t="n"/>
-      <c r="L165" s="6" t="n"/>
-      <c r="M165" s="5" t="n"/>
-      <c r="N165" s="5" t="n"/>
-      <c r="O165" s="5" t="n"/>
-      <c r="P165" s="8" t="n"/>
-      <c r="Q165" s="9" t="n"/>
+      <c r="A165" s="12" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B165" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C165" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D165" s="14" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E165" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F165" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G165" s="13" t="inlineStr"/>
+      <c r="H165" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I165" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J165" s="14" t="inlineStr"/>
+      <c r="K165" s="12" t="inlineStr">
+        <is>
+          <t>173_Netherlands_2016_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L165" s="13" t="inlineStr"/>
+      <c r="M165" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N165" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O165" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P165" s="15" t="inlineStr">
+        <is>
+          <t>Second series: As of 2014, Superimposed on an effigy of the King Willem-Alexander are the words "Willem-Alexander Koning der Nederlanden" (King of the Netherlands). The mint marks appear on either side of the name.</t>
+        </is>
+      </c>
+      <c r="Q165" s="16" t="inlineStr"/>
     </row>
     <row r="166" ht="15" customHeight="1">
-      <c r="A166" s="5" t="n"/>
-      <c r="B166" s="6" t="n"/>
-      <c r="C166" s="5" t="n"/>
-      <c r="D166" s="7" t="n"/>
-      <c r="E166" s="6" t="n"/>
-      <c r="F166" s="6" t="n"/>
-      <c r="G166" s="6" t="n"/>
-      <c r="H166" s="6" t="n"/>
-      <c r="I166" s="6" t="n"/>
-      <c r="J166" s="7" t="n"/>
-      <c r="K166" s="5" t="n"/>
-      <c r="L166" s="6" t="n"/>
-      <c r="M166" s="5" t="n"/>
-      <c r="N166" s="5" t="n"/>
-      <c r="O166" s="5" t="n"/>
-      <c r="P166" s="8" t="n"/>
-      <c r="Q166" s="9" t="n"/>
+      <c r="A166" s="12" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B166" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C166" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D166" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E166" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F166" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G166" s="13" t="inlineStr"/>
+      <c r="H166" s="13" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="I166" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J166" s="14" t="inlineStr"/>
+      <c r="K166" s="12" t="inlineStr">
+        <is>
+          <t>174_Portugal_2002_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L166" s="13" t="inlineStr"/>
+      <c r="M166" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N166" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O166" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P166" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q166" s="16" t="inlineStr">
+        <is>
+          <t>1, 2 and 5-cent coins: these bear the image of the first royal seal, from 1134, along with the inscription "Portugal".
+Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs:</t>
+        </is>
+      </c>
     </row>
     <row r="167" ht="15" customHeight="1">
-      <c r="A167" s="5" t="n"/>
-      <c r="B167" s="6" t="n"/>
-      <c r="C167" s="5" t="n"/>
-      <c r="D167" s="7" t="n"/>
-      <c r="E167" s="6" t="n"/>
-      <c r="F167" s="6" t="n"/>
-      <c r="G167" s="6" t="n"/>
-      <c r="H167" s="6" t="n"/>
-      <c r="I167" s="6" t="n"/>
-      <c r="J167" s="7" t="n"/>
-      <c r="K167" s="5" t="n"/>
-      <c r="L167" s="6" t="n"/>
-      <c r="M167" s="5" t="n"/>
-      <c r="N167" s="5" t="n"/>
-      <c r="O167" s="5" t="n"/>
-      <c r="P167" s="8" t="n"/>
-      <c r="Q167" s="9" t="n"/>
+      <c r="A167" s="12" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B167" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C167" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D167" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E167" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F167" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G167" s="13" t="inlineStr"/>
+      <c r="H167" s="13" t="inlineStr">
+        <is>
+          <t>VG</t>
+        </is>
+      </c>
+      <c r="I167" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J167" s="14" t="inlineStr"/>
+      <c r="K167" s="12" t="inlineStr">
+        <is>
+          <t>175_Portugal_2002_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L167" s="13" t="inlineStr"/>
+      <c r="M167" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N167" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O167" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P167" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q167" s="16" t="inlineStr">
+        <is>
+          <t>1, 2 and 5-cent coins: these bear the image of the first royal seal, from 1134, along with the inscription "Portugal".
+Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs:</t>
+        </is>
+      </c>
     </row>
     <row r="168" ht="15" customHeight="1">
-      <c r="A168" s="5" t="n"/>
-      <c r="B168" s="6" t="n"/>
-      <c r="C168" s="5" t="n"/>
-      <c r="D168" s="7" t="n"/>
-      <c r="E168" s="6" t="n"/>
-      <c r="F168" s="6" t="n"/>
-      <c r="G168" s="6" t="n"/>
-      <c r="H168" s="6" t="n"/>
-      <c r="I168" s="6" t="n"/>
-      <c r="J168" s="7" t="n"/>
-      <c r="K168" s="5" t="n"/>
-      <c r="L168" s="6" t="n"/>
-      <c r="M168" s="5" t="n"/>
-      <c r="N168" s="5" t="n"/>
-      <c r="O168" s="5" t="n"/>
-      <c r="P168" s="8" t="n"/>
-      <c r="Q168" s="9" t="n"/>
+      <c r="A168" s="12" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B168" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C168" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D168" s="14" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E168" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F168" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G168" s="13" t="inlineStr"/>
+      <c r="H168" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I168" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J168" s="14" t="inlineStr"/>
+      <c r="K168" s="12" t="inlineStr">
+        <is>
+          <t>176_Portugal_2016_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L168" s="13" t="inlineStr"/>
+      <c r="M168" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N168" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O168" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P168" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q168" s="16" t="inlineStr">
+        <is>
+          <t>10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
+Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs:</t>
+        </is>
+      </c>
     </row>
     <row r="169" ht="15" customHeight="1">
-      <c r="A169" s="5" t="n"/>
-      <c r="B169" s="6" t="n"/>
-      <c r="C169" s="5" t="n"/>
-      <c r="D169" s="7" t="n"/>
-      <c r="E169" s="6" t="n"/>
-      <c r="F169" s="6" t="n"/>
-      <c r="G169" s="6" t="n"/>
-      <c r="H169" s="6" t="n"/>
-      <c r="I169" s="6" t="n"/>
-      <c r="J169" s="7" t="n"/>
-      <c r="K169" s="5" t="n"/>
-      <c r="L169" s="6" t="n"/>
-      <c r="M169" s="5" t="n"/>
-      <c r="N169" s="5" t="n"/>
-      <c r="O169" s="5" t="n"/>
-      <c r="P169" s="8" t="n"/>
-      <c r="Q169" s="9" t="n"/>
+      <c r="A169" s="12" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B169" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C169" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D169" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E169" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F169" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G169" s="13" t="inlineStr"/>
+      <c r="H169" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I169" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J169" s="14" t="inlineStr"/>
+      <c r="K169" s="12" t="inlineStr">
+        <is>
+          <t>177_Portugal_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L169" s="13" t="inlineStr"/>
+      <c r="M169" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N169" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O169" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P169" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q169" s="16" t="inlineStr">
+        <is>
+          <t>10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
+Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs:</t>
+        </is>
+      </c>
     </row>
     <row r="170" ht="15" customHeight="1">
-      <c r="A170" s="5" t="n"/>
-      <c r="B170" s="6" t="n"/>
-      <c r="C170" s="5" t="n"/>
-      <c r="D170" s="7" t="n"/>
-      <c r="E170" s="6" t="n"/>
-      <c r="F170" s="6" t="n"/>
-      <c r="G170" s="6" t="n"/>
-      <c r="H170" s="6" t="n"/>
-      <c r="I170" s="6" t="n"/>
-      <c r="J170" s="7" t="n"/>
-      <c r="K170" s="5" t="n"/>
-      <c r="L170" s="6" t="n"/>
-      <c r="M170" s="5" t="n"/>
-      <c r="N170" s="5" t="n"/>
-      <c r="O170" s="5" t="n"/>
-      <c r="P170" s="8" t="n"/>
-      <c r="Q170" s="9" t="n"/>
+      <c r="A170" s="12" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B170" s="13" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+      <c r="C170" s="12" t="inlineStr">
+        <is>
+          <t>PT</t>
+        </is>
+      </c>
+      <c r="D170" s="14" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E170" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F170" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G170" s="13" t="inlineStr"/>
+      <c r="H170" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I170" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J170" s="14" t="inlineStr"/>
+      <c r="K170" s="12" t="inlineStr">
+        <is>
+          <t>178_Portugal_2017_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L170" s="13" t="inlineStr"/>
+      <c r="M170" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N170" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O170" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P170" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Portugal.</t>
+        </is>
+      </c>
+      <c r="Q170" s="16" t="inlineStr">
+        <is>
+          <t>10, 20 and 50-cent coins: these depict the royal seal of 1142 as the centrepiece of the design.
+Three different euro designs were chosen from entries to a national competition. Designer Vítor Manuel Fernandes dos Santos, who drew his inspiration from historical symbols and the seals of the first King of Portugal, Dom Afonso Henriques, won the competition with the following motifs:</t>
+        </is>
+      </c>
     </row>
     <row r="171" ht="15" customHeight="1">
       <c r="A171" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -13247,118 +13247,460 @@
       </c>
     </row>
     <row r="171" ht="15" customHeight="1">
-      <c r="A171" s="5" t="n"/>
-      <c r="B171" s="6" t="n"/>
-      <c r="C171" s="5" t="n"/>
-      <c r="D171" s="7" t="n"/>
-      <c r="E171" s="6" t="n"/>
-      <c r="F171" s="6" t="n"/>
-      <c r="G171" s="6" t="n"/>
-      <c r="H171" s="6" t="n"/>
-      <c r="I171" s="6" t="n"/>
-      <c r="J171" s="7" t="n"/>
-      <c r="K171" s="5" t="n"/>
-      <c r="L171" s="6" t="n"/>
-      <c r="M171" s="5" t="n"/>
-      <c r="N171" s="5" t="n"/>
-      <c r="O171" s="5" t="n"/>
-      <c r="P171" s="8" t="n"/>
-      <c r="Q171" s="9" t="n"/>
+      <c r="A171" s="12" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B171" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C171" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D171" s="14" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E171" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F171" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G171" s="13" t="inlineStr"/>
+      <c r="H171" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I171" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J171" s="14" t="inlineStr"/>
+      <c r="K171" s="12" t="inlineStr">
+        <is>
+          <t>179_Slovakia_2020_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L171" s="13" t="inlineStr"/>
+      <c r="M171" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N171" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O171" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P171" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q171" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 1, 2 and 5 cent coins feature the Tatra Mountains’ peak, Kriváň, a symbol of the sovereignty of the Slovak nation, and the national emblem of Slovakia.</t>
+        </is>
+      </c>
     </row>
     <row r="172" ht="15" customHeight="1">
-      <c r="A172" s="5" t="n"/>
-      <c r="B172" s="6" t="n"/>
-      <c r="C172" s="5" t="n"/>
-      <c r="D172" s="7" t="n"/>
-      <c r="E172" s="6" t="n"/>
-      <c r="F172" s="6" t="n"/>
-      <c r="G172" s="6" t="n"/>
-      <c r="H172" s="6" t="n"/>
-      <c r="I172" s="6" t="n"/>
-      <c r="J172" s="7" t="n"/>
-      <c r="K172" s="5" t="n"/>
-      <c r="L172" s="6" t="n"/>
-      <c r="M172" s="5" t="n"/>
-      <c r="N172" s="5" t="n"/>
-      <c r="O172" s="5" t="n"/>
-      <c r="P172" s="8" t="n"/>
-      <c r="Q172" s="9" t="n"/>
+      <c r="A172" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B172" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C172" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D172" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E172" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F172" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G172" s="13" t="inlineStr"/>
+      <c r="H172" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I172" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J172" s="14" t="inlineStr"/>
+      <c r="K172" s="12" t="inlineStr">
+        <is>
+          <t>180_Slovakia_2018_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L172" s="13" t="inlineStr"/>
+      <c r="M172" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N172" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O172" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P172" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q172" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 1, 2 and 5 cent coins feature the Tatra Mountains’ peak, Kriváň, a symbol of the sovereignty of the Slovak nation, and the national emblem of Slovakia.</t>
+        </is>
+      </c>
     </row>
     <row r="173" ht="15" customHeight="1">
-      <c r="A173" s="5" t="n"/>
-      <c r="B173" s="6" t="n"/>
-      <c r="C173" s="5" t="n"/>
-      <c r="D173" s="7" t="n"/>
-      <c r="E173" s="6" t="n"/>
-      <c r="F173" s="6" t="n"/>
-      <c r="G173" s="6" t="n"/>
-      <c r="H173" s="6" t="n"/>
-      <c r="I173" s="6" t="n"/>
-      <c r="J173" s="7" t="n"/>
-      <c r="K173" s="5" t="n"/>
-      <c r="L173" s="6" t="n"/>
-      <c r="M173" s="5" t="n"/>
-      <c r="N173" s="5" t="n"/>
-      <c r="O173" s="5" t="n"/>
-      <c r="P173" s="8" t="n"/>
-      <c r="Q173" s="9" t="n"/>
+      <c r="A173" s="12" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B173" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C173" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D173" s="14" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E173" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F173" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G173" s="13" t="inlineStr"/>
+      <c r="H173" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I173" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J173" s="14" t="inlineStr"/>
+      <c r="K173" s="12" t="inlineStr">
+        <is>
+          <t>181_Slovakia_2020_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L173" s="13" t="inlineStr"/>
+      <c r="M173" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N173" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O173" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P173" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q173" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 1, 2 and 5 cent coins feature the Tatra Mountains’ peak, Kriváň, a symbol of the sovereignty of the Slovak nation, and the national emblem of Slovakia.</t>
+        </is>
+      </c>
     </row>
     <row r="174" ht="15" customHeight="1">
-      <c r="A174" s="5" t="n"/>
-      <c r="B174" s="6" t="n"/>
-      <c r="C174" s="5" t="n"/>
-      <c r="D174" s="7" t="n"/>
-      <c r="E174" s="6" t="n"/>
-      <c r="F174" s="6" t="n"/>
-      <c r="G174" s="6" t="n"/>
-      <c r="H174" s="6" t="n"/>
-      <c r="I174" s="6" t="n"/>
-      <c r="J174" s="7" t="n"/>
-      <c r="K174" s="5" t="n"/>
-      <c r="L174" s="6" t="n"/>
-      <c r="M174" s="5" t="n"/>
-      <c r="N174" s="5" t="n"/>
-      <c r="O174" s="5" t="n"/>
-      <c r="P174" s="8" t="n"/>
-      <c r="Q174" s="9" t="n"/>
+      <c r="A174" s="12" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B174" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C174" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D174" s="14" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E174" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F174" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G174" s="13" t="inlineStr"/>
+      <c r="H174" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I174" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J174" s="14" t="inlineStr"/>
+      <c r="K174" s="12" t="inlineStr">
+        <is>
+          <t>182_Slovakia_2020_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L174" s="13" t="inlineStr"/>
+      <c r="M174" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N174" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O174" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P174" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q174" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 10-, 20- and 50-cent coins depict the Bratislava Castle, a massive rectangular building standing above the Danube whose origins date back to the 9th century. The castle is one of the most famous Slovak monuments and is an important cultural symbol. The design was created by Ján Černaj and Pavol Károly.</t>
+        </is>
+      </c>
     </row>
     <row r="175" ht="15" customHeight="1">
-      <c r="A175" s="5" t="n"/>
-      <c r="B175" s="6" t="n"/>
-      <c r="C175" s="5" t="n"/>
-      <c r="D175" s="7" t="n"/>
-      <c r="E175" s="6" t="n"/>
-      <c r="F175" s="6" t="n"/>
-      <c r="G175" s="6" t="n"/>
-      <c r="H175" s="6" t="n"/>
-      <c r="I175" s="6" t="n"/>
-      <c r="J175" s="7" t="n"/>
-      <c r="K175" s="5" t="n"/>
-      <c r="L175" s="6" t="n"/>
-      <c r="M175" s="5" t="n"/>
-      <c r="N175" s="5" t="n"/>
-      <c r="O175" s="5" t="n"/>
-      <c r="P175" s="8" t="n"/>
-      <c r="Q175" s="9" t="n"/>
+      <c r="A175" s="12" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B175" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C175" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D175" s="14" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E175" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F175" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G175" s="13" t="inlineStr"/>
+      <c r="H175" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I175" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J175" s="14" t="inlineStr"/>
+      <c r="K175" s="12" t="inlineStr">
+        <is>
+          <t>183_Slovakia_2009_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L175" s="13" t="inlineStr"/>
+      <c r="M175" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N175" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O175" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P175" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q175" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 10-, 20- and 50-cent coins depict the Bratislava Castle, a massive rectangular building standing above the Danube whose origins date back to the 9th century. The castle is one of the most famous Slovak monuments and is an important cultural symbol. The design was created by Ján Černaj and Pavol Károly.</t>
+        </is>
+      </c>
     </row>
     <row r="176" ht="15" customHeight="1">
-      <c r="A176" s="5" t="n"/>
-      <c r="B176" s="6" t="n"/>
-      <c r="C176" s="5" t="n"/>
-      <c r="D176" s="7" t="n"/>
-      <c r="E176" s="6" t="n"/>
-      <c r="F176" s="6" t="n"/>
-      <c r="G176" s="6" t="n"/>
-      <c r="H176" s="6" t="n"/>
-      <c r="I176" s="6" t="n"/>
-      <c r="J176" s="7" t="n"/>
-      <c r="K176" s="5" t="n"/>
-      <c r="L176" s="6" t="n"/>
-      <c r="M176" s="5" t="n"/>
-      <c r="N176" s="5" t="n"/>
-      <c r="O176" s="5" t="n"/>
-      <c r="P176" s="8" t="n"/>
-      <c r="Q176" s="9" t="n"/>
+      <c r="A176" s="12" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B176" s="13" t="inlineStr">
+        <is>
+          <t>Slovakia</t>
+        </is>
+      </c>
+      <c r="C176" s="12" t="inlineStr">
+        <is>
+          <t>SK</t>
+        </is>
+      </c>
+      <c r="D176" s="14" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E176" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F176" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G176" s="13" t="inlineStr"/>
+      <c r="H176" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I176" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J176" s="14" t="inlineStr"/>
+      <c r="K176" s="12" t="inlineStr">
+        <is>
+          <t>184_Slovakia_2009_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L176" s="13" t="inlineStr"/>
+      <c r="M176" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N176" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O176" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P176" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Slovakia.</t>
+        </is>
+      </c>
+      <c r="Q176" s="16" t="inlineStr">
+        <is>
+          <t>In July 2004, only two months after the country became a member of the European Union, the National Bank of Slovakia launched an open competition for the design of the national sides of the future Slovak euro coins.
+The 10-, 20- and 50-cent coins depict the Bratislava Castle, a massive rectangular building standing above the Danube whose origins date back to the 9th century. The castle is one of the most famous Slovak monuments and is an important cultural symbol. The design was created by Ján Černaj and Pavol Károly.</t>
+        </is>
+      </c>
     </row>
     <row r="177" ht="15" customHeight="1">
       <c r="A177" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -13703,346 +13703,1384 @@
       </c>
     </row>
     <row r="177" ht="15" customHeight="1">
-      <c r="A177" s="5" t="n"/>
-      <c r="B177" s="6" t="n"/>
-      <c r="C177" s="5" t="n"/>
-      <c r="D177" s="7" t="n"/>
-      <c r="E177" s="6" t="n"/>
-      <c r="F177" s="6" t="n"/>
-      <c r="G177" s="6" t="n"/>
-      <c r="H177" s="6" t="n"/>
-      <c r="I177" s="6" t="n"/>
-      <c r="J177" s="7" t="n"/>
-      <c r="K177" s="5" t="n"/>
-      <c r="L177" s="6" t="n"/>
-      <c r="M177" s="5" t="n"/>
-      <c r="N177" s="5" t="n"/>
-      <c r="O177" s="5" t="n"/>
-      <c r="P177" s="8" t="n"/>
-      <c r="Q177" s="9" t="n"/>
+      <c r="A177" s="12" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B177" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C177" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D177" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E177" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F177" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G177" s="13" t="inlineStr"/>
+      <c r="H177" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I177" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J177" s="14" t="inlineStr"/>
+      <c r="K177" s="12" t="inlineStr">
+        <is>
+          <t>185_Slovenia_2022_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L177" s="13" t="inlineStr"/>
+      <c r="M177" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N177" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O177" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P177" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q177" s="16" t="inlineStr">
+        <is>
+          <t>This coin bears the image of a stork.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="178" ht="15" customHeight="1">
-      <c r="A178" s="5" t="n"/>
-      <c r="B178" s="6" t="n"/>
-      <c r="C178" s="5" t="n"/>
-      <c r="D178" s="7" t="n"/>
-      <c r="E178" s="6" t="n"/>
-      <c r="F178" s="6" t="n"/>
-      <c r="G178" s="6" t="n"/>
-      <c r="H178" s="6" t="n"/>
-      <c r="I178" s="6" t="n"/>
-      <c r="J178" s="7" t="n"/>
-      <c r="K178" s="5" t="n"/>
-      <c r="L178" s="6" t="n"/>
-      <c r="M178" s="5" t="n"/>
-      <c r="N178" s="5" t="n"/>
-      <c r="O178" s="5" t="n"/>
-      <c r="P178" s="8" t="n"/>
-      <c r="Q178" s="9" t="n"/>
+      <c r="A178" s="12" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B178" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C178" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D178" s="14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E178" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F178" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G178" s="13" t="inlineStr"/>
+      <c r="H178" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I178" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J178" s="14" t="inlineStr"/>
+      <c r="K178" s="12" t="inlineStr">
+        <is>
+          <t>186_Slovenia_2025_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L178" s="13" t="inlineStr"/>
+      <c r="M178" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N178" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O178" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P178" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q178" s="16" t="inlineStr">
+        <is>
+          <t>The Sovereign Enthronement Stone features on this coin.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="179" ht="15" customHeight="1">
-      <c r="A179" s="5" t="n"/>
-      <c r="B179" s="6" t="n"/>
-      <c r="C179" s="5" t="n"/>
-      <c r="D179" s="7" t="n"/>
-      <c r="E179" s="6" t="n"/>
-      <c r="F179" s="6" t="n"/>
-      <c r="G179" s="6" t="n"/>
-      <c r="H179" s="6" t="n"/>
-      <c r="I179" s="6" t="n"/>
-      <c r="J179" s="7" t="n"/>
-      <c r="K179" s="5" t="n"/>
-      <c r="L179" s="6" t="n"/>
-      <c r="M179" s="5" t="n"/>
-      <c r="N179" s="5" t="n"/>
-      <c r="O179" s="5" t="n"/>
-      <c r="P179" s="8" t="n"/>
-      <c r="Q179" s="9" t="n"/>
+      <c r="A179" s="12" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B179" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C179" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D179" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E179" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F179" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G179" s="13" t="inlineStr"/>
+      <c r="H179" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I179" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J179" s="14" t="inlineStr"/>
+      <c r="K179" s="12" t="inlineStr">
+        <is>
+          <t>187_Slovenia_2026_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L179" s="13" t="inlineStr"/>
+      <c r="M179" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N179" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O179" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P179" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q179" s="16" t="inlineStr">
+        <is>
+          <t>This coin depicts a sower (a man sowing stars).
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="180" ht="15" customHeight="1">
-      <c r="A180" s="5" t="n"/>
-      <c r="B180" s="6" t="n"/>
-      <c r="C180" s="5" t="n"/>
-      <c r="D180" s="7" t="n"/>
-      <c r="E180" s="6" t="n"/>
-      <c r="F180" s="6" t="n"/>
-      <c r="G180" s="6" t="n"/>
-      <c r="H180" s="6" t="n"/>
-      <c r="I180" s="6" t="n"/>
-      <c r="J180" s="7" t="n"/>
-      <c r="K180" s="5" t="n"/>
-      <c r="L180" s="6" t="n"/>
-      <c r="M180" s="5" t="n"/>
-      <c r="N180" s="5" t="n"/>
-      <c r="O180" s="5" t="n"/>
-      <c r="P180" s="8" t="n"/>
-      <c r="Q180" s="9" t="n"/>
+      <c r="A180" s="12" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B180" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C180" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D180" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E180" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F180" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G180" s="13" t="inlineStr"/>
+      <c r="H180" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I180" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J180" s="14" t="inlineStr"/>
+      <c r="K180" s="12" t="inlineStr">
+        <is>
+          <t>188_Slovenia_2022_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L180" s="13" t="inlineStr"/>
+      <c r="M180" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N180" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O180" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P180" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q180" s="16" t="inlineStr">
+        <is>
+          <t>This coin features architect Jože Plečnik’s unrealised plan for the Slovenian Parliament, known as the ‘Cathedral of Freedom’.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="181" ht="15" customHeight="1">
-      <c r="A181" s="5" t="n"/>
-      <c r="B181" s="6" t="n"/>
-      <c r="C181" s="5" t="n"/>
-      <c r="D181" s="7" t="n"/>
-      <c r="E181" s="6" t="n"/>
-      <c r="F181" s="6" t="n"/>
-      <c r="G181" s="6" t="n"/>
-      <c r="H181" s="6" t="n"/>
-      <c r="I181" s="6" t="n"/>
-      <c r="J181" s="7" t="n"/>
-      <c r="K181" s="5" t="n"/>
-      <c r="L181" s="6" t="n"/>
-      <c r="M181" s="5" t="n"/>
-      <c r="N181" s="5" t="n"/>
-      <c r="O181" s="5" t="n"/>
-      <c r="P181" s="8" t="n"/>
-      <c r="Q181" s="9" t="n"/>
+      <c r="A181" s="12" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B181" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C181" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D181" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E181" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F181" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G181" s="13" t="inlineStr"/>
+      <c r="H181" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I181" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J181" s="14" t="inlineStr"/>
+      <c r="K181" s="12" t="inlineStr">
+        <is>
+          <t>189_Slovenia_2024_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L181" s="13" t="inlineStr"/>
+      <c r="M181" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N181" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O181" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P181" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q181" s="16" t="inlineStr">
+        <is>
+          <t>Lipizzaner horses form the central feature of this design.
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="182" ht="15" customHeight="1">
-      <c r="A182" s="5" t="n"/>
-      <c r="B182" s="6" t="n"/>
-      <c r="C182" s="5" t="n"/>
-      <c r="D182" s="7" t="n"/>
-      <c r="E182" s="6" t="n"/>
-      <c r="F182" s="6" t="n"/>
-      <c r="G182" s="6" t="n"/>
-      <c r="H182" s="6" t="n"/>
-      <c r="I182" s="6" t="n"/>
-      <c r="J182" s="7" t="n"/>
-      <c r="K182" s="5" t="n"/>
-      <c r="L182" s="6" t="n"/>
-      <c r="M182" s="5" t="n"/>
-      <c r="N182" s="5" t="n"/>
-      <c r="O182" s="5" t="n"/>
-      <c r="P182" s="8" t="n"/>
-      <c r="Q182" s="9" t="n"/>
+      <c r="A182" s="12" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B182" s="13" t="inlineStr">
+        <is>
+          <t>Slovenia</t>
+        </is>
+      </c>
+      <c r="C182" s="12" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
+      <c r="D182" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E182" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F182" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G182" s="13" t="inlineStr"/>
+      <c r="H182" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I182" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J182" s="14" t="inlineStr"/>
+      <c r="K182" s="12" t="inlineStr">
+        <is>
+          <t>190_Slovenia_2024_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L182" s="13" t="inlineStr"/>
+      <c r="M182" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N182" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O182" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P182" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Slovenia.</t>
+        </is>
+      </c>
+      <c r="Q182" s="16" t="inlineStr">
+        <is>
+          <t>The Triglav mountain is depicted on this coin (Slovenia’s highest mountain).
+The designs of the Slovenian euro coins were unanimously chosen in 2005 by the Bank of Slovenia and the Slovenian Ministry of Finance from the proposals submitted by five reputed Slovenian designers. They are the work of Miljenko Licul, Maja Licul...</t>
+        </is>
+      </c>
     </row>
     <row r="183" ht="15" customHeight="1">
-      <c r="A183" s="5" t="n"/>
-      <c r="B183" s="6" t="n"/>
-      <c r="C183" s="5" t="n"/>
-      <c r="D183" s="7" t="n"/>
-      <c r="E183" s="6" t="n"/>
-      <c r="F183" s="6" t="n"/>
-      <c r="G183" s="6" t="n"/>
-      <c r="H183" s="6" t="n"/>
-      <c r="I183" s="6" t="n"/>
-      <c r="J183" s="7" t="n"/>
-      <c r="K183" s="5" t="n"/>
-      <c r="L183" s="6" t="n"/>
-      <c r="M183" s="5" t="n"/>
-      <c r="N183" s="5" t="n"/>
-      <c r="O183" s="5" t="n"/>
-      <c r="P183" s="8" t="n"/>
-      <c r="Q183" s="9" t="n"/>
+      <c r="A183" s="12" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B183" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C183" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D183" s="14" t="inlineStr">
+        <is>
+          <t>2005</t>
+        </is>
+      </c>
+      <c r="E183" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F183" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G183" s="13" t="inlineStr"/>
+      <c r="H183" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I183" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J183" s="14" t="inlineStr"/>
+      <c r="K183" s="12" t="inlineStr">
+        <is>
+          <t>191_Spain_2005_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L183" s="13" t="inlineStr"/>
+      <c r="M183" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N183" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O183" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P183" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q183" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="184" ht="15" customHeight="1">
-      <c r="A184" s="5" t="n"/>
-      <c r="B184" s="6" t="n"/>
-      <c r="C184" s="5" t="n"/>
-      <c r="D184" s="7" t="n"/>
-      <c r="E184" s="6" t="n"/>
-      <c r="F184" s="6" t="n"/>
-      <c r="G184" s="6" t="n"/>
-      <c r="H184" s="6" t="n"/>
-      <c r="I184" s="6" t="n"/>
-      <c r="J184" s="7" t="n"/>
-      <c r="K184" s="5" t="n"/>
-      <c r="L184" s="6" t="n"/>
-      <c r="M184" s="5" t="n"/>
-      <c r="N184" s="5" t="n"/>
-      <c r="O184" s="5" t="n"/>
-      <c r="P184" s="8" t="n"/>
-      <c r="Q184" s="9" t="n"/>
+      <c r="A184" s="12" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B184" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C184" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D184" s="14" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E184" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F184" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G184" s="13" t="inlineStr"/>
+      <c r="H184" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I184" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J184" s="14" t="inlineStr"/>
+      <c r="K184" s="12" t="inlineStr">
+        <is>
+          <t>192_Spain_2017_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L184" s="13" t="inlineStr"/>
+      <c r="M184" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N184" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O184" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P184" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q184" s="16" t="inlineStr">
+        <is>
+          <t>Second series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="185" ht="15" customHeight="1">
-      <c r="A185" s="5" t="n"/>
-      <c r="B185" s="6" t="n"/>
-      <c r="C185" s="5" t="n"/>
-      <c r="D185" s="7" t="n"/>
-      <c r="E185" s="6" t="n"/>
-      <c r="F185" s="6" t="n"/>
-      <c r="G185" s="6" t="n"/>
-      <c r="H185" s="6" t="n"/>
-      <c r="I185" s="6" t="n"/>
-      <c r="J185" s="7" t="n"/>
-      <c r="K185" s="5" t="n"/>
-      <c r="L185" s="6" t="n"/>
-      <c r="M185" s="5" t="n"/>
-      <c r="N185" s="5" t="n"/>
-      <c r="O185" s="5" t="n"/>
-      <c r="P185" s="8" t="n"/>
-      <c r="Q185" s="9" t="n"/>
+      <c r="A185" s="12" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B185" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C185" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D185" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E185" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F185" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G185" s="13" t="inlineStr"/>
+      <c r="H185" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I185" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J185" s="14" t="inlineStr"/>
+      <c r="K185" s="12" t="inlineStr">
+        <is>
+          <t>193_Spain_2006_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L185" s="13" t="inlineStr"/>
+      <c r="M185" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N185" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O185" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P185" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q185" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="186" ht="15" customHeight="1">
-      <c r="A186" s="5" t="n"/>
-      <c r="B186" s="6" t="n"/>
-      <c r="C186" s="5" t="n"/>
-      <c r="D186" s="7" t="n"/>
-      <c r="E186" s="6" t="n"/>
-      <c r="F186" s="6" t="n"/>
-      <c r="G186" s="6" t="n"/>
-      <c r="H186" s="6" t="n"/>
-      <c r="I186" s="6" t="n"/>
-      <c r="J186" s="7" t="n"/>
-      <c r="K186" s="5" t="n"/>
-      <c r="L186" s="6" t="n"/>
-      <c r="M186" s="5" t="n"/>
-      <c r="N186" s="5" t="n"/>
-      <c r="O186" s="5" t="n"/>
-      <c r="P186" s="8" t="n"/>
-      <c r="Q186" s="9" t="n"/>
+      <c r="A186" s="12" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B186" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C186" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D186" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E186" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F186" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G186" s="13" t="inlineStr"/>
+      <c r="H186" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I186" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J186" s="14" t="inlineStr"/>
+      <c r="K186" s="12" t="inlineStr">
+        <is>
+          <t>194_Spain_2018_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L186" s="13" t="inlineStr"/>
+      <c r="M186" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N186" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O186" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P186" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q186" s="16" t="inlineStr">
+        <is>
+          <t>Second series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="187" ht="15" customHeight="1">
-      <c r="A187" s="5" t="n"/>
-      <c r="B187" s="6" t="n"/>
-      <c r="C187" s="5" t="n"/>
-      <c r="D187" s="7" t="n"/>
-      <c r="E187" s="6" t="n"/>
-      <c r="F187" s="6" t="n"/>
-      <c r="G187" s="6" t="n"/>
-      <c r="H187" s="6" t="n"/>
-      <c r="I187" s="6" t="n"/>
-      <c r="J187" s="7" t="n"/>
-      <c r="K187" s="5" t="n"/>
-      <c r="L187" s="6" t="n"/>
-      <c r="M187" s="5" t="n"/>
-      <c r="N187" s="5" t="n"/>
-      <c r="O187" s="5" t="n"/>
-      <c r="P187" s="8" t="n"/>
-      <c r="Q187" s="9" t="n"/>
+      <c r="A187" s="12" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B187" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C187" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D187" s="14" t="inlineStr">
+        <is>
+          <t>2003</t>
+        </is>
+      </c>
+      <c r="E187" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F187" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G187" s="13" t="inlineStr"/>
+      <c r="H187" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I187" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J187" s="14" t="inlineStr"/>
+      <c r="K187" s="12" t="inlineStr">
+        <is>
+          <t>195_Spain_2003_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L187" s="13" t="inlineStr"/>
+      <c r="M187" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N187" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O187" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P187" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q187" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="188" ht="15" customHeight="1">
-      <c r="A188" s="5" t="n"/>
-      <c r="B188" s="6" t="n"/>
-      <c r="C188" s="5" t="n"/>
-      <c r="D188" s="7" t="n"/>
-      <c r="E188" s="6" t="n"/>
-      <c r="F188" s="6" t="n"/>
-      <c r="G188" s="6" t="n"/>
-      <c r="H188" s="6" t="n"/>
-      <c r="I188" s="6" t="n"/>
-      <c r="J188" s="7" t="n"/>
-      <c r="K188" s="5" t="n"/>
-      <c r="L188" s="6" t="n"/>
-      <c r="M188" s="5" t="n"/>
-      <c r="N188" s="5" t="n"/>
-      <c r="O188" s="5" t="n"/>
-      <c r="P188" s="8" t="n"/>
-      <c r="Q188" s="9" t="n"/>
+      <c r="A188" s="12" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B188" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C188" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D188" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E188" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F188" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G188" s="13" t="inlineStr"/>
+      <c r="H188" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I188" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J188" s="14" t="inlineStr"/>
+      <c r="K188" s="12" t="inlineStr">
+        <is>
+          <t>196_Spain_2018_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L188" s="13" t="inlineStr"/>
+      <c r="M188" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N188" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O188" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P188" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q188" s="16" t="inlineStr">
+        <is>
+          <t>Second  series. 
+1, 2 and 5-cent coins: the cathedral of Santiago de Compostela, a jewel of Spanish Romanesque architecture and one of the most famous pilgrimage destinations in the world, is pictured on these coins. They show the monumental facade of the Obradoiro, a splendid example of Spanish baroque construction, started in 1667 by Jose del Toro and Domingo de Andrade. It was finished in the 18th century by Fernando Casas y Novoa.
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="5" t="n"/>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="5" t="n"/>
-      <c r="D189" s="7" t="n"/>
-      <c r="E189" s="6" t="n"/>
-      <c r="F189" s="6" t="n"/>
-      <c r="G189" s="6" t="n"/>
-      <c r="H189" s="6" t="n"/>
-      <c r="I189" s="6" t="n"/>
-      <c r="J189" s="7" t="n"/>
-      <c r="K189" s="5" t="n"/>
-      <c r="L189" s="6" t="n"/>
-      <c r="M189" s="5" t="n"/>
-      <c r="N189" s="5" t="n"/>
-      <c r="O189" s="5" t="n"/>
-      <c r="P189" s="8" t="n"/>
-      <c r="Q189" s="9" t="n"/>
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B189" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D189" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E189" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F189" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G189" s="13" t="inlineStr"/>
+      <c r="H189" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J189" s="14" t="inlineStr"/>
+      <c r="K189" s="12" t="inlineStr">
+        <is>
+          <t>197_Spain_1999_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L189" s="13" t="inlineStr"/>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N189" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O189" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P189" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q189" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="5" t="n"/>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="5" t="n"/>
-      <c r="D190" s="7" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="6" t="n"/>
-      <c r="G190" s="6" t="n"/>
-      <c r="H190" s="6" t="n"/>
-      <c r="I190" s="6" t="n"/>
-      <c r="J190" s="7" t="n"/>
-      <c r="K190" s="5" t="n"/>
-      <c r="L190" s="6" t="n"/>
-      <c r="M190" s="5" t="n"/>
-      <c r="N190" s="5" t="n"/>
-      <c r="O190" s="5" t="n"/>
-      <c r="P190" s="8" t="n"/>
-      <c r="Q190" s="9" t="n"/>
+      <c r="A190" s="12" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D190" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E190" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F190" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G190" s="13" t="inlineStr"/>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J190" s="14" t="inlineStr"/>
+      <c r="K190" s="12" t="inlineStr">
+        <is>
+          <t>198_Spain_2000_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L190" s="13" t="inlineStr"/>
+      <c r="M190" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N190" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O190" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P190" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q190" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="5" t="n"/>
-      <c r="B191" s="6" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="7" t="n"/>
-      <c r="E191" s="6" t="n"/>
-      <c r="F191" s="6" t="n"/>
-      <c r="G191" s="6" t="n"/>
-      <c r="H191" s="6" t="n"/>
-      <c r="I191" s="6" t="n"/>
-      <c r="J191" s="7" t="n"/>
-      <c r="K191" s="5" t="n"/>
-      <c r="L191" s="6" t="n"/>
-      <c r="M191" s="5" t="n"/>
-      <c r="N191" s="5" t="n"/>
-      <c r="O191" s="5" t="n"/>
-      <c r="P191" s="8" t="n"/>
-      <c r="Q191" s="9" t="n"/>
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>2000</t>
+        </is>
+      </c>
+      <c r="E191" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F191" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G191" s="13" t="inlineStr"/>
+      <c r="H191" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J191" s="14" t="inlineStr"/>
+      <c r="K191" s="12" t="inlineStr">
+        <is>
+          <t>199_Spain_2000_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L191" s="13" t="inlineStr"/>
+      <c r="M191" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N191" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O191" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P191" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q191" s="16" t="inlineStr">
+        <is>
+          <t>First series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="5" t="n"/>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="5" t="n"/>
-      <c r="D192" s="7" t="n"/>
-      <c r="E192" s="6" t="n"/>
-      <c r="F192" s="6" t="n"/>
-      <c r="G192" s="6" t="n"/>
-      <c r="H192" s="6" t="n"/>
-      <c r="I192" s="6" t="n"/>
-      <c r="J192" s="7" t="n"/>
-      <c r="K192" s="5" t="n"/>
-      <c r="L192" s="6" t="n"/>
-      <c r="M192" s="5" t="n"/>
-      <c r="N192" s="5" t="n"/>
-      <c r="O192" s="5" t="n"/>
-      <c r="P192" s="8" t="n"/>
-      <c r="Q192" s="9" t="n"/>
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E192" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr"/>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="inlineStr"/>
+      <c r="K192" s="12" t="inlineStr">
+        <is>
+          <t>200_Spain_2021_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L192" s="13" t="inlineStr"/>
+      <c r="M192" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N192" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O192" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P192" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q192" s="16" t="inlineStr">
+        <is>
+          <t>Second series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="6" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="7" t="n"/>
-      <c r="E193" s="6" t="n"/>
-      <c r="F193" s="6" t="n"/>
-      <c r="G193" s="6" t="n"/>
-      <c r="H193" s="6" t="n"/>
-      <c r="I193" s="6" t="n"/>
-      <c r="J193" s="7" t="n"/>
-      <c r="K193" s="5" t="n"/>
-      <c r="L193" s="6" t="n"/>
-      <c r="M193" s="5" t="n"/>
-      <c r="N193" s="5" t="n"/>
-      <c r="O193" s="5" t="n"/>
-      <c r="P193" s="8" t="n"/>
-      <c r="Q193" s="9" t="n"/>
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="B193" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E193" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F193" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G193" s="13" t="inlineStr"/>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J193" s="14" t="inlineStr"/>
+      <c r="K193" s="12" t="inlineStr">
+        <is>
+          <t>201_Spain_2024_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L193" s="13" t="inlineStr"/>
+      <c r="M193" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N193" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O193" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P193" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q193" s="16" t="inlineStr">
+        <is>
+          <t>Second series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="5" t="n"/>
-      <c r="B194" s="6" t="n"/>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="7" t="n"/>
-      <c r="E194" s="6" t="n"/>
-      <c r="F194" s="6" t="n"/>
-      <c r="G194" s="6" t="n"/>
-      <c r="H194" s="6" t="n"/>
-      <c r="I194" s="6" t="n"/>
-      <c r="J194" s="7" t="n"/>
-      <c r="K194" s="5" t="n"/>
-      <c r="L194" s="6" t="n"/>
-      <c r="M194" s="5" t="n"/>
-      <c r="N194" s="5" t="n"/>
-      <c r="O194" s="5" t="n"/>
-      <c r="P194" s="8" t="n"/>
-      <c r="Q194" s="9" t="n"/>
+      <c r="A194" s="12" t="inlineStr">
+        <is>
+          <t>202</t>
+        </is>
+      </c>
+      <c r="B194" s="13" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>ES</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E194" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G194" s="13" t="inlineStr"/>
+      <c r="H194" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="inlineStr"/>
+      <c r="K194" s="12" t="inlineStr">
+        <is>
+          <t>202_Spain_2018_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L194" s="13" t="inlineStr"/>
+      <c r="M194" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N194" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O194" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P194" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Spain.</t>
+        </is>
+      </c>
+      <c r="Q194" s="16" t="inlineStr">
+        <is>
+          <t>Second series. 
+10, 20 and 50-cent coins: Miguel de Cervantes, the father of Spanish literature, is shown on these coins, reflecting "the universality of the man and his work".
+Spain’s coins feature three designs with effigies of the King, Miguel de Cervantes and the cathedral of Santiago de Compostela.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
       <c r="A195" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -724,8 +724,10 @@
           <t>BG</t>
         </is>
       </c>
-      <c r="D4" s="14" t="n">
-        <v>2026</v>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="E4" s="13" t="inlineStr">
         <is>
@@ -737,11 +739,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G4" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G4" s="13" t="inlineStr"/>
       <c r="H4" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -755,7 +753,7 @@
       <c r="J4" s="14" t="inlineStr"/>
       <c r="K4" s="12" t="inlineStr">
         <is>
-          <t>005_Bulgaria_2026_2Euro_Regular.jpeg</t>
+          <t>005_Bulgaria_2026_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L4" s="13" t="inlineStr"/>
@@ -779,7 +777,13 @@
           <t>Regular 2 € circulation coin of Bulgaria.</t>
         </is>
       </c>
-      <c r="Q4" s="16" t="inlineStr"/>
+      <c r="Q4" s="16" t="inlineStr">
+        <is>
+          <t>Bulgaria has chosen three designs for their national sides of the euro coins. All the coins also depict the 12 stars of the European flag.
+The €2 coin features a portrait of Saint Paisius of Hilendar, a key figure of the Bulgarian national revival and author of Istoriya Slavyanobolgarskaya (Slavo-Bulgarian History). The design includes the year of issuance, the inscription “БЪЛГАРИЯ” (the country’s name in Bulgarian) and the word “ЕВРО” (“EURO”) in Cyrillic script.
+The inscription “БОЖЕ ПАЗИ БЪЛГАРИЯ” (“GOD PROTECT BULGARIA”) is written twice, both normally and in reverse, around the edge of the coin.</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="15" customHeight="1">
       <c r="A5" s="12" t="inlineStr">
@@ -875,8 +879,10 @@
           <t>PT</t>
         </is>
       </c>
-      <c r="D6" s="14" t="n">
-        <v>2002</v>
+      <c r="D6" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
         <is>
@@ -888,11 +894,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G6" s="13" t="inlineStr"/>
       <c r="H6" s="13" t="inlineStr">
         <is>
           <t>VF</t>
@@ -906,7 +908,7 @@
       <c r="J6" s="14" t="inlineStr"/>
       <c r="K6" s="12" t="inlineStr">
         <is>
-          <t>007_Portugal_2002_2Euro_Regular.jpeg</t>
+          <t>007_Portugal_2002_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L6" s="13" t="inlineStr"/>
@@ -932,7 +934,8 @@
       </c>
       <c r="Q6" s="16" t="inlineStr">
         <is>
-          <t>€2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144. Edge lettering of the €2 coin: five coats of arms and seven castles, all equally spaced.</t>
+          <t>€2 coins: the country's castles and coats of arms are set amid the European stars. This symbolises dialogue, the exchange of values and the dynamics of the building of Europe. The centrepiece is the royal seal of 1144. Edge lettering of the €2 coin: five coats of arms and seven castles, all equally spaced.
+The edge lettering on the €2 coin consists of five coats of arms and seven castles equally spaced.</t>
         </is>
       </c>
     </row>
@@ -952,8 +955,10 @@
           <t>SM</t>
         </is>
       </c>
-      <c r="D7" s="14" t="n">
-        <v>2021</v>
+      <c r="D7" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
       </c>
       <c r="E7" s="13" t="inlineStr">
         <is>
@@ -965,11 +970,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G7" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G7" s="13" t="inlineStr"/>
       <c r="H7" s="13" t="inlineStr">
         <is>
           <t>AU</t>
@@ -983,7 +984,7 @@
       <c r="J7" s="14" t="inlineStr"/>
       <c r="K7" s="12" t="inlineStr">
         <is>
-          <t>008_San-Marino_2021_2Euro_Regular.jpeg</t>
+          <t>008_San-Marino_2021_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L7" s="13" t="inlineStr"/>
@@ -1009,7 +1010,8 @@
       </c>
       <c r="Q7" s="16" t="inlineStr">
         <is>
-          <t>Second series: The portrait of Saint Marino, detail of a painting by Giovan Battista Urbinelli, is shown on this coin.</t>
+          <t>Second series
+The  portrait of Saint Marino, detail of a painting by Giovan Battista Urbinelli, the date 2017, the mintmark of the Italian Mint ‘R’, the legend ‘San Marino’, AL initials of the artist, arched 12 stars; The edge-lettering of the 2-euro coin is: 2 *, repeated six times, alternately upright and inverted.</t>
         </is>
       </c>
     </row>
@@ -1029,8 +1031,10 @@
           <t>SK</t>
         </is>
       </c>
-      <c r="D8" s="14" t="n">
-        <v>2026</v>
+      <c r="D8" s="14" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
@@ -1042,11 +1046,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G8" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G8" s="13" t="inlineStr"/>
       <c r="H8" s="13" t="inlineStr">
         <is>
           <t>AU</t>
@@ -1060,7 +1060,7 @@
       <c r="J8" s="14" t="inlineStr"/>
       <c r="K8" s="12" t="inlineStr">
         <is>
-          <t>009_Slovakia_2026_2Euro_Regular.jpeg</t>
+          <t>009_Slovakia_2026_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L8" s="13" t="inlineStr"/>
@@ -1086,7 +1086,7 @@
       </c>
       <c r="Q8" s="16" t="inlineStr">
         <is>
-          <t>€2 coins depict a double cross on three hills, as featured in the national emblem of Slovakia.</t>
+          <t>€2 coins depict a double cross on three hills (the Tatra, the Mátra and the Fatra) which are part of the Slovak coat of arms and have been a symbol of the Slovak nation since the 16th century. The motif appears against a background of stylized rocks, expressing the stability and strength of the state. It was designed by sculptor Ivan Rehak.</t>
         </is>
       </c>
     </row>
@@ -14640,308 +14640,1227 @@
       </c>
     </row>
     <row r="189" ht="15" customHeight="1">
-      <c r="A189" s="5" t="n"/>
-      <c r="B189" s="6" t="n"/>
-      <c r="C189" s="5" t="n"/>
-      <c r="D189" s="7" t="n"/>
-      <c r="E189" s="6" t="n"/>
-      <c r="F189" s="6" t="n"/>
-      <c r="G189" s="6" t="n"/>
-      <c r="H189" s="6" t="n"/>
-      <c r="I189" s="6" t="n"/>
-      <c r="J189" s="7" t="n"/>
-      <c r="K189" s="5" t="n"/>
-      <c r="L189" s="6" t="n"/>
-      <c r="M189" s="5" t="n"/>
-      <c r="N189" s="5" t="n"/>
-      <c r="O189" s="5" t="n"/>
-      <c r="P189" s="8" t="n"/>
-      <c r="Q189" s="9" t="n"/>
+      <c r="A189" s="12" t="inlineStr">
+        <is>
+          <t>204</t>
+        </is>
+      </c>
+      <c r="B189" s="13" t="inlineStr">
+        <is>
+          <t>Austria</t>
+        </is>
+      </c>
+      <c r="C189" s="12" t="inlineStr">
+        <is>
+          <t>AT</t>
+        </is>
+      </c>
+      <c r="D189" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E189" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F189" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G189" s="13" t="inlineStr"/>
+      <c r="H189" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I189" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J189" s="14" t="inlineStr"/>
+      <c r="K189" s="12" t="inlineStr">
+        <is>
+          <t>204_Austria_2023_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L189" s="13" t="inlineStr"/>
+      <c r="M189" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N189" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O189" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P189" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Austria.</t>
+        </is>
+      </c>
+      <c r="Q189" s="16" t="inlineStr">
+        <is>
+          <t>The €2 coin shows the portrait of the radical pacifist Bertha von Suttner, awarded the Nobel Peace Prize in 1905. The edge lettering on the €2 coin is ‘2 EURO ***’, repeated four times, alternately upright and inverted.
+Austria chose to produce a series of coins illustrating flowers, architecture and famous people from its history. The designs were chosen by a national panel and public opinion poll. Austrian artist Josef Kaiser created the designs. This coin shows the secession building in Vienna, illustrating the birth of art nouveau in Austria. The building symbolises the birth of a new age and represents a bridge to a new monetary era.</t>
+        </is>
+      </c>
     </row>
     <row r="190" ht="15" customHeight="1">
-      <c r="A190" s="5" t="n"/>
-      <c r="B190" s="6" t="n"/>
-      <c r="C190" s="5" t="n"/>
-      <c r="D190" s="7" t="n"/>
-      <c r="E190" s="6" t="n"/>
-      <c r="F190" s="6" t="n"/>
-      <c r="G190" s="6" t="n"/>
-      <c r="H190" s="6" t="n"/>
-      <c r="I190" s="6" t="n"/>
-      <c r="J190" s="7" t="n"/>
-      <c r="K190" s="5" t="n"/>
-      <c r="L190" s="6" t="n"/>
-      <c r="M190" s="5" t="n"/>
-      <c r="N190" s="5" t="n"/>
-      <c r="O190" s="5" t="n"/>
-      <c r="P190" s="8" t="n"/>
-      <c r="Q190" s="9" t="n"/>
+      <c r="A190" s="12" t="inlineStr">
+        <is>
+          <t>205</t>
+        </is>
+      </c>
+      <c r="B190" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C190" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D190" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E190" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F190" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G190" s="13" t="inlineStr"/>
+      <c r="H190" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I190" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J190" s="14" t="inlineStr"/>
+      <c r="K190" s="12" t="inlineStr">
+        <is>
+          <t>205_Croatia_2023_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L190" s="13" t="inlineStr"/>
+      <c r="M190" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N190" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O190" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P190" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q190" s="16" t="inlineStr">
+        <is>
+          <t>Croatia has chosen four designs for their national sides of the euro coins, all featuring the distinctive Croatian chequerboard pattern in the background. All the coins also depict the 12 stars of the European flag.
+The €2 coin features a map of Croatia on a chequerboard background. The design, by Ivan Šivak, includes the year of issuance and the inscription “HRVATSKA”, the country’s name in Croatian.
+Edge lettering of the €2 coin: “O LIJEPA O DRAGA O SLATKA SLOBODO” (“Oh beautiful, oh dear, oh sweet freedom”), a line from Ivan Gundulić’s famous play, Dubravka.</t>
+        </is>
+      </c>
     </row>
     <row r="191" ht="15" customHeight="1">
-      <c r="A191" s="5" t="n"/>
-      <c r="B191" s="6" t="n"/>
-      <c r="C191" s="5" t="n"/>
-      <c r="D191" s="7" t="n"/>
-      <c r="E191" s="6" t="n"/>
-      <c r="F191" s="6" t="n"/>
-      <c r="G191" s="6" t="n"/>
-      <c r="H191" s="6" t="n"/>
-      <c r="I191" s="6" t="n"/>
-      <c r="J191" s="7" t="n"/>
-      <c r="K191" s="5" t="n"/>
-      <c r="L191" s="6" t="n"/>
-      <c r="M191" s="5" t="n"/>
-      <c r="N191" s="5" t="n"/>
-      <c r="O191" s="5" t="n"/>
-      <c r="P191" s="8" t="n"/>
-      <c r="Q191" s="9" t="n"/>
+      <c r="A191" s="12" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="B191" s="13" t="inlineStr">
+        <is>
+          <t>Croatia</t>
+        </is>
+      </c>
+      <c r="C191" s="12" t="inlineStr">
+        <is>
+          <t>HR</t>
+        </is>
+      </c>
+      <c r="D191" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E191" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F191" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G191" s="13" t="inlineStr"/>
+      <c r="H191" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I191" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J191" s="14" t="inlineStr"/>
+      <c r="K191" s="12" t="inlineStr">
+        <is>
+          <t>206_Croatia_2018_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L191" s="13" t="inlineStr"/>
+      <c r="M191" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N191" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O191" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P191" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Croatia.</t>
+        </is>
+      </c>
+      <c r="Q191" s="16" t="inlineStr">
+        <is>
+          <t>The €1 and €2 coins depict a cruciform idol from the Chalcolithic period (3000 BC). This characteristic example of the island's prehistoric art reflects Cyprus's place at the heart of civilisation and antiquity.</t>
+        </is>
+      </c>
     </row>
     <row r="192" ht="15" customHeight="1">
-      <c r="A192" s="5" t="n"/>
-      <c r="B192" s="6" t="n"/>
-      <c r="C192" s="5" t="n"/>
-      <c r="D192" s="7" t="n"/>
-      <c r="E192" s="6" t="n"/>
-      <c r="F192" s="6" t="n"/>
-      <c r="G192" s="6" t="n"/>
-      <c r="H192" s="6" t="n"/>
-      <c r="I192" s="6" t="n"/>
-      <c r="J192" s="7" t="n"/>
-      <c r="K192" s="5" t="n"/>
-      <c r="L192" s="6" t="n"/>
-      <c r="M192" s="5" t="n"/>
-      <c r="N192" s="5" t="n"/>
-      <c r="O192" s="5" t="n"/>
-      <c r="P192" s="8" t="n"/>
-      <c r="Q192" s="9" t="n"/>
+      <c r="A192" s="12" t="inlineStr">
+        <is>
+          <t>207</t>
+        </is>
+      </c>
+      <c r="B192" s="13" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="C192" s="12" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="D192" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E192" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F192" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G192" s="13" t="inlineStr"/>
+      <c r="H192" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I192" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J192" s="14" t="inlineStr"/>
+      <c r="K192" s="12" t="inlineStr">
+        <is>
+          <t>207_Estonia_2011_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L192" s="13" t="inlineStr"/>
+      <c r="M192" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N192" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O192" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P192" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Estonia.</t>
+        </is>
+      </c>
+      <c r="Q192" s="16" t="inlineStr">
+        <is>
+          <t>The design for the national side of Estonia’s coins is the same for all denominations. It features a geographical image of Estonia and the word "Eesti", which means "Estonia".
+The edge lettering of the 2 euro coin is "EESTI"", repeated two times upright and inverted.
+The Estonian euro coins have been in circulation as from 1 January 2011.</t>
+        </is>
+      </c>
     </row>
     <row r="193" ht="15" customHeight="1">
-      <c r="A193" s="5" t="n"/>
-      <c r="B193" s="6" t="n"/>
-      <c r="C193" s="5" t="n"/>
-      <c r="D193" s="7" t="n"/>
-      <c r="E193" s="6" t="n"/>
-      <c r="F193" s="6" t="n"/>
-      <c r="G193" s="6" t="n"/>
-      <c r="H193" s="6" t="n"/>
-      <c r="I193" s="6" t="n"/>
-      <c r="J193" s="7" t="n"/>
-      <c r="K193" s="5" t="n"/>
-      <c r="L193" s="6" t="n"/>
-      <c r="M193" s="5" t="n"/>
-      <c r="N193" s="5" t="n"/>
-      <c r="O193" s="5" t="n"/>
-      <c r="P193" s="8" t="n"/>
-      <c r="Q193" s="9" t="n"/>
+      <c r="A193" s="12" t="inlineStr">
+        <is>
+          <t>208</t>
+        </is>
+      </c>
+      <c r="B193" s="13" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C193" s="12" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D193" s="14" t="inlineStr">
+        <is>
+          <t>2018</t>
+        </is>
+      </c>
+      <c r="E193" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F193" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G193" s="13" t="inlineStr"/>
+      <c r="H193" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I193" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J193" s="14" t="inlineStr"/>
+      <c r="K193" s="12" t="inlineStr">
+        <is>
+          <t>208_Finland_2018_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L193" s="13" t="inlineStr"/>
+      <c r="M193" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N193" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O193" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P193" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Finland.</t>
+        </is>
+      </c>
+      <c r="Q193" s="16" t="inlineStr">
+        <is>
+          <t>The motif on this coin comprises cloudberries and cloudberry flowers in a design by Raimo Heino. Edge lettering of the €2 coin: SUOMI FINLAND ***, where the * represents a lion's head.</t>
+        </is>
+      </c>
     </row>
     <row r="194" ht="15" customHeight="1">
-      <c r="A194" s="5" t="n"/>
-      <c r="B194" s="6" t="n"/>
-      <c r="C194" s="5" t="n"/>
-      <c r="D194" s="7" t="n"/>
-      <c r="E194" s="6" t="n"/>
-      <c r="F194" s="6" t="n"/>
-      <c r="G194" s="6" t="n"/>
-      <c r="H194" s="6" t="n"/>
-      <c r="I194" s="6" t="n"/>
-      <c r="J194" s="7" t="n"/>
-      <c r="K194" s="5" t="n"/>
-      <c r="L194" s="6" t="n"/>
-      <c r="M194" s="5" t="n"/>
-      <c r="N194" s="5" t="n"/>
-      <c r="O194" s="5" t="n"/>
-      <c r="P194" s="8" t="n"/>
-      <c r="Q194" s="9" t="n"/>
+      <c r="A194" s="12" t="inlineStr">
+        <is>
+          <t>209</t>
+        </is>
+      </c>
+      <c r="B194" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C194" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D194" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E194" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F194" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G194" s="13" t="inlineStr"/>
+      <c r="H194" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I194" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J194" s="14" t="inlineStr"/>
+      <c r="K194" s="12" t="inlineStr">
+        <is>
+          <t>209_France_2022_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L194" s="13" t="inlineStr"/>
+      <c r="M194" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N194" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O194" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P194" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q194" s="16" t="inlineStr">
+        <is>
+          <t>Second series.
+As of 2022, France issued 1 and 2 euro coins with new designs. The modified designs are in line with the symbolism of the previous designs of the 1 and 2 euro coins: the tree of life. They represent a mixture of the two species that make up the emblem of the Republic: the oak, image of strength and solidity, and the olive tree, symbol of peace. The tree and the motto stand within a hexagon.
+Edge lettering of the €2 coin: 2**, repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="195" ht="15" customHeight="1">
-      <c r="A195" s="5" t="n"/>
-      <c r="B195" s="6" t="n"/>
-      <c r="C195" s="5" t="n"/>
-      <c r="D195" s="7" t="n"/>
-      <c r="E195" s="6" t="n"/>
-      <c r="F195" s="6" t="n"/>
-      <c r="G195" s="6" t="n"/>
-      <c r="H195" s="6" t="n"/>
-      <c r="I195" s="6" t="n"/>
-      <c r="J195" s="7" t="n"/>
-      <c r="K195" s="5" t="n"/>
-      <c r="L195" s="6" t="n"/>
-      <c r="M195" s="5" t="n"/>
-      <c r="N195" s="5" t="n"/>
-      <c r="O195" s="5" t="n"/>
-      <c r="P195" s="8" t="n"/>
-      <c r="Q195" s="9" t="n"/>
+      <c r="A195" s="12" t="inlineStr">
+        <is>
+          <t>210</t>
+        </is>
+      </c>
+      <c r="B195" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C195" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D195" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E195" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F195" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G195" s="13" t="inlineStr"/>
+      <c r="H195" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I195" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J195" s="14" t="inlineStr"/>
+      <c r="K195" s="12" t="inlineStr">
+        <is>
+          <t>210_France_2021_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L195" s="13" t="inlineStr"/>
+      <c r="M195" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N195" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O195" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P195" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q195" s="16" t="inlineStr">
+        <is>
+          <t>First series
+On the €1 and €2 coins, a tree symbolising life, growth and stability is framed by a hexagon – France – and surrounded by the motto of the French Republic: ‘Liberté, Égalité, Fraternité’ (Freedom, Equality, Fraternity). The edge lettering on the €2 coin is ‘2**’ repeated six times, alternately upright and inverted.
+Edge lettering of the €2 coin: 2**, repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="196" ht="15" customHeight="1">
-      <c r="A196" s="5" t="n"/>
-      <c r="B196" s="6" t="n"/>
-      <c r="C196" s="5" t="n"/>
-      <c r="D196" s="7" t="n"/>
-      <c r="E196" s="6" t="n"/>
-      <c r="F196" s="6" t="n"/>
-      <c r="G196" s="6" t="n"/>
-      <c r="H196" s="6" t="n"/>
-      <c r="I196" s="6" t="n"/>
-      <c r="J196" s="7" t="n"/>
-      <c r="K196" s="5" t="n"/>
-      <c r="L196" s="6" t="n"/>
-      <c r="M196" s="5" t="n"/>
-      <c r="N196" s="5" t="n"/>
-      <c r="O196" s="5" t="n"/>
-      <c r="P196" s="8" t="n"/>
-      <c r="Q196" s="9" t="n"/>
+      <c r="A196" s="12" t="inlineStr">
+        <is>
+          <t>211</t>
+        </is>
+      </c>
+      <c r="B196" s="13" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="C196" s="12" t="inlineStr">
+        <is>
+          <t>DE</t>
+        </is>
+      </c>
+      <c r="D196" s="14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E196" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F196" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G196" s="13" t="inlineStr"/>
+      <c r="H196" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I196" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J196" s="14" t="inlineStr"/>
+      <c r="K196" s="12" t="inlineStr">
+        <is>
+          <t>211_Germany_2025_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L196" s="13" t="inlineStr"/>
+      <c r="M196" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N196" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O196" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P196" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Germany.</t>
+        </is>
+      </c>
+      <c r="Q196" s="16" t="inlineStr">
+        <is>
+          <t>German officials and experts in numismatics chose three different designs for their euro coins. 10, 20 and 50-cent coins: the Brandenburg Gate, a symbol of the division of Germany and its subsequent reunification, is the motif used on these coins. The perspective of the design, by Reinhard Heinsdorff, emphasises the opening of the gate, stressing the unification of Germany and Europe.
+The €1 and €2 coins show the emblem of the federal eagle, the symbol of German sovereignty. They were designed by Heinz and Snechana Russewa-Hoyer. The edge lettering on the €2 coin consists of the words 'EINIGKEIT UND RECHT UND FREIHEIT' (unity, justice and freedom) and the design of the federal eagle.</t>
+        </is>
+      </c>
     </row>
     <row r="197" ht="15" customHeight="1">
-      <c r="A197" s="5" t="n"/>
-      <c r="B197" s="6" t="n"/>
-      <c r="C197" s="5" t="n"/>
-      <c r="D197" s="7" t="n"/>
-      <c r="E197" s="6" t="n"/>
-      <c r="F197" s="6" t="n"/>
-      <c r="G197" s="6" t="n"/>
-      <c r="H197" s="6" t="n"/>
-      <c r="I197" s="6" t="n"/>
-      <c r="J197" s="7" t="n"/>
-      <c r="K197" s="5" t="n"/>
-      <c r="L197" s="6" t="n"/>
-      <c r="M197" s="5" t="n"/>
-      <c r="N197" s="5" t="n"/>
-      <c r="O197" s="5" t="n"/>
-      <c r="P197" s="8" t="n"/>
-      <c r="Q197" s="9" t="n"/>
+      <c r="A197" s="12" t="inlineStr">
+        <is>
+          <t>212</t>
+        </is>
+      </c>
+      <c r="B197" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C197" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D197" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E197" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F197" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G197" s="13" t="inlineStr"/>
+      <c r="H197" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I197" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J197" s="14" t="inlineStr"/>
+      <c r="K197" s="12" t="inlineStr">
+        <is>
+          <t>212_Greece_2002_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L197" s="13" t="inlineStr"/>
+      <c r="M197" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N197" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O197" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P197" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q197" s="16" t="inlineStr">
+        <is>
+          <t>This coin depicts a scene from a mosaic in Sparta (third century AD), showing Europa being abducted by Zeus, who has taken the form of a bull. Europa is a figure from Greek mythology after whom Europe was named. Edge lettering of the €2 coin: EΛΛHNIKH ΔHMOKPATIA * (Hellenic Republic).
+The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.</t>
+        </is>
+      </c>
     </row>
     <row r="198" ht="15" customHeight="1">
-      <c r="A198" s="5" t="n"/>
-      <c r="B198" s="6" t="n"/>
-      <c r="C198" s="5" t="n"/>
-      <c r="D198" s="7" t="n"/>
-      <c r="E198" s="6" t="n"/>
-      <c r="F198" s="6" t="n"/>
-      <c r="G198" s="6" t="n"/>
-      <c r="H198" s="6" t="n"/>
-      <c r="I198" s="6" t="n"/>
-      <c r="J198" s="7" t="n"/>
-      <c r="K198" s="5" t="n"/>
-      <c r="L198" s="6" t="n"/>
-      <c r="M198" s="5" t="n"/>
-      <c r="N198" s="5" t="n"/>
-      <c r="O198" s="5" t="n"/>
-      <c r="P198" s="8" t="n"/>
-      <c r="Q198" s="9" t="n"/>
+      <c r="A198" s="12" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="B198" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C198" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D198" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E198" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F198" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G198" s="13" t="inlineStr"/>
+      <c r="H198" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I198" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J198" s="14" t="inlineStr"/>
+      <c r="K198" s="12" t="inlineStr">
+        <is>
+          <t>213_Italy_2021_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L198" s="13" t="inlineStr"/>
+      <c r="M198" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N198" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O198" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P198" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q198" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+Depicted on this coin is a portrait drawn by Raphaël of Dante Alighieri, housed in the Pope Julius II Wing of the Vatican City Palace. Edge lettering of the €2 coin: 2*, repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="199" ht="15" customHeight="1">
-      <c r="A199" s="5" t="n"/>
-      <c r="B199" s="6" t="n"/>
-      <c r="C199" s="5" t="n"/>
-      <c r="D199" s="7" t="n"/>
-      <c r="E199" s="6" t="n"/>
-      <c r="F199" s="6" t="n"/>
-      <c r="G199" s="6" t="n"/>
-      <c r="H199" s="6" t="n"/>
-      <c r="I199" s="6" t="n"/>
-      <c r="J199" s="7" t="n"/>
-      <c r="K199" s="5" t="n"/>
-      <c r="L199" s="6" t="n"/>
-      <c r="M199" s="5" t="n"/>
-      <c r="N199" s="5" t="n"/>
-      <c r="O199" s="5" t="n"/>
-      <c r="P199" s="8" t="n"/>
-      <c r="Q199" s="9" t="n"/>
+      <c r="A199" s="12" t="inlineStr">
+        <is>
+          <t>214</t>
+        </is>
+      </c>
+      <c r="B199" s="13" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C199" s="12" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D199" s="14" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E199" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F199" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G199" s="13" t="inlineStr"/>
+      <c r="H199" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I199" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J199" s="14" t="inlineStr"/>
+      <c r="K199" s="12" t="inlineStr">
+        <is>
+          <t>214_Lithuania_2015_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L199" s="13" t="inlineStr"/>
+      <c r="M199" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N199" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O199" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P199" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Lithuania.</t>
+        </is>
+      </c>
+      <c r="Q199" s="16" t="inlineStr">
+        <is>
+          <t>Lithuania’s euro coins show the coat of arms of the Republic of Lithuania, Vytis, the country of issuance "LIETUVA" and the year of issuance "2015". The coins also feature the 12 stars of the European flag. They were designed by the sculptor Antanas Žukauskas.
+The edge-lettering of the 2-euro coin bears the inscription "LAISVĖ * VIENYBĖ * GEROVĖ *", meaning Liberty-Solidarity-Prosperity." (Freedom * Unity * Well-Being *)</t>
+        </is>
+      </c>
     </row>
     <row r="200" ht="15" customHeight="1">
-      <c r="A200" s="5" t="n"/>
-      <c r="B200" s="6" t="n"/>
-      <c r="C200" s="5" t="n"/>
-      <c r="D200" s="7" t="n"/>
-      <c r="E200" s="6" t="n"/>
-      <c r="F200" s="6" t="n"/>
-      <c r="G200" s="6" t="n"/>
-      <c r="H200" s="6" t="n"/>
-      <c r="I200" s="6" t="n"/>
-      <c r="J200" s="7" t="n"/>
-      <c r="K200" s="5" t="n"/>
-      <c r="L200" s="6" t="n"/>
-      <c r="M200" s="5" t="n"/>
-      <c r="N200" s="5" t="n"/>
-      <c r="O200" s="5" t="n"/>
-      <c r="P200" s="8" t="n"/>
-      <c r="Q200" s="9" t="n"/>
+      <c r="A200" s="12" t="inlineStr">
+        <is>
+          <t>215</t>
+        </is>
+      </c>
+      <c r="B200" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C200" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D200" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E200" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F200" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G200" s="13" t="inlineStr"/>
+      <c r="H200" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I200" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J200" s="14" t="inlineStr"/>
+      <c r="K200" s="12" t="inlineStr">
+        <is>
+          <t>215_Luxembourg_2002_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L200" s="13" t="inlineStr"/>
+      <c r="M200" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N200" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O200" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P200" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q200" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").
+The edge lettering on the €2 coin is ‘2**’ repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="201" ht="15" customHeight="1">
-      <c r="A201" s="5" t="n"/>
-      <c r="B201" s="6" t="n"/>
-      <c r="C201" s="5" t="n"/>
-      <c r="D201" s="7" t="n"/>
-      <c r="E201" s="6" t="n"/>
-      <c r="F201" s="6" t="n"/>
-      <c r="G201" s="6" t="n"/>
-      <c r="H201" s="6" t="n"/>
-      <c r="I201" s="6" t="n"/>
-      <c r="J201" s="7" t="n"/>
-      <c r="K201" s="5" t="n"/>
-      <c r="L201" s="6" t="n"/>
-      <c r="M201" s="5" t="n"/>
-      <c r="N201" s="5" t="n"/>
-      <c r="O201" s="5" t="n"/>
-      <c r="P201" s="8" t="n"/>
-      <c r="Q201" s="9" t="n"/>
+      <c r="A201" s="12" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="B201" s="13" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C201" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D201" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E201" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F201" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G201" s="13" t="inlineStr"/>
+      <c r="H201" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I201" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J201" s="14" t="inlineStr"/>
+      <c r="K201" s="12" t="inlineStr">
+        <is>
+          <t>216_Malta_2008_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L201" s="13" t="inlineStr"/>
+      <c r="M201" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N201" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O201" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P201" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Malta.</t>
+        </is>
+      </c>
+      <c r="Q201" s="16" t="inlineStr">
+        <is>
+          <t>The €1 and €2 coins show the emblem used by the Sovereign Order of Malta. During the Order's rule over Malta, between 1530 and 1798, the eight-pointed cross became associated with the island and is now often referred to as the Maltese Cross.</t>
+        </is>
+      </c>
     </row>
     <row r="202" ht="15" customHeight="1">
-      <c r="A202" s="5" t="n"/>
-      <c r="B202" s="6" t="n"/>
-      <c r="C202" s="5" t="n"/>
-      <c r="D202" s="7" t="n"/>
-      <c r="E202" s="6" t="n"/>
-      <c r="F202" s="6" t="n"/>
-      <c r="G202" s="6" t="n"/>
-      <c r="H202" s="6" t="n"/>
-      <c r="I202" s="6" t="n"/>
-      <c r="J202" s="7" t="n"/>
-      <c r="K202" s="5" t="n"/>
-      <c r="L202" s="6" t="n"/>
-      <c r="M202" s="5" t="n"/>
-      <c r="N202" s="5" t="n"/>
-      <c r="O202" s="5" t="n"/>
-      <c r="P202" s="8" t="n"/>
-      <c r="Q202" s="9" t="n"/>
+      <c r="A202" s="12" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="B202" s="13" t="inlineStr">
+        <is>
+          <t>Monaco</t>
+        </is>
+      </c>
+      <c r="C202" s="12" t="inlineStr">
+        <is>
+          <t>MC</t>
+        </is>
+      </c>
+      <c r="D202" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E202" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F202" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G202" s="13" t="inlineStr"/>
+      <c r="H202" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I202" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J202" s="14" t="inlineStr"/>
+      <c r="K202" s="12" t="inlineStr">
+        <is>
+          <t>217_Monaco_2024_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L202" s="13" t="inlineStr"/>
+      <c r="M202" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N202" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O202" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P202" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Monaco.</t>
+        </is>
+      </c>
+      <c r="Q202" s="16" t="inlineStr">
+        <is>
+          <t>Second series
+The second series, introduced in 2006, features a portrait of Prince Albert II on the €2 and €1 coins. His monogram appears on the 50, 20 and 10 cent coins. The coat of arms of the Grimaldi House remains the main design on the 5, 2 and 1 cent coins.
+Following the death of its Head of State, Prince Rainier III, Monaco issued a new series of euro coins in 2006. The portrait of His Highness Prince Albert II features on the €2 and €1 coins, and his monogram is depicted in the 10, 20, and 50-cent coins. As in the 2002 series, the 1, 2, and 5-cent coins show the coat of arms of the Sovereign Princes of Monaco.
+In both series, the edge lettering on the €2 coin is ‘2**’, repeated six times, alternately upright and inverted.</t>
+        </is>
+      </c>
     </row>
     <row r="203" ht="15" customHeight="1">
-      <c r="A203" s="5" t="n"/>
-      <c r="B203" s="6" t="n"/>
-      <c r="C203" s="5" t="n"/>
-      <c r="D203" s="7" t="n"/>
-      <c r="E203" s="6" t="n"/>
-      <c r="F203" s="6" t="n"/>
-      <c r="G203" s="6" t="n"/>
-      <c r="H203" s="6" t="n"/>
-      <c r="I203" s="6" t="n"/>
-      <c r="J203" s="7" t="n"/>
-      <c r="K203" s="5" t="n"/>
-      <c r="L203" s="6" t="n"/>
-      <c r="M203" s="5" t="n"/>
-      <c r="N203" s="5" t="n"/>
-      <c r="O203" s="5" t="n"/>
-      <c r="P203" s="8" t="n"/>
-      <c r="Q203" s="9" t="n"/>
+      <c r="A203" s="12" t="inlineStr">
+        <is>
+          <t>218</t>
+        </is>
+      </c>
+      <c r="B203" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C203" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D203" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E203" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F203" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G203" s="13" t="inlineStr"/>
+      <c r="H203" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I203" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J203" s="14" t="inlineStr"/>
+      <c r="K203" s="12" t="inlineStr">
+        <is>
+          <t>218_Netherlands_2024_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L203" s="13" t="inlineStr"/>
+      <c r="M203" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N203" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O203" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P203" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Netherlands.</t>
+        </is>
+      </c>
+      <c r="Q203" s="16" t="inlineStr">
+        <is>
+          <t>Second series
+The second series, introduced in 2014, shows King Willem-Alexander and bears the inscription "Willem-Alexander Koning der Nederlanden" (King of the Netherlands).
+Second series: King Willem-Alexander is shown with the inscription "Willem-Alexander Koning der Nederlanden" (King of the Netherlands). The mint marks appear on either side of the year of issuance. Edge-lettering of the €2 coin, both series: GOD * ZIJ * MET * ONS * (God be with us).
+The Netherlands chose two designs by Bruno Ninaber van Eyben, showing Queen Beatrix, for the first series. There are two series of coins in circulation. Both are valid.</t>
+        </is>
+      </c>
     </row>
     <row r="204" ht="15" customHeight="1">
-      <c r="A204" s="5" t="n"/>
-      <c r="B204" s="6" t="n"/>
-      <c r="C204" s="5" t="n"/>
-      <c r="D204" s="7" t="n"/>
-      <c r="E204" s="6" t="n"/>
-      <c r="F204" s="6" t="n"/>
-      <c r="G204" s="6" t="n"/>
-      <c r="H204" s="6" t="n"/>
-      <c r="I204" s="6" t="n"/>
-      <c r="J204" s="7" t="n"/>
-      <c r="K204" s="5" t="n"/>
-      <c r="L204" s="6" t="n"/>
-      <c r="M204" s="5" t="n"/>
-      <c r="N204" s="5" t="n"/>
-      <c r="O204" s="5" t="n"/>
-      <c r="P204" s="8" t="n"/>
-      <c r="Q204" s="9" t="n"/>
+      <c r="A204" s="12" t="inlineStr">
+        <is>
+          <t>219</t>
+        </is>
+      </c>
+      <c r="B204" s="13" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="C204" s="12" t="inlineStr">
+        <is>
+          <t>NL</t>
+        </is>
+      </c>
+      <c r="D204" s="14" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E204" s="13" t="inlineStr">
+        <is>
+          <t>2 €</t>
+        </is>
+      </c>
+      <c r="F204" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G204" s="13" t="inlineStr"/>
+      <c r="H204" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I204" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J204" s="14" t="inlineStr"/>
+      <c r="K204" s="12" t="inlineStr">
+        <is>
+          <t>219_Netherlands_2001_2euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L204" s="13" t="inlineStr"/>
+      <c r="M204" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N204" s="12" t="inlineStr">
+        <is>
+          <t>8.50 g</t>
+        </is>
+      </c>
+      <c r="O204" s="12" t="inlineStr">
+        <is>
+          <t>25.75 mm</t>
+        </is>
+      </c>
+      <c r="P204" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 € circulation coin of Netherlands.</t>
+        </is>
+      </c>
+      <c r="Q204" s="16" t="inlineStr">
+        <is>
+          <t>First series
+Queen Beatrix is shown with the inscription "Beatrix Koningin der Nederlanden" (Queen of the Netherlands).
+The Netherlands chose two designs by Bruno Ninaber van Eyben, showing Queen Beatrix, for the first series. There are two series of coins in circulation. Both are valid.</t>
+        </is>
+      </c>
     </row>
     <row r="205" ht="15" customHeight="1">
       <c r="A205" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -14800,12 +14800,12 @@
       </c>
       <c r="B191" s="13" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Cyprus</t>
         </is>
       </c>
       <c r="C191" s="12" t="inlineStr">
         <is>
-          <t>HR</t>
+          <t>CY</t>
         </is>
       </c>
       <c r="D191" s="14" t="inlineStr">
@@ -14837,7 +14837,7 @@
       <c r="J191" s="14" t="inlineStr"/>
       <c r="K191" s="12" t="inlineStr">
         <is>
-          <t>206_Croatia_2018_2euro_Regular.jpeg</t>
+          <t>206_Cyprus_2018_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L191" s="13" t="inlineStr"/>
@@ -14858,7 +14858,7 @@
       </c>
       <c r="P191" s="15" t="inlineStr">
         <is>
-          <t>Regular 2 € circulation coin of Croatia.</t>
+          <t>Regular 2 € circulation coin of Cyprus.</t>
         </is>
       </c>
       <c r="Q191" s="16" t="inlineStr">

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -801,8 +801,10 @@
           <t>ES</t>
         </is>
       </c>
-      <c r="D5" s="14" t="n">
-        <v>1999</v>
+      <c r="D5" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
       </c>
       <c r="E5" s="13" t="inlineStr">
         <is>
@@ -814,14 +816,10 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G5" s="13" t="inlineStr">
-        <is>
-          <t>2 Euro</t>
-        </is>
-      </c>
+      <c r="G5" s="13" t="inlineStr"/>
       <c r="H5" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>F</t>
         </is>
       </c>
       <c r="I5" s="13" t="inlineStr">
@@ -832,7 +830,7 @@
       <c r="J5" s="14" t="inlineStr"/>
       <c r="K5" s="12" t="inlineStr">
         <is>
-          <t>006_Spain_1999_2Euro_Regular.jpeg</t>
+          <t>006_Spain_1999_2euro_Regular.jpeg</t>
         </is>
       </c>
       <c r="L5" s="13" t="inlineStr"/>
@@ -858,7 +856,8 @@
       </c>
       <c r="Q5" s="16" t="inlineStr">
         <is>
-          <t>The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.
+          <t>First series
+The first and second series show a portrait of King Juan Carlos I de Borbón y Borbón.
 In 2015, Spain introduced a third series of €1 and €2 coins showing the new King Felipe VI and the country code ‘ESPAÑA 2015’. The mint mark appears at the right of the effigy.</t>
         </is>
       </c>
@@ -10679,7 +10678,7 @@
       <c r="G136" s="13" t="inlineStr"/>
       <c r="H136" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I136" s="13" t="inlineStr">
@@ -10716,7 +10715,7 @@
       </c>
       <c r="Q136" s="16" t="inlineStr">
         <is>
-          <t>This coin shows the poet France Prešeren and the inscription "Shivé naj vsi naródi" (God’s blessing on all nations) − a line taken from his poem "Zdravljica" which is also used in the country’s national anthem. Edge lettering of the €2 coin: SLOVENIJA followed by an engraved dot.</t>
+          <t>The €2 coin shows the portrait of France Prešeren, Slovenia's greatest poet, together with the line 'Shivé naj vsi naródi' (God’s blessing on all nations) in his handwriting. The words are taken from the seventh verse of his poem Zdravlijca (‘A Toast’), which is also the Slovenian national anthem. The edge lettering consists of the word SLOVENIJA followed by an engraved dot.</t>
         </is>
       </c>
     </row>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -10426,8 +10426,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D133" s="14" t="n">
-        <v>2002</v>
+      <c r="D133" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
         <is>
@@ -10439,11 +10441,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G133" s="13" t="inlineStr">
-        <is>
-          <t>10 cent</t>
-        </is>
-      </c>
+      <c r="G133" s="13" t="inlineStr"/>
       <c r="H133" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -10457,7 +10455,7 @@
       <c r="J133" s="14" t="inlineStr"/>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>137_Germany_2002_10cent_Regular.jpeg</t>
+          <t>137_Germany_2024_10cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr"/>
@@ -10504,8 +10502,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D134" s="14" t="n">
-        <v>2002</v>
+      <c r="D134" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="E134" s="13" t="inlineStr">
         <is>
@@ -10517,11 +10517,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G134" s="13" t="inlineStr">
-        <is>
-          <t>20 cent</t>
-        </is>
-      </c>
+      <c r="G134" s="13" t="inlineStr"/>
       <c r="H134" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -10535,7 +10531,7 @@
       <c r="J134" s="14" t="inlineStr"/>
       <c r="K134" s="12" t="inlineStr">
         <is>
-          <t>138_Germany_2002_20cent_Regular.jpeg</t>
+          <t>138_Germany_2023_20cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L134" s="13" t="inlineStr"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -5415,7 +5415,7 @@
       <c r="H65" s="13" t="inlineStr"/>
       <c r="I65" s="13" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Found</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr"/>
@@ -15858,23 +15858,80 @@
       </c>
     </row>
     <row r="205" ht="15" customHeight="1">
-      <c r="A205" s="5" t="n"/>
-      <c r="B205" s="6" t="n"/>
-      <c r="C205" s="5" t="n"/>
-      <c r="D205" s="7" t="n"/>
-      <c r="E205" s="6" t="n"/>
-      <c r="F205" s="6" t="n"/>
-      <c r="G205" s="6" t="n"/>
-      <c r="H205" s="6" t="n"/>
-      <c r="I205" s="6" t="n"/>
-      <c r="J205" s="7" t="n"/>
-      <c r="K205" s="5" t="n"/>
-      <c r="L205" s="6" t="n"/>
-      <c r="M205" s="5" t="n"/>
-      <c r="N205" s="5" t="n"/>
-      <c r="O205" s="5" t="n"/>
-      <c r="P205" s="8" t="n"/>
-      <c r="Q205" s="9" t="n"/>
+      <c r="A205" s="12" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="B205" s="13" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C205" s="12" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D205" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E205" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F205" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G205" s="13" t="inlineStr"/>
+      <c r="H205" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I205" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J205" s="14" t="inlineStr"/>
+      <c r="K205" s="12" t="inlineStr">
+        <is>
+          <t>220_Cyprus_2008_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L205" s="13" t="inlineStr"/>
+      <c r="M205" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N205" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O205" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P205" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Cyprus.</t>
+        </is>
+      </c>
+      <c r="Q205" s="16" t="inlineStr">
+        <is>
+          <t>Featured on the 10, 20 and 50-cent coins is the Kyrenia ship, a trading vessel which dates back to the fourth century BC and a symbol of Cyprus's seafaring history and its importance as a centre of trade.
+An open competition was launched in 2005 by the Central Bank of Cyprus to select the designs of the Cypriot euro coins, which were to have three different motifs reflecting the country’s specificity with regard to culture, nature and the sea.</t>
+        </is>
+      </c>
     </row>
     <row r="206" ht="15" customHeight="1">
       <c r="A206" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -5277,7 +5277,7 @@
       <c r="H63" s="13" t="inlineStr"/>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Missing</t>
+          <t>Found</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr"/>
@@ -15934,23 +15934,81 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="5" t="n"/>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="7" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="6" t="n"/>
-      <c r="G206" s="6" t="n"/>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="6" t="n"/>
-      <c r="J206" s="7" t="n"/>
-      <c r="K206" s="5" t="n"/>
-      <c r="L206" s="6" t="n"/>
-      <c r="M206" s="5" t="n"/>
-      <c r="N206" s="5" t="n"/>
-      <c r="O206" s="5" t="n"/>
-      <c r="P206" s="8" t="n"/>
-      <c r="Q206" s="9" t="n"/>
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="n">
+        <v>2030</v>
+      </c>
+      <c r="E206" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G206" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="inlineStr"/>
+      <c r="K206" s="12" t="inlineStr">
+        <is>
+          <t>221_Cyprus_2030_1cent_Regular.png</t>
+        </is>
+      </c>
+      <c r="L206" s="13" t="inlineStr"/>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N206" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P206" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Cyprus.</t>
+        </is>
+      </c>
+      <c r="Q206" s="16" t="inlineStr">
+        <is>
+          <t>test</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -5269,15 +5269,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G63" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
+      <c r="G63" s="13" t="inlineStr"/>
       <c r="H63" s="13" t="inlineStr"/>
       <c r="I63" s="13" t="inlineStr">
         <is>
-          <t>Found</t>
+          <t>Missing</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr"/>
@@ -15934,81 +15930,23 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="12" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="B206" s="13" t="inlineStr">
-        <is>
-          <t>Cyprus</t>
-        </is>
-      </c>
-      <c r="C206" s="12" t="inlineStr">
-        <is>
-          <t>CY</t>
-        </is>
-      </c>
-      <c r="D206" s="14" t="n">
-        <v>2030</v>
-      </c>
-      <c r="E206" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="F206" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G206" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="I206" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J206" s="14" t="inlineStr"/>
-      <c r="K206" s="12" t="inlineStr">
-        <is>
-          <t>221_Cyprus_2030_1cent_Regular.png</t>
-        </is>
-      </c>
-      <c r="L206" s="13" t="inlineStr"/>
-      <c r="M206" s="12" t="inlineStr">
-        <is>
-          <t>Copper-plated steel</t>
-        </is>
-      </c>
-      <c r="N206" s="12" t="inlineStr">
-        <is>
-          <t>2.30 g</t>
-        </is>
-      </c>
-      <c r="O206" s="12" t="inlineStr">
-        <is>
-          <t>16.25 mm</t>
-        </is>
-      </c>
-      <c r="P206" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 cent circulation coin of Cyprus.</t>
-        </is>
-      </c>
-      <c r="Q206" s="16" t="inlineStr">
-        <is>
-          <t>test</t>
-        </is>
-      </c>
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="6" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="7" t="n"/>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="6" t="n"/>
+      <c r="G206" s="6" t="n"/>
+      <c r="H206" s="6" t="n"/>
+      <c r="I206" s="6" t="n"/>
+      <c r="J206" s="7" t="n"/>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="6" t="n"/>
+      <c r="M206" s="5" t="n"/>
+      <c r="N206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="8" t="n"/>
+      <c r="Q206" s="9" t="n"/>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -8109,11 +8109,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G103" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
+      <c r="G103" s="13" t="inlineStr"/>
       <c r="H103" s="13" t="inlineStr"/>
       <c r="I103" s="13" t="inlineStr">
         <is>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -8177,11 +8177,7 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G104" s="13" t="inlineStr">
-        <is>
-          <t>2 cent</t>
-        </is>
-      </c>
+      <c r="G104" s="13" t="inlineStr"/>
       <c r="H104" s="13" t="inlineStr"/>
       <c r="I104" s="13" t="inlineStr">
         <is>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -15922,23 +15922,79 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="5" t="n"/>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="7" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="6" t="n"/>
-      <c r="G206" s="6" t="n"/>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="6" t="n"/>
-      <c r="J206" s="7" t="n"/>
-      <c r="K206" s="5" t="n"/>
-      <c r="L206" s="6" t="n"/>
-      <c r="M206" s="5" t="n"/>
-      <c r="N206" s="5" t="n"/>
-      <c r="O206" s="5" t="n"/>
-      <c r="P206" s="8" t="n"/>
-      <c r="Q206" s="9" t="n"/>
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="inlineStr">
+        <is>
+          <t>Vatican City</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="E206" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G206" s="13" t="inlineStr"/>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>AU</t>
+        </is>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="inlineStr"/>
+      <c r="K206" s="12" t="inlineStr">
+        <is>
+          <t>221_Vatican-City_2030_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L206" s="13" t="inlineStr"/>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N206" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P206" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Vatican City.</t>
+        </is>
+      </c>
+      <c r="Q206" s="16" t="inlineStr">
+        <is>
+          <t>TEST</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -15922,79 +15922,23 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="12" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="B206" s="13" t="inlineStr">
-        <is>
-          <t>Vatican City</t>
-        </is>
-      </c>
-      <c r="C206" s="12" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D206" s="14" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="E206" s="13" t="inlineStr">
-        <is>
-          <t>1 cent</t>
-        </is>
-      </c>
-      <c r="F206" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G206" s="13" t="inlineStr"/>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <t>AU</t>
-        </is>
-      </c>
-      <c r="I206" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J206" s="14" t="inlineStr"/>
-      <c r="K206" s="12" t="inlineStr">
-        <is>
-          <t>221_Vatican-City_2030_1cent_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L206" s="13" t="inlineStr"/>
-      <c r="M206" s="12" t="inlineStr">
-        <is>
-          <t>Copper-plated steel</t>
-        </is>
-      </c>
-      <c r="N206" s="12" t="inlineStr">
-        <is>
-          <t>2.30 g</t>
-        </is>
-      </c>
-      <c r="O206" s="12" t="inlineStr">
-        <is>
-          <t>16.25 mm</t>
-        </is>
-      </c>
-      <c r="P206" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 cent circulation coin of Vatican City.</t>
-        </is>
-      </c>
-      <c r="Q206" s="16" t="inlineStr">
-        <is>
-          <t>TEST</t>
-        </is>
-      </c>
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="6" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="7" t="n"/>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="6" t="n"/>
+      <c r="G206" s="6" t="n"/>
+      <c r="H206" s="6" t="n"/>
+      <c r="I206" s="6" t="n"/>
+      <c r="J206" s="7" t="n"/>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="6" t="n"/>
+      <c r="M206" s="5" t="n"/>
+      <c r="N206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="8" t="n"/>
+      <c r="Q206" s="9" t="n"/>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -15922,23 +15922,81 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="5" t="n"/>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="7" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="6" t="n"/>
-      <c r="G206" s="6" t="n"/>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="6" t="n"/>
-      <c r="J206" s="7" t="n"/>
-      <c r="K206" s="5" t="n"/>
-      <c r="L206" s="6" t="n"/>
-      <c r="M206" s="5" t="n"/>
-      <c r="N206" s="5" t="n"/>
-      <c r="O206" s="5" t="n"/>
-      <c r="P206" s="8" t="n"/>
-      <c r="Q206" s="9" t="n"/>
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="inlineStr">
+        <is>
+          <t>Vatican City</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>VA</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="n">
+        <v>2035</v>
+      </c>
+      <c r="E206" s="13" t="inlineStr">
+        <is>
+          <t>1 €</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G206" s="13" t="inlineStr">
+        <is>
+          <t>1 Euro</t>
+        </is>
+      </c>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="inlineStr"/>
+      <c r="K206" s="12" t="inlineStr">
+        <is>
+          <t>221_Vatican-City_2035_1Euro_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L206" s="13" t="inlineStr"/>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>Bimetallic</t>
+        </is>
+      </c>
+      <c r="N206" s="12" t="inlineStr">
+        <is>
+          <t>7.50 g</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>23.25 mm</t>
+        </is>
+      </c>
+      <c r="P206" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 € circulation coin of Vatican City.</t>
+        </is>
+      </c>
+      <c r="Q206" s="16" t="inlineStr">
+        <is>
+          <t>Refresh test</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -15922,81 +15922,23 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="12" t="inlineStr">
-        <is>
-          <t>221</t>
-        </is>
-      </c>
-      <c r="B206" s="13" t="inlineStr">
-        <is>
-          <t>Vatican City</t>
-        </is>
-      </c>
-      <c r="C206" s="12" t="inlineStr">
-        <is>
-          <t>VA</t>
-        </is>
-      </c>
-      <c r="D206" s="14" t="n">
-        <v>2035</v>
-      </c>
-      <c r="E206" s="13" t="inlineStr">
-        <is>
-          <t>1 €</t>
-        </is>
-      </c>
-      <c r="F206" s="13" t="inlineStr">
-        <is>
-          <t>Regular</t>
-        </is>
-      </c>
-      <c r="G206" s="13" t="inlineStr">
-        <is>
-          <t>1 Euro</t>
-        </is>
-      </c>
-      <c r="H206" s="13" t="inlineStr">
-        <is>
-          <t>XF</t>
-        </is>
-      </c>
-      <c r="I206" s="13" t="inlineStr">
-        <is>
-          <t>Collection</t>
-        </is>
-      </c>
-      <c r="J206" s="14" t="inlineStr"/>
-      <c r="K206" s="12" t="inlineStr">
-        <is>
-          <t>221_Vatican-City_2035_1Euro_Regular.jpeg</t>
-        </is>
-      </c>
-      <c r="L206" s="13" t="inlineStr"/>
-      <c r="M206" s="12" t="inlineStr">
-        <is>
-          <t>Bimetallic</t>
-        </is>
-      </c>
-      <c r="N206" s="12" t="inlineStr">
-        <is>
-          <t>7.50 g</t>
-        </is>
-      </c>
-      <c r="O206" s="12" t="inlineStr">
-        <is>
-          <t>23.25 mm</t>
-        </is>
-      </c>
-      <c r="P206" s="15" t="inlineStr">
-        <is>
-          <t>Regular 1 € circulation coin of Vatican City.</t>
-        </is>
-      </c>
-      <c r="Q206" s="16" t="inlineStr">
-        <is>
-          <t>Refresh test</t>
-        </is>
-      </c>
+      <c r="A206" s="5" t="n"/>
+      <c r="B206" s="6" t="n"/>
+      <c r="C206" s="5" t="n"/>
+      <c r="D206" s="7" t="n"/>
+      <c r="E206" s="6" t="n"/>
+      <c r="F206" s="6" t="n"/>
+      <c r="G206" s="6" t="n"/>
+      <c r="H206" s="6" t="n"/>
+      <c r="I206" s="6" t="n"/>
+      <c r="J206" s="7" t="n"/>
+      <c r="K206" s="5" t="n"/>
+      <c r="L206" s="6" t="n"/>
+      <c r="M206" s="5" t="n"/>
+      <c r="N206" s="5" t="n"/>
+      <c r="O206" s="5" t="n"/>
+      <c r="P206" s="8" t="n"/>
+      <c r="Q206" s="9" t="n"/>
     </row>
     <row r="207" ht="15" customHeight="1">
       <c r="A207" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -9082,8 +9082,10 @@
           <t>AT</t>
         </is>
       </c>
-      <c r="D116" s="14" t="n">
-        <v>2021</v>
+      <c r="D116" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
       </c>
       <c r="E116" s="13" t="inlineStr">
         <is>
@@ -15922,251 +15924,979 @@
       </c>
     </row>
     <row r="206" ht="15" customHeight="1">
-      <c r="A206" s="5" t="n"/>
-      <c r="B206" s="6" t="n"/>
-      <c r="C206" s="5" t="n"/>
-      <c r="D206" s="7" t="n"/>
-      <c r="E206" s="6" t="n"/>
-      <c r="F206" s="6" t="n"/>
-      <c r="G206" s="6" t="n"/>
-      <c r="H206" s="6" t="n"/>
-      <c r="I206" s="6" t="n"/>
-      <c r="J206" s="7" t="n"/>
-      <c r="K206" s="5" t="n"/>
-      <c r="L206" s="6" t="n"/>
-      <c r="M206" s="5" t="n"/>
-      <c r="N206" s="5" t="n"/>
-      <c r="O206" s="5" t="n"/>
-      <c r="P206" s="8" t="n"/>
-      <c r="Q206" s="9" t="n"/>
+      <c r="A206" s="12" t="inlineStr">
+        <is>
+          <t>221</t>
+        </is>
+      </c>
+      <c r="B206" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C206" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D206" s="14" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="E206" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F206" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G206" s="13" t="inlineStr"/>
+      <c r="H206" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I206" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J206" s="14" t="inlineStr"/>
+      <c r="K206" s="12" t="inlineStr">
+        <is>
+          <t>221_Belgium_2007_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L206" s="13" t="inlineStr"/>
+      <c r="M206" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N206" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O206" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P206" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q206" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="207" ht="15" customHeight="1">
-      <c r="A207" s="5" t="n"/>
-      <c r="B207" s="6" t="n"/>
-      <c r="C207" s="5" t="n"/>
-      <c r="D207" s="7" t="n"/>
-      <c r="E207" s="6" t="n"/>
-      <c r="F207" s="6" t="n"/>
-      <c r="G207" s="6" t="n"/>
-      <c r="H207" s="6" t="n"/>
-      <c r="I207" s="6" t="n"/>
-      <c r="J207" s="7" t="n"/>
-      <c r="K207" s="5" t="n"/>
-      <c r="L207" s="6" t="n"/>
-      <c r="M207" s="5" t="n"/>
-      <c r="N207" s="5" t="n"/>
-      <c r="O207" s="5" t="n"/>
-      <c r="P207" s="8" t="n"/>
-      <c r="Q207" s="9" t="n"/>
+      <c r="A207" s="12" t="inlineStr">
+        <is>
+          <t>222</t>
+        </is>
+      </c>
+      <c r="B207" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C207" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D207" s="14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E207" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F207" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G207" s="13" t="inlineStr"/>
+      <c r="H207" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I207" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J207" s="14" t="inlineStr"/>
+      <c r="K207" s="12" t="inlineStr">
+        <is>
+          <t>222_Belgium_2013_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L207" s="13" t="inlineStr"/>
+      <c r="M207" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N207" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O207" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P207" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q207" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="208" ht="15" customHeight="1">
-      <c r="A208" s="5" t="n"/>
-      <c r="B208" s="6" t="n"/>
-      <c r="C208" s="5" t="n"/>
-      <c r="D208" s="7" t="n"/>
-      <c r="E208" s="6" t="n"/>
-      <c r="F208" s="6" t="n"/>
-      <c r="G208" s="6" t="n"/>
-      <c r="H208" s="6" t="n"/>
-      <c r="I208" s="6" t="n"/>
-      <c r="J208" s="7" t="n"/>
-      <c r="K208" s="5" t="n"/>
-      <c r="L208" s="6" t="n"/>
-      <c r="M208" s="5" t="n"/>
-      <c r="N208" s="5" t="n"/>
-      <c r="O208" s="5" t="n"/>
-      <c r="P208" s="8" t="n"/>
-      <c r="Q208" s="9" t="n"/>
+      <c r="A208" s="12" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="B208" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C208" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D208" s="14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E208" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F208" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G208" s="13" t="inlineStr"/>
+      <c r="H208" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I208" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J208" s="14" t="inlineStr"/>
+      <c r="K208" s="12" t="inlineStr">
+        <is>
+          <t>223_Belgium_2013_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L208" s="13" t="inlineStr"/>
+      <c r="M208" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N208" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O208" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P208" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q208" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="209" ht="15" customHeight="1">
-      <c r="A209" s="5" t="n"/>
-      <c r="B209" s="6" t="n"/>
-      <c r="C209" s="5" t="n"/>
-      <c r="D209" s="7" t="n"/>
-      <c r="E209" s="6" t="n"/>
-      <c r="F209" s="6" t="n"/>
-      <c r="G209" s="6" t="n"/>
-      <c r="H209" s="6" t="n"/>
-      <c r="I209" s="6" t="n"/>
-      <c r="J209" s="7" t="n"/>
-      <c r="K209" s="5" t="n"/>
-      <c r="L209" s="6" t="n"/>
-      <c r="M209" s="5" t="n"/>
-      <c r="N209" s="5" t="n"/>
-      <c r="O209" s="5" t="n"/>
-      <c r="P209" s="8" t="n"/>
-      <c r="Q209" s="9" t="n"/>
+      <c r="A209" s="12" t="inlineStr">
+        <is>
+          <t>224</t>
+        </is>
+      </c>
+      <c r="B209" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C209" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D209" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E209" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F209" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G209" s="13" t="inlineStr"/>
+      <c r="H209" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I209" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J209" s="14" t="inlineStr"/>
+      <c r="K209" s="12" t="inlineStr">
+        <is>
+          <t>224_Belgium_2006_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L209" s="13" t="inlineStr"/>
+      <c r="M209" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N209" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O209" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P209" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q209" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="210" ht="15" customHeight="1">
-      <c r="A210" s="5" t="n"/>
-      <c r="B210" s="6" t="n"/>
-      <c r="C210" s="5" t="n"/>
-      <c r="D210" s="7" t="n"/>
-      <c r="E210" s="6" t="n"/>
-      <c r="F210" s="6" t="n"/>
-      <c r="G210" s="6" t="n"/>
-      <c r="H210" s="6" t="n"/>
-      <c r="I210" s="6" t="n"/>
-      <c r="J210" s="7" t="n"/>
-      <c r="K210" s="5" t="n"/>
-      <c r="L210" s="6" t="n"/>
-      <c r="M210" s="5" t="n"/>
-      <c r="N210" s="5" t="n"/>
-      <c r="O210" s="5" t="n"/>
-      <c r="P210" s="8" t="n"/>
-      <c r="Q210" s="9" t="n"/>
+      <c r="A210" s="12" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="B210" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C210" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D210" s="14" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E210" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F210" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G210" s="13" t="inlineStr"/>
+      <c r="H210" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I210" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J210" s="14" t="inlineStr"/>
+      <c r="K210" s="12" t="inlineStr">
+        <is>
+          <t>225_Belgium_2012_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L210" s="13" t="inlineStr"/>
+      <c r="M210" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N210" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O210" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P210" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q210" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="211" ht="15" customHeight="1">
-      <c r="A211" s="5" t="n"/>
-      <c r="B211" s="6" t="n"/>
-      <c r="C211" s="5" t="n"/>
-      <c r="D211" s="7" t="n"/>
-      <c r="E211" s="6" t="n"/>
-      <c r="F211" s="6" t="n"/>
-      <c r="G211" s="6" t="n"/>
-      <c r="H211" s="6" t="n"/>
-      <c r="I211" s="6" t="n"/>
-      <c r="J211" s="7" t="n"/>
-      <c r="K211" s="5" t="n"/>
-      <c r="L211" s="6" t="n"/>
-      <c r="M211" s="5" t="n"/>
-      <c r="N211" s="5" t="n"/>
-      <c r="O211" s="5" t="n"/>
-      <c r="P211" s="8" t="n"/>
-      <c r="Q211" s="9" t="n"/>
+      <c r="A211" s="12" t="inlineStr">
+        <is>
+          <t>226</t>
+        </is>
+      </c>
+      <c r="B211" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C211" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D211" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="E211" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F211" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G211" s="13" t="inlineStr"/>
+      <c r="H211" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I211" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J211" s="14" t="inlineStr"/>
+      <c r="K211" s="12" t="inlineStr">
+        <is>
+          <t>226_Belgium_2022_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L211" s="13" t="inlineStr"/>
+      <c r="M211" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N211" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O211" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P211" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q211" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="212" ht="15" customHeight="1">
-      <c r="A212" s="5" t="n"/>
-      <c r="B212" s="6" t="n"/>
-      <c r="C212" s="5" t="n"/>
-      <c r="D212" s="7" t="n"/>
-      <c r="E212" s="6" t="n"/>
-      <c r="F212" s="6" t="n"/>
-      <c r="G212" s="6" t="n"/>
-      <c r="H212" s="6" t="n"/>
-      <c r="I212" s="6" t="n"/>
-      <c r="J212" s="7" t="n"/>
-      <c r="K212" s="5" t="n"/>
-      <c r="L212" s="6" t="n"/>
-      <c r="M212" s="5" t="n"/>
-      <c r="N212" s="5" t="n"/>
-      <c r="O212" s="5" t="n"/>
-      <c r="P212" s="8" t="n"/>
-      <c r="Q212" s="9" t="n"/>
+      <c r="A212" s="12" t="inlineStr">
+        <is>
+          <t>227</t>
+        </is>
+      </c>
+      <c r="B212" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C212" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D212" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E212" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F212" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G212" s="13" t="inlineStr"/>
+      <c r="H212" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I212" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J212" s="14" t="inlineStr"/>
+      <c r="K212" s="12" t="inlineStr">
+        <is>
+          <t>227_Belgium_1999_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L212" s="13" t="inlineStr"/>
+      <c r="M212" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N212" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O212" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P212" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q212" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="213" ht="15" customHeight="1">
-      <c r="A213" s="5" t="n"/>
-      <c r="B213" s="6" t="n"/>
-      <c r="C213" s="5" t="n"/>
-      <c r="D213" s="7" t="n"/>
-      <c r="E213" s="6" t="n"/>
-      <c r="F213" s="6" t="n"/>
-      <c r="G213" s="6" t="n"/>
-      <c r="H213" s="6" t="n"/>
-      <c r="I213" s="6" t="n"/>
-      <c r="J213" s="7" t="n"/>
-      <c r="K213" s="5" t="n"/>
-      <c r="L213" s="6" t="n"/>
-      <c r="M213" s="5" t="n"/>
-      <c r="N213" s="5" t="n"/>
-      <c r="O213" s="5" t="n"/>
-      <c r="P213" s="8" t="n"/>
-      <c r="Q213" s="9" t="n"/>
+      <c r="A213" s="12" t="inlineStr">
+        <is>
+          <t>228</t>
+        </is>
+      </c>
+      <c r="B213" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C213" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D213" s="14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E213" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F213" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G213" s="13" t="inlineStr"/>
+      <c r="H213" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I213" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J213" s="14" t="inlineStr"/>
+      <c r="K213" s="12" t="inlineStr">
+        <is>
+          <t>228_Belgium_2013_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L213" s="13" t="inlineStr"/>
+      <c r="M213" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N213" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O213" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P213" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q213" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="214" ht="15" customHeight="1">
-      <c r="A214" s="5" t="n"/>
-      <c r="B214" s="6" t="n"/>
-      <c r="C214" s="5" t="n"/>
-      <c r="D214" s="7" t="n"/>
-      <c r="E214" s="6" t="n"/>
-      <c r="F214" s="6" t="n"/>
-      <c r="G214" s="6" t="n"/>
-      <c r="H214" s="6" t="n"/>
-      <c r="I214" s="6" t="n"/>
-      <c r="J214" s="7" t="n"/>
-      <c r="K214" s="5" t="n"/>
-      <c r="L214" s="6" t="n"/>
-      <c r="M214" s="5" t="n"/>
-      <c r="N214" s="5" t="n"/>
-      <c r="O214" s="5" t="n"/>
-      <c r="P214" s="8" t="n"/>
-      <c r="Q214" s="9" t="n"/>
+      <c r="A214" s="12" t="inlineStr">
+        <is>
+          <t>229</t>
+        </is>
+      </c>
+      <c r="B214" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C214" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D214" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E214" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F214" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G214" s="13" t="inlineStr"/>
+      <c r="H214" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I214" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J214" s="14" t="inlineStr"/>
+      <c r="K214" s="12" t="inlineStr">
+        <is>
+          <t>229_Belgium_2023_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L214" s="13" t="inlineStr"/>
+      <c r="M214" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N214" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O214" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P214" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q214" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="215" ht="15" customHeight="1">
-      <c r="A215" s="5" t="n"/>
-      <c r="B215" s="6" t="n"/>
-      <c r="C215" s="5" t="n"/>
-      <c r="D215" s="7" t="n"/>
-      <c r="E215" s="6" t="n"/>
-      <c r="F215" s="6" t="n"/>
-      <c r="G215" s="6" t="n"/>
-      <c r="H215" s="6" t="n"/>
-      <c r="I215" s="6" t="n"/>
-      <c r="J215" s="7" t="n"/>
-      <c r="K215" s="5" t="n"/>
-      <c r="L215" s="6" t="n"/>
-      <c r="M215" s="5" t="n"/>
-      <c r="N215" s="5" t="n"/>
-      <c r="O215" s="5" t="n"/>
-      <c r="P215" s="8" t="n"/>
-      <c r="Q215" s="9" t="n"/>
+      <c r="A215" s="12" t="inlineStr">
+        <is>
+          <t>230</t>
+        </is>
+      </c>
+      <c r="B215" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C215" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D215" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E215" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F215" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G215" s="13" t="inlineStr"/>
+      <c r="H215" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I215" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J215" s="14" t="inlineStr"/>
+      <c r="K215" s="12" t="inlineStr">
+        <is>
+          <t>230_Belgium_2011_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L215" s="13" t="inlineStr"/>
+      <c r="M215" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N215" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O215" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P215" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q215" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="216" ht="15" customHeight="1">
-      <c r="A216" s="5" t="n"/>
-      <c r="B216" s="6" t="n"/>
-      <c r="C216" s="5" t="n"/>
-      <c r="D216" s="7" t="n"/>
-      <c r="E216" s="6" t="n"/>
-      <c r="F216" s="6" t="n"/>
-      <c r="G216" s="6" t="n"/>
-      <c r="H216" s="6" t="n"/>
-      <c r="I216" s="6" t="n"/>
-      <c r="J216" s="7" t="n"/>
-      <c r="K216" s="5" t="n"/>
-      <c r="L216" s="6" t="n"/>
-      <c r="M216" s="5" t="n"/>
-      <c r="N216" s="5" t="n"/>
-      <c r="O216" s="5" t="n"/>
-      <c r="P216" s="8" t="n"/>
-      <c r="Q216" s="9" t="n"/>
+      <c r="A216" s="12" t="inlineStr">
+        <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="B216" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C216" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D216" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E216" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F216" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G216" s="13" t="inlineStr"/>
+      <c r="H216" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I216" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J216" s="14" t="inlineStr"/>
+      <c r="K216" s="12" t="inlineStr">
+        <is>
+          <t>231_Belgium_2023_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L216" s="13" t="inlineStr"/>
+      <c r="M216" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N216" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O216" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P216" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q216" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="217" ht="15" customHeight="1">
-      <c r="A217" s="5" t="n"/>
-      <c r="B217" s="6" t="n"/>
-      <c r="C217" s="5" t="n"/>
-      <c r="D217" s="7" t="n"/>
-      <c r="E217" s="6" t="n"/>
-      <c r="F217" s="6" t="n"/>
-      <c r="G217" s="6" t="n"/>
-      <c r="H217" s="6" t="n"/>
-      <c r="I217" s="6" t="n"/>
-      <c r="J217" s="7" t="n"/>
-      <c r="K217" s="5" t="n"/>
-      <c r="L217" s="6" t="n"/>
-      <c r="M217" s="5" t="n"/>
-      <c r="N217" s="5" t="n"/>
-      <c r="O217" s="5" t="n"/>
-      <c r="P217" s="8" t="n"/>
-      <c r="Q217" s="9" t="n"/>
+      <c r="A217" s="12" t="inlineStr">
+        <is>
+          <t>232</t>
+        </is>
+      </c>
+      <c r="B217" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C217" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D217" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E217" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F217" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G217" s="13" t="inlineStr"/>
+      <c r="H217" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I217" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J217" s="14" t="inlineStr"/>
+      <c r="K217" s="12" t="inlineStr">
+        <is>
+          <t>232_Belgium_1999_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L217" s="13" t="inlineStr"/>
+      <c r="M217" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N217" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O217" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P217" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q217" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="218" ht="15" customHeight="1">
-      <c r="A218" s="5" t="n"/>
-      <c r="B218" s="6" t="n"/>
-      <c r="C218" s="5" t="n"/>
-      <c r="D218" s="7" t="n"/>
-      <c r="E218" s="6" t="n"/>
-      <c r="F218" s="6" t="n"/>
-      <c r="G218" s="6" t="n"/>
-      <c r="H218" s="6" t="n"/>
-      <c r="I218" s="6" t="n"/>
-      <c r="J218" s="7" t="n"/>
-      <c r="K218" s="5" t="n"/>
-      <c r="L218" s="6" t="n"/>
-      <c r="M218" s="5" t="n"/>
-      <c r="N218" s="5" t="n"/>
-      <c r="O218" s="5" t="n"/>
-      <c r="P218" s="8" t="n"/>
-      <c r="Q218" s="9" t="n"/>
+      <c r="A218" s="12" t="inlineStr">
+        <is>
+          <t>233</t>
+        </is>
+      </c>
+      <c r="B218" s="13" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C218" s="12" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D218" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E218" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F218" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G218" s="13" t="inlineStr"/>
+      <c r="H218" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I218" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J218" s="14" t="inlineStr"/>
+      <c r="K218" s="12" t="inlineStr">
+        <is>
+          <t>233_Cyprus_2008_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L218" s="13" t="inlineStr"/>
+      <c r="M218" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N218" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O218" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P218" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Cyprus.</t>
+        </is>
+      </c>
+      <c r="Q218" s="16" t="inlineStr">
+        <is>
+          <t>Featured on the 10, 20 and 50-cent coins is the Kyrenia ship, a trading vessel which dates back to the fourth century BC and a symbol of Cyprus's seafaring history and its importance as a centre of trade.</t>
+        </is>
+      </c>
     </row>
     <row r="219" ht="15" customHeight="1">
       <c r="A219" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -8384,8 +8384,10 @@
           <t>CY</t>
         </is>
       </c>
-      <c r="D107" s="14" t="n">
-        <v>2002</v>
+      <c r="D107" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
       </c>
       <c r="E107" s="13" t="inlineStr">
         <is>
@@ -16899,270 +16901,1072 @@
       </c>
     </row>
     <row r="219" ht="15" customHeight="1">
-      <c r="A219" s="5" t="n"/>
-      <c r="B219" s="6" t="n"/>
-      <c r="C219" s="5" t="n"/>
-      <c r="D219" s="7" t="n"/>
-      <c r="E219" s="6" t="n"/>
-      <c r="F219" s="6" t="n"/>
-      <c r="G219" s="6" t="n"/>
-      <c r="H219" s="6" t="n"/>
-      <c r="I219" s="6" t="n"/>
-      <c r="J219" s="7" t="n"/>
-      <c r="K219" s="5" t="n"/>
-      <c r="L219" s="6" t="n"/>
-      <c r="M219" s="5" t="n"/>
-      <c r="N219" s="5" t="n"/>
-      <c r="O219" s="5" t="n"/>
-      <c r="P219" s="8" t="n"/>
-      <c r="Q219" s="9" t="n"/>
+      <c r="A219" s="12" t="inlineStr">
+        <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="B219" s="13" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C219" s="12" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D219" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E219" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F219" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G219" s="13" t="inlineStr"/>
+      <c r="H219" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I219" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J219" s="14" t="inlineStr"/>
+      <c r="K219" s="12" t="inlineStr">
+        <is>
+          <t>234_Cyprus_2008_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L219" s="13" t="inlineStr"/>
+      <c r="M219" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N219" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O219" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P219" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Cyprus.</t>
+        </is>
+      </c>
+      <c r="Q219" s="16" t="inlineStr">
+        <is>
+          <t>Featured on the 10, 20 and 50-cent coins is the Kyrenia ship, a trading vessel which dates back to the fourth century BC and a symbol of Cyprus's seafaring history and its importance as a centre of trade.</t>
+        </is>
+      </c>
     </row>
     <row r="220" ht="15" customHeight="1">
-      <c r="A220" s="5" t="n"/>
-      <c r="B220" s="6" t="n"/>
-      <c r="C220" s="5" t="n"/>
-      <c r="D220" s="7" t="n"/>
-      <c r="E220" s="6" t="n"/>
-      <c r="F220" s="6" t="n"/>
-      <c r="G220" s="6" t="n"/>
-      <c r="H220" s="6" t="n"/>
-      <c r="I220" s="6" t="n"/>
-      <c r="J220" s="7" t="n"/>
-      <c r="K220" s="5" t="n"/>
-      <c r="L220" s="6" t="n"/>
-      <c r="M220" s="5" t="n"/>
-      <c r="N220" s="5" t="n"/>
-      <c r="O220" s="5" t="n"/>
-      <c r="P220" s="8" t="n"/>
-      <c r="Q220" s="9" t="n"/>
+      <c r="A220" s="12" t="inlineStr">
+        <is>
+          <t>235</t>
+        </is>
+      </c>
+      <c r="B220" s="13" t="inlineStr">
+        <is>
+          <t>Cyprus</t>
+        </is>
+      </c>
+      <c r="C220" s="12" t="inlineStr">
+        <is>
+          <t>CY</t>
+        </is>
+      </c>
+      <c r="D220" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E220" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F220" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G220" s="13" t="inlineStr"/>
+      <c r="H220" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I220" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J220" s="14" t="inlineStr"/>
+      <c r="K220" s="12" t="inlineStr">
+        <is>
+          <t>235_Cyprus_2008_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L220" s="13" t="inlineStr"/>
+      <c r="M220" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N220" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O220" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P220" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Cyprus.</t>
+        </is>
+      </c>
+      <c r="Q220" s="16" t="inlineStr">
+        <is>
+          <t>The 1, 2 and 5-cent coins show the moufflon, a species of wild sheep found on Cyprus and representative of the island's wildlife.</t>
+        </is>
+      </c>
     </row>
     <row r="221" ht="15" customHeight="1">
-      <c r="A221" s="5" t="n"/>
-      <c r="B221" s="6" t="n"/>
-      <c r="C221" s="5" t="n"/>
-      <c r="D221" s="7" t="n"/>
-      <c r="E221" s="6" t="n"/>
-      <c r="F221" s="6" t="n"/>
-      <c r="G221" s="6" t="n"/>
-      <c r="H221" s="6" t="n"/>
-      <c r="I221" s="6" t="n"/>
-      <c r="J221" s="7" t="n"/>
-      <c r="K221" s="5" t="n"/>
-      <c r="L221" s="6" t="n"/>
-      <c r="M221" s="5" t="n"/>
-      <c r="N221" s="5" t="n"/>
-      <c r="O221" s="5" t="n"/>
-      <c r="P221" s="8" t="n"/>
-      <c r="Q221" s="9" t="n"/>
+      <c r="A221" s="12" t="inlineStr">
+        <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="B221" s="13" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="C221" s="12" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="D221" s="14" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E221" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F221" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G221" s="13" t="inlineStr"/>
+      <c r="H221" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I221" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J221" s="14" t="inlineStr"/>
+      <c r="K221" s="12" t="inlineStr">
+        <is>
+          <t>236_Estonia_2012_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L221" s="13" t="inlineStr"/>
+      <c r="M221" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N221" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O221" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P221" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Estonia.</t>
+        </is>
+      </c>
+      <c r="Q221" s="16" t="inlineStr">
+        <is>
+          <t>The design for the national side of Estonia’s coins is the same for all denominations. It features a geographical image of Estonia and the word "Eesti", which means "Estonia".</t>
+        </is>
+      </c>
     </row>
     <row r="222" ht="15" customHeight="1">
-      <c r="A222" s="5" t="n"/>
-      <c r="B222" s="6" t="n"/>
-      <c r="C222" s="5" t="n"/>
-      <c r="D222" s="7" t="n"/>
-      <c r="E222" s="6" t="n"/>
-      <c r="F222" s="6" t="n"/>
-      <c r="G222" s="6" t="n"/>
-      <c r="H222" s="6" t="n"/>
-      <c r="I222" s="6" t="n"/>
-      <c r="J222" s="7" t="n"/>
-      <c r="K222" s="5" t="n"/>
-      <c r="L222" s="6" t="n"/>
-      <c r="M222" s="5" t="n"/>
-      <c r="N222" s="5" t="n"/>
-      <c r="O222" s="5" t="n"/>
-      <c r="P222" s="8" t="n"/>
-      <c r="Q222" s="9" t="n"/>
+      <c r="A222" s="12" t="inlineStr">
+        <is>
+          <t>237</t>
+        </is>
+      </c>
+      <c r="B222" s="13" t="inlineStr">
+        <is>
+          <t>Estonia</t>
+        </is>
+      </c>
+      <c r="C222" s="12" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="D222" s="14" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E222" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F222" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G222" s="13" t="inlineStr"/>
+      <c r="H222" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I222" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J222" s="14" t="inlineStr"/>
+      <c r="K222" s="12" t="inlineStr">
+        <is>
+          <t>237_Estonia_2012_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L222" s="13" t="inlineStr"/>
+      <c r="M222" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N222" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O222" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P222" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Estonia.</t>
+        </is>
+      </c>
+      <c r="Q222" s="16" t="inlineStr">
+        <is>
+          <t>The design for the national side of Estonia’s coins is the same for all denominations. It features a geographical image of Estonia and the word "Eesti", which means "Estonia".</t>
+        </is>
+      </c>
     </row>
     <row r="223" ht="15" customHeight="1">
-      <c r="A223" s="5" t="n"/>
-      <c r="B223" s="6" t="n"/>
-      <c r="C223" s="5" t="n"/>
-      <c r="D223" s="7" t="n"/>
-      <c r="E223" s="6" t="n"/>
-      <c r="F223" s="6" t="n"/>
-      <c r="G223" s="6" t="n"/>
-      <c r="H223" s="6" t="n"/>
-      <c r="I223" s="6" t="n"/>
-      <c r="J223" s="7" t="n"/>
-      <c r="K223" s="5" t="n"/>
-      <c r="L223" s="6" t="n"/>
-      <c r="M223" s="5" t="n"/>
-      <c r="N223" s="5" t="n"/>
-      <c r="O223" s="5" t="n"/>
-      <c r="P223" s="8" t="n"/>
-      <c r="Q223" s="9" t="n"/>
+      <c r="A223" s="12" t="inlineStr">
+        <is>
+          <t>238</t>
+        </is>
+      </c>
+      <c r="B223" s="13" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C223" s="12" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D223" s="14" t="inlineStr">
+        <is>
+          <t>2001</t>
+        </is>
+      </c>
+      <c r="E223" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F223" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G223" s="13" t="inlineStr"/>
+      <c r="H223" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I223" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J223" s="14" t="inlineStr"/>
+      <c r="K223" s="12" t="inlineStr">
+        <is>
+          <t>238_Finland_2001_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L223" s="13" t="inlineStr"/>
+      <c r="M223" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N223" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O223" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P223" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Finland.</t>
+        </is>
+      </c>
+      <c r="Q223" s="16" t="inlineStr">
+        <is>
+          <t>Finland chose three designs based upon motifs similar to those used before on national coins. 1, 2, 5, 10, 20 and 50-cent coins: these show the Finnish heraldic lion in a reproduction of a design by the sculptor Heikki Häiväoja. The heraldic lion in a variety of designs has been used on several Finnish coins over the years, for example on the 1 markka coins between 1964 and 2001.</t>
+        </is>
+      </c>
     </row>
     <row r="224" ht="15" customHeight="1">
-      <c r="A224" s="5" t="n"/>
-      <c r="B224" s="6" t="n"/>
-      <c r="C224" s="5" t="n"/>
-      <c r="D224" s="7" t="n"/>
-      <c r="E224" s="6" t="n"/>
-      <c r="F224" s="6" t="n"/>
-      <c r="G224" s="6" t="n"/>
-      <c r="H224" s="6" t="n"/>
-      <c r="I224" s="6" t="n"/>
-      <c r="J224" s="7" t="n"/>
-      <c r="K224" s="5" t="n"/>
-      <c r="L224" s="6" t="n"/>
-      <c r="M224" s="5" t="n"/>
-      <c r="N224" s="5" t="n"/>
-      <c r="O224" s="5" t="n"/>
-      <c r="P224" s="8" t="n"/>
-      <c r="Q224" s="9" t="n"/>
+      <c r="A224" s="12" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="B224" s="13" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C224" s="12" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D224" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E224" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F224" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G224" s="13" t="inlineStr"/>
+      <c r="H224" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I224" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J224" s="14" t="inlineStr"/>
+      <c r="K224" s="12" t="inlineStr">
+        <is>
+          <t>239_Finland_1999_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L224" s="13" t="inlineStr"/>
+      <c r="M224" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N224" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O224" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P224" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Finland.</t>
+        </is>
+      </c>
+      <c r="Q224" s="16" t="inlineStr">
+        <is>
+          <t>Finland chose three designs based upon motifs similar to those used before on national coins. 1, 2, 5, 10, 20 and 50-cent coins: these show the Finnish heraldic lion in a reproduction of a design by the sculptor Heikki Häiväoja. The heraldic lion in a variety of designs has been used on several Finnish coins over the years, for example on the 1 markka coins between 1964 and 2001.</t>
+        </is>
+      </c>
     </row>
     <row r="225" ht="15" customHeight="1">
-      <c r="A225" s="5" t="n"/>
-      <c r="B225" s="6" t="n"/>
-      <c r="C225" s="5" t="n"/>
-      <c r="D225" s="7" t="n"/>
-      <c r="E225" s="6" t="n"/>
-      <c r="F225" s="6" t="n"/>
-      <c r="G225" s="6" t="n"/>
-      <c r="H225" s="6" t="n"/>
-      <c r="I225" s="6" t="n"/>
-      <c r="J225" s="7" t="n"/>
-      <c r="K225" s="5" t="n"/>
-      <c r="L225" s="6" t="n"/>
-      <c r="M225" s="5" t="n"/>
-      <c r="N225" s="5" t="n"/>
-      <c r="O225" s="5" t="n"/>
-      <c r="P225" s="8" t="n"/>
-      <c r="Q225" s="9" t="n"/>
+      <c r="A225" s="12" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="B225" s="13" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C225" s="12" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D225" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E225" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F225" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G225" s="13" t="inlineStr"/>
+      <c r="H225" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I225" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J225" s="14" t="inlineStr"/>
+      <c r="K225" s="12" t="inlineStr">
+        <is>
+          <t>240_Finland_2006_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L225" s="13" t="inlineStr"/>
+      <c r="M225" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N225" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O225" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P225" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Finland.</t>
+        </is>
+      </c>
+      <c r="Q225" s="16" t="inlineStr">
+        <is>
+          <t>Finland chose three designs based upon motifs similar to those used before on national coins. 1, 2, 5, 10, 20 and 50-cent coins: these show the Finnish heraldic lion in a reproduction of a design by the sculptor Heikki Häiväoja. The heraldic lion in a variety of designs has been used on several Finnish coins over the years, for example on the 1 markka coins between 1964 and 2001.</t>
+        </is>
+      </c>
     </row>
     <row r="226" ht="15" customHeight="1">
-      <c r="A226" s="5" t="n"/>
-      <c r="B226" s="6" t="n"/>
-      <c r="C226" s="5" t="n"/>
-      <c r="D226" s="7" t="n"/>
-      <c r="E226" s="6" t="n"/>
-      <c r="F226" s="6" t="n"/>
-      <c r="G226" s="6" t="n"/>
-      <c r="H226" s="6" t="n"/>
-      <c r="I226" s="6" t="n"/>
-      <c r="J226" s="7" t="n"/>
-      <c r="K226" s="5" t="n"/>
-      <c r="L226" s="6" t="n"/>
-      <c r="M226" s="5" t="n"/>
-      <c r="N226" s="5" t="n"/>
-      <c r="O226" s="5" t="n"/>
-      <c r="P226" s="8" t="n"/>
-      <c r="Q226" s="9" t="n"/>
+      <c r="A226" s="12" t="inlineStr">
+        <is>
+          <t>241</t>
+        </is>
+      </c>
+      <c r="B226" s="13" t="inlineStr">
+        <is>
+          <t>Finland</t>
+        </is>
+      </c>
+      <c r="C226" s="12" t="inlineStr">
+        <is>
+          <t>FI</t>
+        </is>
+      </c>
+      <c r="D226" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E226" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F226" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G226" s="13" t="inlineStr"/>
+      <c r="H226" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I226" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J226" s="14" t="inlineStr"/>
+      <c r="K226" s="12" t="inlineStr">
+        <is>
+          <t>241_Finland_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L226" s="13" t="inlineStr"/>
+      <c r="M226" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N226" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O226" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P226" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Finland.</t>
+        </is>
+      </c>
+      <c r="Q226" s="16" t="inlineStr">
+        <is>
+          <t>Finland chose three designs based upon motifs similar to those used before on national coins. 1, 2, 5, 10, 20 and 50-cent coins: these show the Finnish heraldic lion in a reproduction of a design by the sculptor Heikki Häiväoja. The heraldic lion in a variety of designs has been used on several Finnish coins over the years, for example on the 1 markka coins between 1964 and 2001.</t>
+        </is>
+      </c>
     </row>
     <row r="227" ht="15" customHeight="1">
-      <c r="A227" s="5" t="n"/>
-      <c r="B227" s="6" t="n"/>
-      <c r="C227" s="5" t="n"/>
-      <c r="D227" s="7" t="n"/>
-      <c r="E227" s="6" t="n"/>
-      <c r="F227" s="6" t="n"/>
-      <c r="G227" s="6" t="n"/>
-      <c r="H227" s="6" t="n"/>
-      <c r="I227" s="6" t="n"/>
-      <c r="J227" s="7" t="n"/>
-      <c r="K227" s="5" t="n"/>
-      <c r="L227" s="6" t="n"/>
-      <c r="M227" s="5" t="n"/>
-      <c r="N227" s="5" t="n"/>
-      <c r="O227" s="5" t="n"/>
-      <c r="P227" s="8" t="n"/>
-      <c r="Q227" s="9" t="n"/>
+      <c r="A227" s="12" t="inlineStr">
+        <is>
+          <t>242</t>
+        </is>
+      </c>
+      <c r="B227" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C227" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D227" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E227" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F227" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G227" s="13" t="inlineStr"/>
+      <c r="H227" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I227" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J227" s="14" t="inlineStr"/>
+      <c r="K227" s="12" t="inlineStr">
+        <is>
+          <t>242_France_2021_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L227" s="13" t="inlineStr"/>
+      <c r="M227" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N227" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O227" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P227" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q227" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 10, 20 and 50-cent coins depict a sower, a traditional feature of French coins and stamps since 1898.</t>
+        </is>
+      </c>
     </row>
     <row r="228" ht="15" customHeight="1">
-      <c r="A228" s="5" t="n"/>
-      <c r="B228" s="6" t="n"/>
-      <c r="C228" s="5" t="n"/>
-      <c r="D228" s="7" t="n"/>
-      <c r="E228" s="6" t="n"/>
-      <c r="F228" s="6" t="n"/>
-      <c r="G228" s="6" t="n"/>
-      <c r="H228" s="6" t="n"/>
-      <c r="I228" s="6" t="n"/>
-      <c r="J228" s="7" t="n"/>
-      <c r="K228" s="5" t="n"/>
-      <c r="L228" s="6" t="n"/>
-      <c r="M228" s="5" t="n"/>
-      <c r="N228" s="5" t="n"/>
-      <c r="O228" s="5" t="n"/>
-      <c r="P228" s="8" t="n"/>
-      <c r="Q228" s="9" t="n"/>
+      <c r="A228" s="12" t="inlineStr">
+        <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="B228" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C228" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D228" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E228" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F228" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G228" s="13" t="inlineStr"/>
+      <c r="H228" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I228" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J228" s="14" t="inlineStr"/>
+      <c r="K228" s="12" t="inlineStr">
+        <is>
+          <t>243_France_2021_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L228" s="13" t="inlineStr"/>
+      <c r="M228" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N228" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O228" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P228" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q228" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 10, 20 and 50-cent coins depict a sower, a traditional feature of French coins and stamps since 1898.</t>
+        </is>
+      </c>
     </row>
     <row r="229" ht="15" customHeight="1">
-      <c r="A229" s="5" t="n"/>
-      <c r="B229" s="6" t="n"/>
-      <c r="C229" s="5" t="n"/>
-      <c r="D229" s="7" t="n"/>
-      <c r="E229" s="6" t="n"/>
-      <c r="F229" s="6" t="n"/>
-      <c r="G229" s="6" t="n"/>
-      <c r="H229" s="6" t="n"/>
-      <c r="I229" s="6" t="n"/>
-      <c r="J229" s="7" t="n"/>
-      <c r="K229" s="5" t="n"/>
-      <c r="L229" s="6" t="n"/>
-      <c r="M229" s="5" t="n"/>
-      <c r="N229" s="5" t="n"/>
-      <c r="O229" s="5" t="n"/>
-      <c r="P229" s="8" t="n"/>
-      <c r="Q229" s="9" t="n"/>
+      <c r="A229" s="12" t="inlineStr">
+        <is>
+          <t>244</t>
+        </is>
+      </c>
+      <c r="B229" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C229" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D229" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E229" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F229" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G229" s="13" t="inlineStr"/>
+      <c r="H229" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I229" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J229" s="14" t="inlineStr"/>
+      <c r="K229" s="12" t="inlineStr">
+        <is>
+          <t>244_France_2021_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L229" s="13" t="inlineStr"/>
+      <c r="M229" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N229" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O229" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P229" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q229" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 10, 20 and 50-cent coins depict a sower, a traditional feature of French coins and stamps since 1898.</t>
+        </is>
+      </c>
     </row>
     <row r="230" ht="15" customHeight="1">
-      <c r="A230" s="5" t="n"/>
-      <c r="B230" s="6" t="n"/>
-      <c r="C230" s="5" t="n"/>
-      <c r="D230" s="7" t="n"/>
-      <c r="E230" s="6" t="n"/>
-      <c r="F230" s="6" t="n"/>
-      <c r="G230" s="6" t="n"/>
-      <c r="H230" s="6" t="n"/>
-      <c r="I230" s="6" t="n"/>
-      <c r="J230" s="7" t="n"/>
-      <c r="K230" s="5" t="n"/>
-      <c r="L230" s="6" t="n"/>
-      <c r="M230" s="5" t="n"/>
-      <c r="N230" s="5" t="n"/>
-      <c r="O230" s="5" t="n"/>
-      <c r="P230" s="8" t="n"/>
-      <c r="Q230" s="9" t="n"/>
+      <c r="A230" s="12" t="inlineStr">
+        <is>
+          <t>245</t>
+        </is>
+      </c>
+      <c r="B230" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C230" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D230" s="14" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="E230" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F230" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G230" s="13" t="inlineStr"/>
+      <c r="H230" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I230" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J230" s="14" t="inlineStr"/>
+      <c r="K230" s="12" t="inlineStr">
+        <is>
+          <t>245_France_2009_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L230" s="13" t="inlineStr"/>
+      <c r="M230" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N230" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O230" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P230" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q230" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 1, 2 and 5-cent coins show a modern portrait of Marianne, the personification of the French Republic.</t>
+        </is>
+      </c>
     </row>
     <row r="231" ht="15" customHeight="1">
-      <c r="A231" s="5" t="n"/>
-      <c r="B231" s="6" t="n"/>
-      <c r="C231" s="5" t="n"/>
-      <c r="D231" s="7" t="n"/>
-      <c r="E231" s="6" t="n"/>
-      <c r="F231" s="6" t="n"/>
-      <c r="G231" s="6" t="n"/>
-      <c r="H231" s="6" t="n"/>
-      <c r="I231" s="6" t="n"/>
-      <c r="J231" s="7" t="n"/>
-      <c r="K231" s="5" t="n"/>
-      <c r="L231" s="6" t="n"/>
-      <c r="M231" s="5" t="n"/>
-      <c r="N231" s="5" t="n"/>
-      <c r="O231" s="5" t="n"/>
-      <c r="P231" s="8" t="n"/>
-      <c r="Q231" s="9" t="n"/>
+      <c r="A231" s="12" t="inlineStr">
+        <is>
+          <t>246</t>
+        </is>
+      </c>
+      <c r="B231" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C231" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D231" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E231" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F231" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G231" s="13" t="inlineStr"/>
+      <c r="H231" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I231" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J231" s="14" t="inlineStr"/>
+      <c r="K231" s="12" t="inlineStr">
+        <is>
+          <t>246_France_2006_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L231" s="13" t="inlineStr"/>
+      <c r="M231" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N231" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O231" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P231" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q231" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 1, 2 and 5-cent coins show a modern portrait of Marianne, the personification of the French Republic.</t>
+        </is>
+      </c>
     </row>
     <row r="232" ht="15" customHeight="1">
-      <c r="A232" s="5" t="n"/>
-      <c r="B232" s="6" t="n"/>
-      <c r="C232" s="5" t="n"/>
-      <c r="D232" s="7" t="n"/>
-      <c r="E232" s="6" t="n"/>
-      <c r="F232" s="6" t="n"/>
-      <c r="G232" s="6" t="n"/>
-      <c r="H232" s="6" t="n"/>
-      <c r="I232" s="6" t="n"/>
-      <c r="J232" s="7" t="n"/>
-      <c r="K232" s="5" t="n"/>
-      <c r="L232" s="6" t="n"/>
-      <c r="M232" s="5" t="n"/>
-      <c r="N232" s="5" t="n"/>
-      <c r="O232" s="5" t="n"/>
-      <c r="P232" s="8" t="n"/>
-      <c r="Q232" s="9" t="n"/>
+      <c r="A232" s="12" t="inlineStr">
+        <is>
+          <t>247</t>
+        </is>
+      </c>
+      <c r="B232" s="13" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="C232" s="12" t="inlineStr">
+        <is>
+          <t>FR</t>
+        </is>
+      </c>
+      <c r="D232" s="14" t="inlineStr">
+        <is>
+          <t>1999</t>
+        </is>
+      </c>
+      <c r="E232" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F232" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G232" s="13" t="inlineStr"/>
+      <c r="H232" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I232" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J232" s="14" t="inlineStr"/>
+      <c r="K232" s="12" t="inlineStr">
+        <is>
+          <t>247_France_1999_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L232" s="13" t="inlineStr"/>
+      <c r="M232" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N232" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O232" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P232" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of France.</t>
+        </is>
+      </c>
+      <c r="Q232" s="16" t="inlineStr">
+        <is>
+          <t>First series
+A competition was organised in 1996-1997 to choose the design of the national sides of the euro coins.
+A panel, chaired by the Minister for Economic and Financial Affairs and made up of experts in numismatics, artists, members of parliament, one former member of the European Commission (Christine Scrivener), the French Mint Director Emmanuel Constans, the General Engraver Pierre Rodier, actress Irène Jacob and members of professional bodies, chose the winning designs from over 1 200 entries received from 97 participants.
+The 1, 2 and 5-cent coins show a modern portrait of Marianne, the personification of the French Republic.</t>
+        </is>
+      </c>
     </row>
     <row r="233" ht="15" customHeight="1">
       <c r="A233" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -10184,8 +10184,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D130" s="14" t="n">
-        <v>2002</v>
+      <c r="D130" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
@@ -10215,7 +10217,7 @@
       <c r="J130" s="14" t="inlineStr"/>
       <c r="K130" s="12" t="inlineStr">
         <is>
-          <t>134_Germany_2002_1cent_Regular.jpeg</t>
+          <t>134_Germany_2023_1cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L130" s="13" t="inlineStr"/>
@@ -10262,8 +10264,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D131" s="14" t="n">
-        <v>2002</v>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
       </c>
       <c r="E131" s="13" t="inlineStr">
         <is>
@@ -10293,7 +10297,7 @@
       <c r="J131" s="14" t="inlineStr"/>
       <c r="K131" s="12" t="inlineStr">
         <is>
-          <t>135_Germany_2002_2cent_Regular.jpeg</t>
+          <t>135_Germany_2020_2cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L131" s="13" t="inlineStr"/>
@@ -10340,8 +10344,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D132" s="14" t="n">
-        <v>2002</v>
+      <c r="D132" s="14" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
       </c>
       <c r="E132" s="13" t="inlineStr">
         <is>
@@ -10371,7 +10377,7 @@
       <c r="J132" s="14" t="inlineStr"/>
       <c r="K132" s="12" t="inlineStr">
         <is>
-          <t>136_Germany_2002_5cent_Regular.jpeg</t>
+          <t>136_Germany_2022_5cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L132" s="13" t="inlineStr"/>
@@ -10420,7 +10426,7 @@
       </c>
       <c r="D133" s="14" t="inlineStr">
         <is>
-          <t>2024</t>
+          <t>2023</t>
         </is>
       </c>
       <c r="E133" s="13" t="inlineStr">
@@ -10433,7 +10439,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G133" s="13" t="inlineStr"/>
+      <c r="G133" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
       <c r="H133" s="13" t="inlineStr">
         <is>
           <t>XF</t>
@@ -10447,7 +10457,7 @@
       <c r="J133" s="14" t="inlineStr"/>
       <c r="K133" s="12" t="inlineStr">
         <is>
-          <t>137_Germany_2024_10cent_Regular.jpeg</t>
+          <t>137_Germany_2023_10cent_Regular.jpeg</t>
         </is>
       </c>
       <c r="L133" s="13" t="inlineStr"/>
@@ -10570,8 +10580,10 @@
           <t>DE</t>
         </is>
       </c>
-      <c r="D135" s="14" t="n">
-        <v>2024</v>
+      <c r="D135" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
       </c>
       <c r="E135" s="13" t="inlineStr">
         <is>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -9716,8 +9716,10 @@
           <t>HR</t>
         </is>
       </c>
-      <c r="D124" s="14" t="n">
-        <v>2023</v>
+      <c r="D124" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
       </c>
       <c r="E124" s="13" t="inlineStr">
         <is>
@@ -17981,42 +17983,154 @@
       </c>
     </row>
     <row r="233" ht="15" customHeight="1">
-      <c r="A233" s="5" t="n"/>
-      <c r="B233" s="6" t="n"/>
-      <c r="C233" s="5" t="n"/>
-      <c r="D233" s="7" t="n"/>
-      <c r="E233" s="6" t="n"/>
-      <c r="F233" s="6" t="n"/>
-      <c r="G233" s="6" t="n"/>
-      <c r="H233" s="6" t="n"/>
-      <c r="I233" s="6" t="n"/>
-      <c r="J233" s="7" t="n"/>
-      <c r="K233" s="5" t="n"/>
-      <c r="L233" s="6" t="n"/>
-      <c r="M233" s="5" t="n"/>
-      <c r="N233" s="5" t="n"/>
-      <c r="O233" s="5" t="n"/>
-      <c r="P233" s="8" t="n"/>
-      <c r="Q233" s="9" t="n"/>
+      <c r="A233" s="12" t="inlineStr">
+        <is>
+          <t>248</t>
+        </is>
+      </c>
+      <c r="B233" s="13" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C233" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D233" s="14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E233" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F233" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G233" s="13" t="inlineStr"/>
+      <c r="H233" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I233" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J233" s="14" t="inlineStr"/>
+      <c r="K233" s="12" t="inlineStr">
+        <is>
+          <t>248_Malta_2013_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L233" s="13" t="inlineStr"/>
+      <c r="M233" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N233" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O233" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P233" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Malta.</t>
+        </is>
+      </c>
+      <c r="Q233" s="16" t="inlineStr">
+        <is>
+          <t>The 1, 2 and 5-cent coins depict the altar at the prehistoric temple complex of Mnajdra, a Neolithic complex dating back to 3600 BC which is considered to be one of the oldest free-standing temple groupings in the world.</t>
+        </is>
+      </c>
     </row>
     <row r="234" ht="15" customHeight="1">
-      <c r="A234" s="5" t="n"/>
-      <c r="B234" s="6" t="n"/>
-      <c r="C234" s="5" t="n"/>
-      <c r="D234" s="7" t="n"/>
-      <c r="E234" s="6" t="n"/>
-      <c r="F234" s="6" t="n"/>
-      <c r="G234" s="6" t="n"/>
-      <c r="H234" s="6" t="n"/>
-      <c r="I234" s="6" t="n"/>
-      <c r="J234" s="7" t="n"/>
-      <c r="K234" s="5" t="n"/>
-      <c r="L234" s="6" t="n"/>
-      <c r="M234" s="5" t="n"/>
-      <c r="N234" s="5" t="n"/>
-      <c r="O234" s="5" t="n"/>
-      <c r="P234" s="8" t="n"/>
-      <c r="Q234" s="9" t="n"/>
+      <c r="A234" s="12" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+      <c r="B234" s="13" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+      <c r="C234" s="12" t="inlineStr">
+        <is>
+          <t>MT</t>
+        </is>
+      </c>
+      <c r="D234" s="14" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="E234" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F234" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G234" s="13" t="inlineStr"/>
+      <c r="H234" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I234" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J234" s="14" t="inlineStr"/>
+      <c r="K234" s="12" t="inlineStr">
+        <is>
+          <t>249_Malta_2008_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L234" s="13" t="inlineStr"/>
+      <c r="M234" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N234" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O234" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P234" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Malta.</t>
+        </is>
+      </c>
+      <c r="Q234" s="16" t="inlineStr">
+        <is>
+          <t>The 10, 20 and 50-cent coins bear the Emblem of Malta, a shield displaying a heraldic representation of the Maltese national flag and supporting a mural crown that represents the fortifications of Malta and denotes a city state. The shield is bounded on the left by an olive branch and on the right by a palm branch, symbols of peace traditionally associated with Malta, forming a wreath tied at its base by a ribbon which carries the inscription "Repubblika ta' Malta" (Republic of Malta).</t>
+        </is>
+      </c>
     </row>
     <row r="235" ht="15" customHeight="1">
       <c r="A235" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -18133,232 +18133,916 @@
       </c>
     </row>
     <row r="235" ht="15" customHeight="1">
-      <c r="A235" s="5" t="n"/>
-      <c r="B235" s="6" t="n"/>
-      <c r="C235" s="5" t="n"/>
-      <c r="D235" s="7" t="n"/>
-      <c r="E235" s="6" t="n"/>
-      <c r="F235" s="6" t="n"/>
-      <c r="G235" s="6" t="n"/>
-      <c r="H235" s="6" t="n"/>
-      <c r="I235" s="6" t="n"/>
-      <c r="J235" s="7" t="n"/>
-      <c r="K235" s="5" t="n"/>
-      <c r="L235" s="6" t="n"/>
-      <c r="M235" s="5" t="n"/>
-      <c r="N235" s="5" t="n"/>
-      <c r="O235" s="5" t="n"/>
-      <c r="P235" s="8" t="n"/>
-      <c r="Q235" s="9" t="n"/>
+      <c r="A235" s="12" t="inlineStr">
+        <is>
+          <t>250</t>
+        </is>
+      </c>
+      <c r="B235" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C235" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D235" s="14" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="E235" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F235" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G235" s="13" t="inlineStr"/>
+      <c r="H235" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I235" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J235" s="14" t="inlineStr"/>
+      <c r="K235" s="12" t="inlineStr">
+        <is>
+          <t>250_Greece_2016_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L235" s="13" t="inlineStr"/>
+      <c r="M235" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N235" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O235" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P235" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q235" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+This design features an advanced model of an Athenian trireme, the largest warship afloat for more than 200 years, dating from the time of the Athenian democracy (fifth century BC).</t>
+        </is>
+      </c>
     </row>
     <row r="236" ht="15" customHeight="1">
-      <c r="A236" s="5" t="n"/>
-      <c r="B236" s="6" t="n"/>
-      <c r="C236" s="5" t="n"/>
-      <c r="D236" s="7" t="n"/>
-      <c r="E236" s="6" t="n"/>
-      <c r="F236" s="6" t="n"/>
-      <c r="G236" s="6" t="n"/>
-      <c r="H236" s="6" t="n"/>
-      <c r="I236" s="6" t="n"/>
-      <c r="J236" s="7" t="n"/>
-      <c r="K236" s="5" t="n"/>
-      <c r="L236" s="6" t="n"/>
-      <c r="M236" s="5" t="n"/>
-      <c r="N236" s="5" t="n"/>
-      <c r="O236" s="5" t="n"/>
-      <c r="P236" s="8" t="n"/>
-      <c r="Q236" s="9" t="n"/>
+      <c r="A236" s="12" t="inlineStr">
+        <is>
+          <t>251</t>
+        </is>
+      </c>
+      <c r="B236" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C236" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D236" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E236" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F236" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G236" s="13" t="inlineStr"/>
+      <c r="H236" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I236" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J236" s="14" t="inlineStr"/>
+      <c r="K236" s="12" t="inlineStr">
+        <is>
+          <t>251_Greece_2024_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L236" s="13" t="inlineStr"/>
+      <c r="M236" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N236" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O236" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P236" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q236" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+Depicted on this coin is a corvette, a type of ship used during the Greek War of Independence (1821-27).</t>
+        </is>
+      </c>
     </row>
     <row r="237" ht="15" customHeight="1">
-      <c r="A237" s="5" t="n"/>
-      <c r="B237" s="6" t="n"/>
-      <c r="C237" s="5" t="n"/>
-      <c r="D237" s="7" t="n"/>
-      <c r="E237" s="6" t="n"/>
-      <c r="F237" s="6" t="n"/>
-      <c r="G237" s="6" t="n"/>
-      <c r="H237" s="6" t="n"/>
-      <c r="I237" s="6" t="n"/>
-      <c r="J237" s="7" t="n"/>
-      <c r="K237" s="5" t="n"/>
-      <c r="L237" s="6" t="n"/>
-      <c r="M237" s="5" t="n"/>
-      <c r="N237" s="5" t="n"/>
-      <c r="O237" s="5" t="n"/>
-      <c r="P237" s="8" t="n"/>
-      <c r="Q237" s="9" t="n"/>
+      <c r="A237" s="12" t="inlineStr">
+        <is>
+          <t>252</t>
+        </is>
+      </c>
+      <c r="B237" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C237" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D237" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E237" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F237" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G237" s="13" t="inlineStr"/>
+      <c r="H237" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I237" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J237" s="14" t="inlineStr"/>
+      <c r="K237" s="12" t="inlineStr">
+        <is>
+          <t>252_Greece_2023_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L237" s="13" t="inlineStr"/>
+      <c r="M237" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N237" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O237" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P237" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q237" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+This coin shows a modern sea-going tanker, reflecting the innovative spirit of Greek shipping.</t>
+        </is>
+      </c>
     </row>
     <row r="238" ht="15" customHeight="1">
-      <c r="A238" s="5" t="n"/>
-      <c r="B238" s="6" t="n"/>
-      <c r="C238" s="5" t="n"/>
-      <c r="D238" s="7" t="n"/>
-      <c r="E238" s="6" t="n"/>
-      <c r="F238" s="6" t="n"/>
-      <c r="G238" s="6" t="n"/>
-      <c r="H238" s="6" t="n"/>
-      <c r="I238" s="6" t="n"/>
-      <c r="J238" s="7" t="n"/>
-      <c r="K238" s="5" t="n"/>
-      <c r="L238" s="6" t="n"/>
-      <c r="M238" s="5" t="n"/>
-      <c r="N238" s="5" t="n"/>
-      <c r="O238" s="5" t="n"/>
-      <c r="P238" s="8" t="n"/>
-      <c r="Q238" s="9" t="n"/>
+      <c r="A238" s="12" t="inlineStr">
+        <is>
+          <t>253</t>
+        </is>
+      </c>
+      <c r="B238" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C238" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D238" s="14" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="E238" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F238" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G238" s="13" t="inlineStr"/>
+      <c r="H238" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I238" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J238" s="14" t="inlineStr"/>
+      <c r="K238" s="12" t="inlineStr">
+        <is>
+          <t>253_Greece_2025_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L238" s="13" t="inlineStr"/>
+      <c r="M238" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N238" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O238" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P238" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q238" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+Rigas Fereos (Velestinlis) (1757-98) is featured on this coin. He was a forerunner and leading figure of the Greek enlightenment, as well as a visionary and herald of Balkan liberation from Ottoman rule.</t>
+        </is>
+      </c>
     </row>
     <row r="239" ht="15" customHeight="1">
-      <c r="A239" s="5" t="n"/>
-      <c r="B239" s="6" t="n"/>
-      <c r="C239" s="5" t="n"/>
-      <c r="D239" s="7" t="n"/>
-      <c r="E239" s="6" t="n"/>
-      <c r="F239" s="6" t="n"/>
-      <c r="G239" s="6" t="n"/>
-      <c r="H239" s="6" t="n"/>
-      <c r="I239" s="6" t="n"/>
-      <c r="J239" s="7" t="n"/>
-      <c r="K239" s="5" t="n"/>
-      <c r="L239" s="6" t="n"/>
-      <c r="M239" s="5" t="n"/>
-      <c r="N239" s="5" t="n"/>
-      <c r="O239" s="5" t="n"/>
-      <c r="P239" s="8" t="n"/>
-      <c r="Q239" s="9" t="n"/>
+      <c r="A239" s="12" t="inlineStr">
+        <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="B239" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C239" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D239" s="14" t="inlineStr">
+        <is>
+          <t>2020</t>
+        </is>
+      </c>
+      <c r="E239" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F239" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G239" s="13" t="inlineStr"/>
+      <c r="H239" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I239" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J239" s="14" t="inlineStr"/>
+      <c r="K239" s="12" t="inlineStr">
+        <is>
+          <t>254_Greece_2020_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L239" s="13" t="inlineStr"/>
+      <c r="M239" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N239" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O239" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P239" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q239" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+This coin commemorates Ioannis Capodistrias (1776-1831), a leading national and European politician and diplomat who became the first Governor of Greece (1830-31) following the Greek War of Independence (1821-27).</t>
+        </is>
+      </c>
     </row>
     <row r="240" ht="15" customHeight="1">
-      <c r="A240" s="5" t="n"/>
-      <c r="B240" s="6" t="n"/>
-      <c r="C240" s="5" t="n"/>
-      <c r="D240" s="7" t="n"/>
-      <c r="E240" s="6" t="n"/>
-      <c r="F240" s="6" t="n"/>
-      <c r="G240" s="6" t="n"/>
-      <c r="H240" s="6" t="n"/>
-      <c r="I240" s="6" t="n"/>
-      <c r="J240" s="7" t="n"/>
-      <c r="K240" s="5" t="n"/>
-      <c r="L240" s="6" t="n"/>
-      <c r="M240" s="5" t="n"/>
-      <c r="N240" s="5" t="n"/>
-      <c r="O240" s="5" t="n"/>
-      <c r="P240" s="8" t="n"/>
-      <c r="Q240" s="9" t="n"/>
+      <c r="A240" s="12" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="B240" s="13" t="inlineStr">
+        <is>
+          <t>Greece</t>
+        </is>
+      </c>
+      <c r="C240" s="12" t="inlineStr">
+        <is>
+          <t>GR</t>
+        </is>
+      </c>
+      <c r="D240" s="14" t="inlineStr">
+        <is>
+          <t>2021</t>
+        </is>
+      </c>
+      <c r="E240" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F240" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G240" s="13" t="inlineStr"/>
+      <c r="H240" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I240" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J240" s="14" t="inlineStr"/>
+      <c r="K240" s="12" t="inlineStr">
+        <is>
+          <t>255_Greece_2021_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L240" s="13" t="inlineStr"/>
+      <c r="M240" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N240" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O240" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P240" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Greece.</t>
+        </is>
+      </c>
+      <c r="Q240" s="16" t="inlineStr">
+        <is>
+          <t>The Minister for the National Economy and the Governor of the Bank of Greece chose the designs for their euro coins from a set of proposals presented by a national technical and artistic committee. The designer of the winning motifs was sculptor Georges Stamatopoulos, sponsored by the Bank of Greece. There is a separate design for each denomination. Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.
+Eleftherios Venizelos (1864-1936), one of Greece's most prominent political figures, is shown on this coin. He was a pioneer in social reform, a renowned diplomat and played a key role in modernising the Greek state and liberating Northern Greece and the Aegean islands.</t>
+        </is>
+      </c>
     </row>
     <row r="241" ht="15" customHeight="1">
-      <c r="A241" s="5" t="n"/>
-      <c r="B241" s="6" t="n"/>
-      <c r="C241" s="5" t="n"/>
-      <c r="D241" s="7" t="n"/>
-      <c r="E241" s="6" t="n"/>
-      <c r="F241" s="6" t="n"/>
-      <c r="G241" s="6" t="n"/>
-      <c r="H241" s="6" t="n"/>
-      <c r="I241" s="6" t="n"/>
-      <c r="J241" s="7" t="n"/>
-      <c r="K241" s="5" t="n"/>
-      <c r="L241" s="6" t="n"/>
-      <c r="M241" s="5" t="n"/>
-      <c r="N241" s="5" t="n"/>
-      <c r="O241" s="5" t="n"/>
-      <c r="P241" s="8" t="n"/>
-      <c r="Q241" s="9" t="n"/>
+      <c r="A241" s="12" t="inlineStr">
+        <is>
+          <t>256</t>
+        </is>
+      </c>
+      <c r="B241" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C241" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D241" s="14" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E241" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F241" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G241" s="13" t="inlineStr"/>
+      <c r="H241" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I241" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J241" s="14" t="inlineStr"/>
+      <c r="K241" s="12" t="inlineStr">
+        <is>
+          <t>256_Italy_2012_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L241" s="13" t="inlineStr"/>
+      <c r="M241" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N241" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O241" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P241" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q241" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+The Castel del Monte appears on this coin.</t>
+        </is>
+      </c>
     </row>
     <row r="242" ht="15" customHeight="1">
-      <c r="A242" s="5" t="n"/>
-      <c r="B242" s="6" t="n"/>
-      <c r="C242" s="5" t="n"/>
-      <c r="D242" s="7" t="n"/>
-      <c r="E242" s="6" t="n"/>
-      <c r="F242" s="6" t="n"/>
-      <c r="G242" s="6" t="n"/>
-      <c r="H242" s="6" t="n"/>
-      <c r="I242" s="6" t="n"/>
-      <c r="J242" s="7" t="n"/>
-      <c r="K242" s="5" t="n"/>
-      <c r="L242" s="6" t="n"/>
-      <c r="M242" s="5" t="n"/>
-      <c r="N242" s="5" t="n"/>
-      <c r="O242" s="5" t="n"/>
-      <c r="P242" s="8" t="n"/>
-      <c r="Q242" s="9" t="n"/>
+      <c r="A242" s="12" t="inlineStr">
+        <is>
+          <t>257</t>
+        </is>
+      </c>
+      <c r="B242" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C242" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D242" s="14" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="E242" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F242" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G242" s="13" t="inlineStr"/>
+      <c r="H242" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I242" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J242" s="14" t="inlineStr"/>
+      <c r="K242" s="12" t="inlineStr">
+        <is>
+          <t>257_Italy_2011_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L242" s="13" t="inlineStr"/>
+      <c r="M242" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N242" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O242" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P242" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q242" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+This coin shows the Mole Antonelliana, a tower designed in 1863 by Alessandro Antonelli.</t>
+        </is>
+      </c>
     </row>
     <row r="243" ht="15" customHeight="1">
-      <c r="A243" s="5" t="n"/>
-      <c r="B243" s="6" t="n"/>
-      <c r="C243" s="5" t="n"/>
-      <c r="D243" s="7" t="n"/>
-      <c r="E243" s="6" t="n"/>
-      <c r="F243" s="6" t="n"/>
-      <c r="G243" s="6" t="n"/>
-      <c r="H243" s="6" t="n"/>
-      <c r="I243" s="6" t="n"/>
-      <c r="J243" s="7" t="n"/>
-      <c r="K243" s="5" t="n"/>
-      <c r="L243" s="6" t="n"/>
-      <c r="M243" s="5" t="n"/>
-      <c r="N243" s="5" t="n"/>
-      <c r="O243" s="5" t="n"/>
-      <c r="P243" s="8" t="n"/>
-      <c r="Q243" s="9" t="n"/>
+      <c r="A243" s="12" t="inlineStr">
+        <is>
+          <t>258</t>
+        </is>
+      </c>
+      <c r="B243" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C243" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D243" s="14" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="E243" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F243" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G243" s="13" t="inlineStr"/>
+      <c r="H243" s="13" t="inlineStr">
+        <is>
+          <t>XF</t>
+        </is>
+      </c>
+      <c r="I243" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J243" s="14" t="inlineStr"/>
+      <c r="K243" s="12" t="inlineStr">
+        <is>
+          <t>258_Italy_2024_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L243" s="13" t="inlineStr"/>
+      <c r="M243" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N243" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O243" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P243" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q243" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+This design features the Flavius amphitheatre, which Emperor Vespasian began building around 75 AD and Emperor Titus inaugurated in 80 AD.</t>
+        </is>
+      </c>
     </row>
     <row r="244" ht="15" customHeight="1">
-      <c r="A244" s="5" t="n"/>
-      <c r="B244" s="6" t="n"/>
-      <c r="C244" s="5" t="n"/>
-      <c r="D244" s="7" t="n"/>
-      <c r="E244" s="6" t="n"/>
-      <c r="F244" s="6" t="n"/>
-      <c r="G244" s="6" t="n"/>
-      <c r="H244" s="6" t="n"/>
-      <c r="I244" s="6" t="n"/>
-      <c r="J244" s="7" t="n"/>
-      <c r="K244" s="5" t="n"/>
-      <c r="L244" s="6" t="n"/>
-      <c r="M244" s="5" t="n"/>
-      <c r="N244" s="5" t="n"/>
-      <c r="O244" s="5" t="n"/>
-      <c r="P244" s="8" t="n"/>
-      <c r="Q244" s="9" t="n"/>
+      <c r="A244" s="12" t="inlineStr">
+        <is>
+          <t>259</t>
+        </is>
+      </c>
+      <c r="B244" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C244" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D244" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E244" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F244" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G244" s="13" t="inlineStr"/>
+      <c r="H244" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I244" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J244" s="14" t="inlineStr"/>
+      <c r="K244" s="12" t="inlineStr">
+        <is>
+          <t>259_Italy_2006_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L244" s="13" t="inlineStr"/>
+      <c r="M244" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N244" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O244" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P244" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q244" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+This coin commemorates one of the greatest triumphs in Italian art. It shows one of the most famous works in the world, the "Birth of Venus" by Sandro Botticelli.</t>
+        </is>
+      </c>
     </row>
     <row r="245" ht="15" customHeight="1">
-      <c r="A245" s="5" t="n"/>
-      <c r="B245" s="6" t="n"/>
-      <c r="C245" s="5" t="n"/>
-      <c r="D245" s="7" t="n"/>
-      <c r="E245" s="6" t="n"/>
-      <c r="F245" s="6" t="n"/>
-      <c r="G245" s="6" t="n"/>
-      <c r="H245" s="6" t="n"/>
-      <c r="I245" s="6" t="n"/>
-      <c r="J245" s="7" t="n"/>
-      <c r="K245" s="5" t="n"/>
-      <c r="L245" s="6" t="n"/>
-      <c r="M245" s="5" t="n"/>
-      <c r="N245" s="5" t="n"/>
-      <c r="O245" s="5" t="n"/>
-      <c r="P245" s="8" t="n"/>
-      <c r="Q245" s="9" t="n"/>
+      <c r="A245" s="12" t="inlineStr">
+        <is>
+          <t>260</t>
+        </is>
+      </c>
+      <c r="B245" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C245" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D245" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E245" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F245" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G245" s="13" t="inlineStr"/>
+      <c r="H245" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I245" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J245" s="14" t="inlineStr"/>
+      <c r="K245" s="12" t="inlineStr">
+        <is>
+          <t>260_Italy_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L245" s="13" t="inlineStr"/>
+      <c r="M245" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N245" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O245" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P245" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q245" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+Portrayed on this coin is a sculpture by Umberto Boccioni, leader of the Italian futurist school.</t>
+        </is>
+      </c>
     </row>
     <row r="246" ht="15" customHeight="1">
-      <c r="A246" s="5" t="n"/>
-      <c r="B246" s="6" t="n"/>
-      <c r="C246" s="5" t="n"/>
-      <c r="D246" s="7" t="n"/>
-      <c r="E246" s="6" t="n"/>
-      <c r="F246" s="6" t="n"/>
-      <c r="G246" s="6" t="n"/>
-      <c r="H246" s="6" t="n"/>
-      <c r="I246" s="6" t="n"/>
-      <c r="J246" s="7" t="n"/>
-      <c r="K246" s="5" t="n"/>
-      <c r="L246" s="6" t="n"/>
-      <c r="M246" s="5" t="n"/>
-      <c r="N246" s="5" t="n"/>
-      <c r="O246" s="5" t="n"/>
-      <c r="P246" s="8" t="n"/>
-      <c r="Q246" s="9" t="n"/>
+      <c r="A246" s="12" t="inlineStr">
+        <is>
+          <t>261</t>
+        </is>
+      </c>
+      <c r="B246" s="13" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
+      <c r="C246" s="12" t="inlineStr">
+        <is>
+          <t>IT</t>
+        </is>
+      </c>
+      <c r="D246" s="14" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="E246" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F246" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G246" s="13" t="inlineStr"/>
+      <c r="H246" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I246" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J246" s="14" t="inlineStr"/>
+      <c r="K246" s="12" t="inlineStr">
+        <is>
+          <t>261_Italy_2023_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L246" s="13" t="inlineStr"/>
+      <c r="M246" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N246" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O246" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P246" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Italy.</t>
+        </is>
+      </c>
+      <c r="Q246" s="16" t="inlineStr">
+        <is>
+          <t>In Italy, the euro coin designs were subject to scrutiny by a national technical and artistic committee before being presented to the nation on RAI UNO, Italy's largest national television station. A different design has been selected for each denomination, chosen from masterpieces by Italy's famous artists. The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.
+The statue of Emperor Marcus Aurelius on horseback is the main feature on this coin.</t>
+        </is>
+      </c>
     </row>
     <row r="247" ht="15" customHeight="1">
       <c r="A247" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -17020,7 +17020,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G220" s="13" t="inlineStr"/>
+      <c r="G220" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
       <c r="H220" s="13" t="inlineStr">
         <is>
           <t>F</t>
@@ -19045,42 +19049,155 @@
       </c>
     </row>
     <row r="247" ht="15" customHeight="1">
-      <c r="A247" s="5" t="n"/>
-      <c r="B247" s="6" t="n"/>
-      <c r="C247" s="5" t="n"/>
-      <c r="D247" s="7" t="n"/>
-      <c r="E247" s="6" t="n"/>
-      <c r="F247" s="6" t="n"/>
-      <c r="G247" s="6" t="n"/>
-      <c r="H247" s="6" t="n"/>
-      <c r="I247" s="6" t="n"/>
-      <c r="J247" s="7" t="n"/>
-      <c r="K247" s="5" t="n"/>
-      <c r="L247" s="6" t="n"/>
-      <c r="M247" s="5" t="n"/>
-      <c r="N247" s="5" t="n"/>
-      <c r="O247" s="5" t="n"/>
-      <c r="P247" s="8" t="n"/>
-      <c r="Q247" s="9" t="n"/>
+      <c r="A247" s="12" t="inlineStr">
+        <is>
+          <t>262</t>
+        </is>
+      </c>
+      <c r="B247" s="13" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+      <c r="C247" s="12" t="inlineStr">
+        <is>
+          <t>LV</t>
+        </is>
+      </c>
+      <c r="D247" s="14" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="E247" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F247" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G247" s="13" t="inlineStr"/>
+      <c r="H247" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I247" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J247" s="14" t="inlineStr"/>
+      <c r="K247" s="12" t="inlineStr">
+        <is>
+          <t>262_Latvia_2014_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L247" s="13" t="inlineStr"/>
+      <c r="M247" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N247" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O247" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P247" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Latvia.</t>
+        </is>
+      </c>
+      <c r="Q247" s="16" t="inlineStr">
+        <is>
+          <t>The Latvian euro coins have been in circulation as of 1 January 2014.
+The 20 cent coin shows the large coat of arms of the Republic of Latvia. The designer is Laimonis Šēnbergs.</t>
+        </is>
+      </c>
     </row>
     <row r="248" ht="15" customHeight="1">
-      <c r="A248" s="5" t="n"/>
-      <c r="B248" s="6" t="n"/>
-      <c r="C248" s="5" t="n"/>
-      <c r="D248" s="7" t="n"/>
-      <c r="E248" s="6" t="n"/>
-      <c r="F248" s="6" t="n"/>
-      <c r="G248" s="6" t="n"/>
-      <c r="H248" s="6" t="n"/>
-      <c r="I248" s="6" t="n"/>
-      <c r="J248" s="7" t="n"/>
-      <c r="K248" s="5" t="n"/>
-      <c r="L248" s="6" t="n"/>
-      <c r="M248" s="5" t="n"/>
-      <c r="N248" s="5" t="n"/>
-      <c r="O248" s="5" t="n"/>
-      <c r="P248" s="8" t="n"/>
-      <c r="Q248" s="9" t="n"/>
+      <c r="A248" s="12" t="inlineStr">
+        <is>
+          <t>263</t>
+        </is>
+      </c>
+      <c r="B248" s="13" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C248" s="12" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D248" s="14" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E248" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F248" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G248" s="13" t="inlineStr"/>
+      <c r="H248" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I248" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J248" s="14" t="inlineStr"/>
+      <c r="K248" s="12" t="inlineStr">
+        <is>
+          <t>263_Lithuania_2015_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L248" s="13" t="inlineStr"/>
+      <c r="M248" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N248" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O248" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P248" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Lithuania.</t>
+        </is>
+      </c>
+      <c r="Q248" s="16" t="inlineStr">
+        <is>
+          <t>Lithuania’s euro coins show the coat of arms of the Republic of Lithuania, Vytis, the country of issuance "LIETUVA" and the year of issuance "2015". The coins also feature the 12 stars of the European flag. They were designed by the sculptor Antanas Žukauskas.</t>
+        </is>
+      </c>
     </row>
     <row r="249" ht="15" customHeight="1">
       <c r="A249" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -18547,10 +18547,14 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G240" s="13" t="inlineStr"/>
+      <c r="G240" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
       <c r="H240" s="13" t="inlineStr">
         <is>
-          <t>VF</t>
+          <t>XF</t>
         </is>
       </c>
       <c r="I240" s="13" t="inlineStr">
@@ -19200,232 +19204,909 @@
       </c>
     </row>
     <row r="249" ht="15" customHeight="1">
-      <c r="A249" s="5" t="n"/>
-      <c r="B249" s="6" t="n"/>
-      <c r="C249" s="5" t="n"/>
-      <c r="D249" s="7" t="n"/>
-      <c r="E249" s="6" t="n"/>
-      <c r="F249" s="6" t="n"/>
-      <c r="G249" s="6" t="n"/>
-      <c r="H249" s="6" t="n"/>
-      <c r="I249" s="6" t="n"/>
-      <c r="J249" s="7" t="n"/>
-      <c r="K249" s="5" t="n"/>
-      <c r="L249" s="6" t="n"/>
-      <c r="M249" s="5" t="n"/>
-      <c r="N249" s="5" t="n"/>
-      <c r="O249" s="5" t="n"/>
-      <c r="P249" s="8" t="n"/>
-      <c r="Q249" s="9" t="n"/>
+      <c r="A249" s="12" t="inlineStr">
+        <is>
+          <t>264</t>
+        </is>
+      </c>
+      <c r="B249" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C249" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D249" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E249" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F249" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G249" s="13" t="inlineStr"/>
+      <c r="H249" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I249" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J249" s="14" t="inlineStr"/>
+      <c r="K249" s="12" t="inlineStr">
+        <is>
+          <t>264_Ireland_2002_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L249" s="13" t="inlineStr"/>
+      <c r="M249" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N249" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O249" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P249" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q249" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
     </row>
     <row r="250" ht="15" customHeight="1">
-      <c r="A250" s="5" t="n"/>
-      <c r="B250" s="6" t="n"/>
-      <c r="C250" s="5" t="n"/>
-      <c r="D250" s="7" t="n"/>
-      <c r="E250" s="6" t="n"/>
-      <c r="F250" s="6" t="n"/>
-      <c r="G250" s="6" t="n"/>
-      <c r="H250" s="6" t="n"/>
-      <c r="I250" s="6" t="n"/>
-      <c r="J250" s="7" t="n"/>
-      <c r="K250" s="5" t="n"/>
-      <c r="L250" s="6" t="n"/>
-      <c r="M250" s="5" t="n"/>
-      <c r="N250" s="5" t="n"/>
-      <c r="O250" s="5" t="n"/>
-      <c r="P250" s="8" t="n"/>
-      <c r="Q250" s="9" t="n"/>
+      <c r="A250" s="12" t="inlineStr">
+        <is>
+          <t>265</t>
+        </is>
+      </c>
+      <c r="B250" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C250" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D250" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E250" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
+      <c r="F250" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G250" s="13" t="inlineStr"/>
+      <c r="H250" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I250" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J250" s="14" t="inlineStr"/>
+      <c r="K250" s="12" t="inlineStr">
+        <is>
+          <t>265_Ireland_2002_5cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L250" s="13" t="inlineStr"/>
+      <c r="M250" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N250" s="12" t="inlineStr">
+        <is>
+          <t>3.92 g</t>
+        </is>
+      </c>
+      <c r="O250" s="12" t="inlineStr">
+        <is>
+          <t>21.25 mm</t>
+        </is>
+      </c>
+      <c r="P250" s="15" t="inlineStr">
+        <is>
+          <t>Regular 5 cent circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q250" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
     </row>
     <row r="251" ht="15" customHeight="1">
-      <c r="A251" s="5" t="n"/>
-      <c r="B251" s="6" t="n"/>
-      <c r="C251" s="5" t="n"/>
-      <c r="D251" s="7" t="n"/>
-      <c r="E251" s="6" t="n"/>
-      <c r="F251" s="6" t="n"/>
-      <c r="G251" s="6" t="n"/>
-      <c r="H251" s="6" t="n"/>
-      <c r="I251" s="6" t="n"/>
-      <c r="J251" s="7" t="n"/>
-      <c r="K251" s="5" t="n"/>
-      <c r="L251" s="6" t="n"/>
-      <c r="M251" s="5" t="n"/>
-      <c r="N251" s="5" t="n"/>
-      <c r="O251" s="5" t="n"/>
-      <c r="P251" s="8" t="n"/>
-      <c r="Q251" s="9" t="n"/>
+      <c r="A251" s="12" t="inlineStr">
+        <is>
+          <t>266</t>
+        </is>
+      </c>
+      <c r="B251" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C251" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D251" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E251" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F251" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G251" s="13" t="inlineStr"/>
+      <c r="H251" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I251" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J251" s="14" t="inlineStr"/>
+      <c r="K251" s="12" t="inlineStr">
+        <is>
+          <t>266_Ireland_2002_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L251" s="13" t="inlineStr"/>
+      <c r="M251" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N251" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O251" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P251" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q251" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
     </row>
     <row r="252" ht="15" customHeight="1">
-      <c r="A252" s="5" t="n"/>
-      <c r="B252" s="6" t="n"/>
-      <c r="C252" s="5" t="n"/>
-      <c r="D252" s="7" t="n"/>
-      <c r="E252" s="6" t="n"/>
-      <c r="F252" s="6" t="n"/>
-      <c r="G252" s="6" t="n"/>
-      <c r="H252" s="6" t="n"/>
-      <c r="I252" s="6" t="n"/>
-      <c r="J252" s="7" t="n"/>
-      <c r="K252" s="5" t="n"/>
-      <c r="L252" s="6" t="n"/>
-      <c r="M252" s="5" t="n"/>
-      <c r="N252" s="5" t="n"/>
-      <c r="O252" s="5" t="n"/>
-      <c r="P252" s="8" t="n"/>
-      <c r="Q252" s="9" t="n"/>
+      <c r="A252" s="12" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="B252" s="13" t="inlineStr">
+        <is>
+          <t>Ireland</t>
+        </is>
+      </c>
+      <c r="C252" s="12" t="inlineStr">
+        <is>
+          <t>IE</t>
+        </is>
+      </c>
+      <c r="D252" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E252" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F252" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G252" s="13" t="inlineStr"/>
+      <c r="H252" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I252" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J252" s="14" t="inlineStr"/>
+      <c r="K252" s="12" t="inlineStr">
+        <is>
+          <t>267_Ireland_2002_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L252" s="13" t="inlineStr"/>
+      <c r="M252" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N252" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O252" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P252" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Ireland.</t>
+        </is>
+      </c>
+      <c r="Q252" s="16" t="inlineStr">
+        <is>
+          <t>The Government of Ireland decided on a single national design for all Irish coin denominations. They show the Celtic harp, a traditional symbol of Ireland, decorated with the year of issue and the inscription "Éire" − the Irish word for Ireland. The harp shown was designed by Jarlath Hayes.</t>
+        </is>
+      </c>
     </row>
     <row r="253" ht="15" customHeight="1">
-      <c r="A253" s="5" t="n"/>
-      <c r="B253" s="6" t="n"/>
-      <c r="C253" s="5" t="n"/>
-      <c r="D253" s="7" t="n"/>
-      <c r="E253" s="6" t="n"/>
-      <c r="F253" s="6" t="n"/>
-      <c r="G253" s="6" t="n"/>
-      <c r="H253" s="6" t="n"/>
-      <c r="I253" s="6" t="n"/>
-      <c r="J253" s="7" t="n"/>
-      <c r="K253" s="5" t="n"/>
-      <c r="L253" s="6" t="n"/>
-      <c r="M253" s="5" t="n"/>
-      <c r="N253" s="5" t="n"/>
-      <c r="O253" s="5" t="n"/>
-      <c r="P253" s="8" t="n"/>
-      <c r="Q253" s="9" t="n"/>
+      <c r="A253" s="12" t="inlineStr">
+        <is>
+          <t>268</t>
+        </is>
+      </c>
+      <c r="B253" s="13" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C253" s="12" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D253" s="14" t="inlineStr">
+        <is>
+          <t>2017</t>
+        </is>
+      </c>
+      <c r="E253" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F253" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G253" s="13" t="inlineStr"/>
+      <c r="H253" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I253" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J253" s="14" t="inlineStr"/>
+      <c r="K253" s="12" t="inlineStr">
+        <is>
+          <t>268_Lithuania_2017_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L253" s="13" t="inlineStr"/>
+      <c r="M253" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N253" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O253" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P253" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Lithuania.</t>
+        </is>
+      </c>
+      <c r="Q253" s="16" t="inlineStr">
+        <is>
+          <t>Lithuania’s euro coins show the coat of arms of the Republic of Lithuania, Vytis, the country of issuance "LIETUVA" and the year of issuance "2015". The coins also feature the 12 stars of the European flag. They were designed by the sculptor Antanas Žukauskas.</t>
+        </is>
+      </c>
     </row>
     <row r="254" ht="15" customHeight="1">
-      <c r="A254" s="5" t="n"/>
-      <c r="B254" s="6" t="n"/>
-      <c r="C254" s="5" t="n"/>
-      <c r="D254" s="7" t="n"/>
-      <c r="E254" s="6" t="n"/>
-      <c r="F254" s="6" t="n"/>
-      <c r="G254" s="6" t="n"/>
-      <c r="H254" s="6" t="n"/>
-      <c r="I254" s="6" t="n"/>
-      <c r="J254" s="7" t="n"/>
-      <c r="K254" s="5" t="n"/>
-      <c r="L254" s="6" t="n"/>
-      <c r="M254" s="5" t="n"/>
-      <c r="N254" s="5" t="n"/>
-      <c r="O254" s="5" t="n"/>
-      <c r="P254" s="8" t="n"/>
-      <c r="Q254" s="9" t="n"/>
+      <c r="A254" s="12" t="inlineStr">
+        <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="B254" s="13" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C254" s="12" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D254" s="14" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E254" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F254" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G254" s="13" t="inlineStr"/>
+      <c r="H254" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I254" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J254" s="14" t="inlineStr"/>
+      <c r="K254" s="12" t="inlineStr">
+        <is>
+          <t>269_Lithuania_2015_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L254" s="13" t="inlineStr"/>
+      <c r="M254" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N254" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O254" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P254" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Lithuania.</t>
+        </is>
+      </c>
+      <c r="Q254" s="16" t="inlineStr">
+        <is>
+          <t>Lithuania’s euro coins show the coat of arms of the Republic of Lithuania, Vytis, the country of issuance "LIETUVA" and the year of issuance "2015". The coins also feature the 12 stars of the European flag. They were designed by the sculptor Antanas Žukauskas.</t>
+        </is>
+      </c>
     </row>
     <row r="255" ht="15" customHeight="1">
-      <c r="A255" s="5" t="n"/>
-      <c r="B255" s="6" t="n"/>
-      <c r="C255" s="5" t="n"/>
-      <c r="D255" s="7" t="n"/>
-      <c r="E255" s="6" t="n"/>
-      <c r="F255" s="6" t="n"/>
-      <c r="G255" s="6" t="n"/>
-      <c r="H255" s="6" t="n"/>
-      <c r="I255" s="6" t="n"/>
-      <c r="J255" s="7" t="n"/>
-      <c r="K255" s="5" t="n"/>
-      <c r="L255" s="6" t="n"/>
-      <c r="M255" s="5" t="n"/>
-      <c r="N255" s="5" t="n"/>
-      <c r="O255" s="5" t="n"/>
-      <c r="P255" s="8" t="n"/>
-      <c r="Q255" s="9" t="n"/>
+      <c r="A255" s="12" t="inlineStr">
+        <is>
+          <t>270</t>
+        </is>
+      </c>
+      <c r="B255" s="13" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+      <c r="C255" s="12" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="D255" s="14" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="E255" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F255" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G255" s="13" t="inlineStr"/>
+      <c r="H255" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I255" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J255" s="14" t="inlineStr"/>
+      <c r="K255" s="12" t="inlineStr">
+        <is>
+          <t>270_Lithuania_2015_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L255" s="13" t="inlineStr"/>
+      <c r="M255" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N255" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O255" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P255" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Lithuania.</t>
+        </is>
+      </c>
+      <c r="Q255" s="16" t="inlineStr">
+        <is>
+          <t>Lithuania’s euro coins show the coat of arms of the Republic of Lithuania, Vytis, the country of issuance "LIETUVA" and the year of issuance "2015". The coins also feature the 12 stars of the European flag. They were designed by the sculptor Antanas Žukauskas.</t>
+        </is>
+      </c>
     </row>
     <row r="256" ht="15" customHeight="1">
-      <c r="A256" s="5" t="n"/>
-      <c r="B256" s="6" t="n"/>
-      <c r="C256" s="5" t="n"/>
-      <c r="D256" s="7" t="n"/>
-      <c r="E256" s="6" t="n"/>
-      <c r="F256" s="6" t="n"/>
-      <c r="G256" s="6" t="n"/>
-      <c r="H256" s="6" t="n"/>
-      <c r="I256" s="6" t="n"/>
-      <c r="J256" s="7" t="n"/>
-      <c r="K256" s="5" t="n"/>
-      <c r="L256" s="6" t="n"/>
-      <c r="M256" s="5" t="n"/>
-      <c r="N256" s="5" t="n"/>
-      <c r="O256" s="5" t="n"/>
-      <c r="P256" s="8" t="n"/>
-      <c r="Q256" s="9" t="n"/>
+      <c r="A256" s="12" t="inlineStr">
+        <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="B256" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C256" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D256" s="14" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="E256" s="13" t="inlineStr">
+        <is>
+          <t>1 cent</t>
+        </is>
+      </c>
+      <c r="F256" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G256" s="13" t="inlineStr"/>
+      <c r="H256" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I256" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J256" s="14" t="inlineStr"/>
+      <c r="K256" s="12" t="inlineStr">
+        <is>
+          <t>271_Luxembourg_2014_1cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L256" s="13" t="inlineStr"/>
+      <c r="M256" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N256" s="12" t="inlineStr">
+        <is>
+          <t>2.30 g</t>
+        </is>
+      </c>
+      <c r="O256" s="12" t="inlineStr">
+        <is>
+          <t>16.25 mm</t>
+        </is>
+      </c>
+      <c r="P256" s="15" t="inlineStr">
+        <is>
+          <t>Regular 1 cent circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q256" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").</t>
+        </is>
+      </c>
     </row>
     <row r="257" ht="15" customHeight="1">
-      <c r="A257" s="5" t="n"/>
-      <c r="B257" s="6" t="n"/>
-      <c r="C257" s="5" t="n"/>
-      <c r="D257" s="7" t="n"/>
-      <c r="E257" s="6" t="n"/>
-      <c r="F257" s="6" t="n"/>
-      <c r="G257" s="6" t="n"/>
-      <c r="H257" s="6" t="n"/>
-      <c r="I257" s="6" t="n"/>
-      <c r="J257" s="7" t="n"/>
-      <c r="K257" s="5" t="n"/>
-      <c r="L257" s="6" t="n"/>
-      <c r="M257" s="5" t="n"/>
-      <c r="N257" s="5" t="n"/>
-      <c r="O257" s="5" t="n"/>
-      <c r="P257" s="8" t="n"/>
-      <c r="Q257" s="9" t="n"/>
+      <c r="A257" s="12" t="inlineStr">
+        <is>
+          <t>272</t>
+        </is>
+      </c>
+      <c r="B257" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C257" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D257" s="14" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="E257" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F257" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G257" s="13" t="inlineStr"/>
+      <c r="H257" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I257" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J257" s="14" t="inlineStr"/>
+      <c r="K257" s="12" t="inlineStr">
+        <is>
+          <t>272_Luxembourg_2014_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L257" s="13" t="inlineStr"/>
+      <c r="M257" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N257" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O257" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P257" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q257" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").</t>
+        </is>
+      </c>
     </row>
     <row r="258" ht="15" customHeight="1">
-      <c r="A258" s="5" t="n"/>
-      <c r="B258" s="6" t="n"/>
-      <c r="C258" s="5" t="n"/>
-      <c r="D258" s="7" t="n"/>
-      <c r="E258" s="6" t="n"/>
-      <c r="F258" s="6" t="n"/>
-      <c r="G258" s="6" t="n"/>
-      <c r="H258" s="6" t="n"/>
-      <c r="I258" s="6" t="n"/>
-      <c r="J258" s="7" t="n"/>
-      <c r="K258" s="5" t="n"/>
-      <c r="L258" s="6" t="n"/>
-      <c r="M258" s="5" t="n"/>
-      <c r="N258" s="5" t="n"/>
-      <c r="O258" s="5" t="n"/>
-      <c r="P258" s="8" t="n"/>
-      <c r="Q258" s="9" t="n"/>
+      <c r="A258" s="12" t="inlineStr">
+        <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="B258" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C258" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D258" s="14" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="E258" s="13" t="inlineStr">
+        <is>
+          <t>10 cent</t>
+        </is>
+      </c>
+      <c r="F258" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G258" s="13" t="inlineStr"/>
+      <c r="H258" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I258" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J258" s="14" t="inlineStr"/>
+      <c r="K258" s="12" t="inlineStr">
+        <is>
+          <t>273_Luxembourg_2002_10cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L258" s="13" t="inlineStr"/>
+      <c r="M258" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N258" s="12" t="inlineStr">
+        <is>
+          <t>4.10 g</t>
+        </is>
+      </c>
+      <c r="O258" s="12" t="inlineStr">
+        <is>
+          <t>19.75 mm</t>
+        </is>
+      </c>
+      <c r="P258" s="15" t="inlineStr">
+        <is>
+          <t>Regular 10 cent circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q258" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").</t>
+        </is>
+      </c>
     </row>
     <row r="259" ht="15" customHeight="1">
-      <c r="A259" s="5" t="n"/>
-      <c r="B259" s="6" t="n"/>
-      <c r="C259" s="5" t="n"/>
-      <c r="D259" s="7" t="n"/>
-      <c r="E259" s="6" t="n"/>
-      <c r="F259" s="6" t="n"/>
-      <c r="G259" s="6" t="n"/>
-      <c r="H259" s="6" t="n"/>
-      <c r="I259" s="6" t="n"/>
-      <c r="J259" s="7" t="n"/>
-      <c r="K259" s="5" t="n"/>
-      <c r="L259" s="6" t="n"/>
-      <c r="M259" s="5" t="n"/>
-      <c r="N259" s="5" t="n"/>
-      <c r="O259" s="5" t="n"/>
-      <c r="P259" s="8" t="n"/>
-      <c r="Q259" s="9" t="n"/>
+      <c r="A259" s="12" t="inlineStr">
+        <is>
+          <t>274</t>
+        </is>
+      </c>
+      <c r="B259" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C259" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D259" s="14" t="inlineStr">
+        <is>
+          <t>2013</t>
+        </is>
+      </c>
+      <c r="E259" s="13" t="inlineStr">
+        <is>
+          <t>20 cent</t>
+        </is>
+      </c>
+      <c r="F259" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G259" s="13" t="inlineStr"/>
+      <c r="H259" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I259" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J259" s="14" t="inlineStr"/>
+      <c r="K259" s="12" t="inlineStr">
+        <is>
+          <t>274_Luxembourg_2013_20cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L259" s="13" t="inlineStr"/>
+      <c r="M259" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N259" s="12" t="inlineStr">
+        <is>
+          <t>5.74 g</t>
+        </is>
+      </c>
+      <c r="O259" s="12" t="inlineStr">
+        <is>
+          <t>22.25 mm</t>
+        </is>
+      </c>
+      <c r="P259" s="15" t="inlineStr">
+        <is>
+          <t>Regular 20 cent circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q259" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").</t>
+        </is>
+      </c>
     </row>
     <row r="260" ht="15" customHeight="1">
-      <c r="A260" s="5" t="n"/>
-      <c r="B260" s="6" t="n"/>
-      <c r="C260" s="5" t="n"/>
-      <c r="D260" s="7" t="n"/>
-      <c r="E260" s="6" t="n"/>
-      <c r="F260" s="6" t="n"/>
-      <c r="G260" s="6" t="n"/>
-      <c r="H260" s="6" t="n"/>
-      <c r="I260" s="6" t="n"/>
-      <c r="J260" s="7" t="n"/>
-      <c r="K260" s="5" t="n"/>
-      <c r="L260" s="6" t="n"/>
-      <c r="M260" s="5" t="n"/>
-      <c r="N260" s="5" t="n"/>
-      <c r="O260" s="5" t="n"/>
-      <c r="P260" s="8" t="n"/>
-      <c r="Q260" s="9" t="n"/>
+      <c r="A260" s="12" t="inlineStr">
+        <is>
+          <t>275</t>
+        </is>
+      </c>
+      <c r="B260" s="13" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+      <c r="C260" s="12" t="inlineStr">
+        <is>
+          <t>LU</t>
+        </is>
+      </c>
+      <c r="D260" s="14" t="inlineStr">
+        <is>
+          <t>2004</t>
+        </is>
+      </c>
+      <c r="E260" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
+      <c r="F260" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G260" s="13" t="inlineStr"/>
+      <c r="H260" s="13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="I260" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J260" s="14" t="inlineStr"/>
+      <c r="K260" s="12" t="inlineStr">
+        <is>
+          <t>275_Luxembourg_2004_50cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L260" s="13" t="inlineStr"/>
+      <c r="M260" s="12" t="inlineStr">
+        <is>
+          <t>Nordic gold</t>
+        </is>
+      </c>
+      <c r="N260" s="12" t="inlineStr">
+        <is>
+          <t>7.80 g</t>
+        </is>
+      </c>
+      <c r="O260" s="12" t="inlineStr">
+        <is>
+          <t>24.25 mm</t>
+        </is>
+      </c>
+      <c r="P260" s="15" t="inlineStr">
+        <is>
+          <t>Regular 50 cent circulation coin of Luxembourg.</t>
+        </is>
+      </c>
+      <c r="Q260" s="16" t="inlineStr">
+        <is>
+          <t>Yvette Gastauer-Claire designed the coins by agreement with the Royal Household and the Luxembourg Government.
+All the Luxembourg coins bear the profile of His Royal Highness Grand Duke Henri. They also bear the year of issue and the word "Luxembourg" written in Luxembourgish ("Lëtzebuerg").</t>
+        </is>
+      </c>
     </row>
     <row r="261" ht="15" customHeight="1">
       <c r="A261" s="5" t="n"/>

--- a/data/Euro_Coin_Catalog_Automation.xlsx
+++ b/data/Euro_Coin_Catalog_Automation.xlsx
@@ -16120,7 +16120,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G208" s="13" t="inlineStr"/>
+      <c r="G208" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
       <c r="H208" s="13" t="inlineStr">
         <is>
           <t>F</t>
@@ -16270,7 +16274,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G210" s="13" t="inlineStr"/>
+      <c r="G210" s="13" t="inlineStr">
+        <is>
+          <t>5 cent</t>
+        </is>
+      </c>
       <c r="H210" s="13" t="inlineStr">
         <is>
           <t>F</t>
@@ -16795,7 +16803,11 @@
           <t>Regular</t>
         </is>
       </c>
-      <c r="G217" s="13" t="inlineStr"/>
+      <c r="G217" s="13" t="inlineStr">
+        <is>
+          <t>50 cent</t>
+        </is>
+      </c>
       <c r="H217" s="13" t="inlineStr">
         <is>
           <t>F</t>
@@ -20109,23 +20121,79 @@
       </c>
     </row>
     <row r="261" ht="15" customHeight="1">
-      <c r="A261" s="5" t="n"/>
-      <c r="B261" s="6" t="n"/>
-      <c r="C261" s="5" t="n"/>
-      <c r="D261" s="7" t="n"/>
-      <c r="E261" s="6" t="n"/>
-      <c r="F261" s="6" t="n"/>
-      <c r="G261" s="6" t="n"/>
-      <c r="H261" s="6" t="n"/>
-      <c r="I261" s="6" t="n"/>
-      <c r="J261" s="7" t="n"/>
-      <c r="K261" s="5" t="n"/>
-      <c r="L261" s="6" t="n"/>
-      <c r="M261" s="5" t="n"/>
-      <c r="N261" s="5" t="n"/>
-      <c r="O261" s="5" t="n"/>
-      <c r="P261" s="8" t="n"/>
-      <c r="Q261" s="9" t="n"/>
+      <c r="A261" s="12" t="inlineStr">
+        <is>
+          <t>276</t>
+        </is>
+      </c>
+      <c r="B261" s="13" t="inlineStr">
+        <is>
+          <t>Belgium</t>
+        </is>
+      </c>
+      <c r="C261" s="12" t="inlineStr">
+        <is>
+          <t>BE</t>
+        </is>
+      </c>
+      <c r="D261" s="14" t="inlineStr">
+        <is>
+          <t>2006</t>
+        </is>
+      </c>
+      <c r="E261" s="13" t="inlineStr">
+        <is>
+          <t>2 cent</t>
+        </is>
+      </c>
+      <c r="F261" s="13" t="inlineStr">
+        <is>
+          <t>Regular</t>
+        </is>
+      </c>
+      <c r="G261" s="13" t="inlineStr"/>
+      <c r="H261" s="13" t="inlineStr">
+        <is>
+          <t>VF</t>
+        </is>
+      </c>
+      <c r="I261" s="13" t="inlineStr">
+        <is>
+          <t>Collection</t>
+        </is>
+      </c>
+      <c r="J261" s="14" t="inlineStr"/>
+      <c r="K261" s="12" t="inlineStr">
+        <is>
+          <t>276_Belgium_2006_2cent_Regular.jpeg</t>
+        </is>
+      </c>
+      <c r="L261" s="13" t="inlineStr"/>
+      <c r="M261" s="12" t="inlineStr">
+        <is>
+          <t>Copper-plated steel</t>
+        </is>
+      </c>
+      <c r="N261" s="12" t="inlineStr">
+        <is>
+          <t>3.06 g</t>
+        </is>
+      </c>
+      <c r="O261" s="12" t="inlineStr">
+        <is>
+          <t>18.75 mm</t>
+        </is>
+      </c>
+      <c r="P261" s="15" t="inlineStr">
+        <is>
+          <t>Regular 2 cent circulation coin of Belgium.</t>
+        </is>
+      </c>
+      <c r="Q261" s="16" t="inlineStr">
+        <is>
+          <t>All denominations of the first series, issued in 2002, show the effigy of His Majesty Albert II, King of the Belgians, encircled by the twelve stars of the European Union with the royal monogram (capital 'A' and crown) to the right. The Belgian euro coins were designed by Jan Alfons Keustermans, Director of the Municipal Academy of Fine Arts of Turnhout, and chosen by a panel made up of high-ranked officials, experts in numismatics and artists.</t>
+        </is>
+      </c>
     </row>
     <row r="262" ht="15" customHeight="1">
       <c r="A262" s="5" t="n"/>
